--- a/back/storage/app/ads/2026-10/meta-okt-Format.xlsx
+++ b/back/storage/app/ads/2026-10/meta-okt-Format.xlsx
@@ -1,14 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr date1904="false"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\projects\pulse-kembaliapps\ads-performance\back\storage\app\ads\2026-10\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1889F0B6-8660-4E6B-B539-3B9BEFC263EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Formatted Report" r:id="rId3" sheetId="1"/>
-    <sheet name="Raw Data Report" r:id="rId4" sheetId="2" state="hidden"/>
+    <sheet name="Formatted Report" sheetId="1" r:id="rId1"/>
+    <sheet name="Raw Data Report" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -141,85 +149,70 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="d/m"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color indexed="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <sz val="11.0"/>
-      <color rgb="FF000000"/>
-      <u val="none"/>
     </font>
     <font>
+      <sz val="18"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-      <sz val="11.0"/>
-      <color rgb="FF000000"/>
-      <u val="none"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-      <sz val="18.0"/>
-      <color rgb="FFFFFFFF"/>
-      <u val="none"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-      <sz val="11.0"/>
-      <color rgb="FFFFFFFF"/>
-      <u val="none"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <sz val="11.0"/>
-      <color rgb="FFFFFFFF"/>
-      <u val="single"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <color rgb="FF000000"/>
-      <b val="true"/>
-      <u val="none"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="darkGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
-      <patternFill patternType="none">
-        <fgColor rgb="FFFFFF"/>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF"/>
+        <fgColor rgb="FF41596C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="41596C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="A0B0BA"/>
+        <fgColor rgb="FFA0B0BA"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="32">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -230,423 +223,123 @@
     <border>
       <left/>
       <right/>
-      <top>
-        <color rgb="000000"/>
-      </top>
+      <top/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top>
-        <color rgb="000000"/>
+      <top style="thin">
+        <color rgb="FF000000"/>
       </top>
-      <bottom>
-        <color rgb="000000"/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right>
-        <color rgb="000000"/>
-      </right>
-      <top>
-        <color rgb="000000"/>
-      </top>
-      <bottom>
-        <color rgb="000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left>
-        <color rgb="000000"/>
-      </left>
-      <right>
-        <color rgb="000000"/>
-      </right>
-      <top>
-        <color rgb="000000"/>
-      </top>
-      <bottom>
-        <color rgb="000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left>
-        <color rgb="000000"/>
-      </left>
-      <right>
-        <color rgb="000000"/>
-      </right>
-      <bottom>
-        <color rgb="000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left>
-        <color rgb="000000"/>
-      </left>
-      <right>
-        <color rgb="000000"/>
-      </right>
-      <top>
-        <color rgb="000000"/>
-      </top>
-      <diagonal/>
-    </border>
-    <border>
-      <left>
-        <color rgb="000000"/>
-      </left>
-      <top>
-        <color rgb="000000"/>
-      </top>
-      <bottom>
-        <color rgb="000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left>
-        <color rgb="000000"/>
-      </left>
-      <right>
-        <color rgb="000000"/>
+      <right style="thin">
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color rgb="000000"/>
-      </top>
-      <bottom>
-        <color rgb="000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left>
-        <color rgb="000000"/>
-      </left>
-      <right>
-        <color rgb="000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="000000"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color rgb="000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left>
-        <color rgb="000000"/>
-      </left>
-      <top style="thin">
-        <color rgb="000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="000000"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="000000"/>
+        <color rgb="FF000000"/>
       </left>
-      <right>
-        <color rgb="000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="000000"/>
-      </bottom>
+      <right/>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
-      <right>
-        <color rgb="000000"/>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
       </right>
-      <top style="thin">
-        <color rgb="000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="000000"/>
-      </bottom>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left>
-        <color rgb="000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="000000"/>
-      </top>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
-        <color rgb="000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <right style="thin">
-        <color rgb="000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="000000"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="000000"/>
+        <color rgb="FF000000"/>
       </left>
-      <right>
-        <color rgb="000000"/>
-      </right>
-      <top>
-        <color rgb="000000"/>
-      </top>
-      <bottom>
-        <color rgb="000000"/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left>
-        <color rgb="000000"/>
-      </left>
+      <left/>
       <right style="thin">
-        <color rgb="000000"/>
+        <color rgb="FF000000"/>
       </right>
-      <top>
-        <color rgb="000000"/>
-      </top>
-      <bottom>
-        <color rgb="000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <right style="thin">
-        <color rgb="000000"/>
-      </right>
-      <top>
-        <color rgb="000000"/>
-      </top>
-      <bottom>
-        <color rgb="000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left>
-        <color rgb="000000"/>
-      </left>
-      <right>
-        <color rgb="000000"/>
-      </right>
-      <top>
-        <color rgb="000000"/>
-      </top>
+      <top/>
       <bottom style="thin">
-        <color rgb="000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left>
-        <color rgb="000000"/>
-      </left>
-      <top>
-        <color rgb="000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="000000"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="000000"/>
+        <color rgb="FF90949C"/>
       </left>
-      <right>
-        <color rgb="000000"/>
+      <right style="thin">
+        <color rgb="FF90949C"/>
       </right>
-      <top>
-        <color rgb="000000"/>
+      <top style="thin">
+        <color rgb="FF90949C"/>
       </top>
       <bottom style="thin">
-        <color rgb="000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <right>
-        <color rgb="000000"/>
-      </right>
-      <top>
-        <color rgb="000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left>
-        <color rgb="000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="000000"/>
-      </right>
-      <top>
-        <color rgb="000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <right style="thin">
-        <color rgb="000000"/>
-      </right>
-      <top>
-        <color rgb="000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left>
-        <color rgb="000000"/>
-      </left>
-      <right>
-        <color rgb="000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="90949C"/>
-      </top>
-      <bottom>
-        <color rgb="000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left>
-        <color rgb="000000"/>
-      </left>
-      <right>
-        <color rgb="000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="90949C"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left>
-        <color rgb="000000"/>
-      </left>
-      <right>
-        <color rgb="000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="90949C"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="90949C"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left>
-        <color rgb="000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="90949C"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="90949C"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left>
-        <color rgb="000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="90949C"/>
-      </right>
-      <top style="thin">
-        <color rgb="90949C"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="90949C"/>
+        <color rgb="FF90949C"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="000000"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color rgb="90949C"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color rgb="90949C"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color rgb="90949C"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="90949C"/>
-      </left>
-      <right style="thin">
-        <color rgb="90949C"/>
-      </right>
-      <top style="thin">
-        <color rgb="90949C"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="90949C"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="000000"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -655,145 +348,123 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="33">
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="9" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="3" borderId="15" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="3" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="3" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="3" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="3" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="3" borderId="16" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="3" borderId="20" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="3" borderId="18" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="3" borderId="18" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="3" borderId="18" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="3" borderId="18" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="18" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="3" borderId="22" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="3" borderId="30" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="3" borderId="30" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="31" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="3" borderId="31" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="3" borderId="31" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="31" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <xdr:twoCellAnchor editAs="twoCell">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>95250</xdr:colOff>
@@ -808,13 +479,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="Picture 1" descr="Picture"/>
+        <xdr:cNvPr id="2" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="true"/>
+          <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -835,8 +512,8 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <xdr:twoCellAnchor editAs="twoCell">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>95250</xdr:colOff>
@@ -851,13 +528,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="Picture 1" descr="Picture"/>
+        <xdr:cNvPr id="2" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="true"/>
+          <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -877,34 +560,315 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4472C4"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:S33"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetFormatPr defaultColWidth="12.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="20" max="16384" style="1" width="12.7109375"/>
-    <col min="19" max="19" style="1" width="23.4375" customWidth="true"/>
-    <col min="18" max="18" style="1" width="23.4375" customWidth="true"/>
-    <col min="17" max="17" style="1" width="23.4375" customWidth="true"/>
-    <col min="16" max="16" style="1" width="23.4375" customWidth="true"/>
-    <col min="15" max="15" style="1" width="23.4375" customWidth="true"/>
-    <col min="14" max="14" style="1" width="23.4375" customWidth="true"/>
-    <col min="13" max="13" style="1" width="23.4375" customWidth="true"/>
-    <col min="12" max="12" style="1" width="23.4375" customWidth="true"/>
-    <col min="11" max="11" style="1" width="23.4375" customWidth="true"/>
-    <col min="10" max="10" style="1" width="23.4375" customWidth="true"/>
-    <col min="9" max="9" style="1" width="23.4375" customWidth="true"/>
-    <col min="8" max="8" style="1" width="23.4375" customWidth="true"/>
-    <col min="7" max="7" style="1" width="23.4375" customWidth="true"/>
-    <col min="6" max="6" style="1" width="23.4375" customWidth="true"/>
-    <col min="5" max="5" style="1" width="1.953125" customWidth="true"/>
-    <col min="4" max="4" style="1" width="23.4375" customWidth="true"/>
-    <col min="3" max="3" style="1" width="23.4375" customWidth="true"/>
-    <col min="2" max="2" style="1" width="58.59375" customWidth="true"/>
-    <col min="1" max="1" width="5.15625" style="1" customWidth="true"/>
+    <col min="1" max="1" width="5.1796875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="58.6328125" style="1" customWidth="1"/>
+    <col min="3" max="4" width="23.453125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="1.90625" style="1" customWidth="1"/>
+    <col min="6" max="19" width="23.453125" style="1" customWidth="1"/>
+    <col min="20" max="16384" width="12.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="33.0" customHeight="true" s="5" customFormat="true">
+    <row r="1" spans="1:19" s="5" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2"/>
       <c r="B1" s="3" t="s">
         <v>0</v>
@@ -916,7 +880,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B3" s="7" t="s">
         <v>3</v>
       </c>
@@ -972,7 +936,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B4" s="11" t="s">
         <v>20</v>
       </c>
@@ -991,32 +955,32 @@
       <c r="G4" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="H4" s="14" t="n">
-        <v>30124.0</v>
-      </c>
-      <c r="I4" s="14" t="n">
-        <v>49624.0</v>
-      </c>
-      <c r="J4" s="12" t="n">
-        <v>1.64732439</v>
+      <c r="H4" s="14">
+        <v>30124</v>
+      </c>
+      <c r="I4" s="14">
+        <v>49624</v>
+      </c>
+      <c r="J4" s="12">
+        <v>1.6473243900000001</v>
       </c>
       <c r="K4" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="L4" s="12" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="M4" s="15" t="n">
-        <v>1017845.0</v>
-      </c>
-      <c r="N4" s="15" t="n">
-        <v>127230.625</v>
-      </c>
-      <c r="O4" s="12" t="n">
-        <v>44783.0</v>
-      </c>
-      <c r="P4" s="12" t="n">
-        <v>436.0</v>
+      <c r="L4" s="12">
+        <v>8</v>
+      </c>
+      <c r="M4" s="15">
+        <v>1017845</v>
+      </c>
+      <c r="N4" s="15">
+        <v>227230.625</v>
+      </c>
+      <c r="O4" s="12">
+        <v>44783</v>
+      </c>
+      <c r="P4" s="12">
+        <v>436</v>
       </c>
       <c r="Q4" s="16" t="s">
         <v>25</v>
@@ -1028,7 +992,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B5" s="11" t="s">
         <v>2</v>
       </c>
@@ -1047,32 +1011,32 @@
       <c r="G5" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="H5" s="14" t="n">
-        <v>5384.0</v>
-      </c>
-      <c r="I5" s="14" t="n">
-        <v>6921.0</v>
-      </c>
-      <c r="J5" s="12" t="n">
-        <v>1.28547548</v>
+      <c r="H5" s="14">
+        <v>5384</v>
+      </c>
+      <c r="I5" s="14">
+        <v>6921</v>
+      </c>
+      <c r="J5" s="12">
+        <v>1.2854754799999999</v>
       </c>
       <c r="K5" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="L5" s="12" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="M5" s="15" t="n">
-        <v>116395.0</v>
-      </c>
-      <c r="N5" s="15" t="n">
+      <c r="L5" s="12">
+        <v>2</v>
+      </c>
+      <c r="M5" s="15">
+        <v>116395</v>
+      </c>
+      <c r="N5" s="15">
         <v>58197.5</v>
       </c>
-      <c r="O5" s="12" t="n">
-        <v>6046.0</v>
-      </c>
-      <c r="P5" s="12" t="n">
-        <v>114.0</v>
+      <c r="O5" s="12">
+        <v>6046</v>
+      </c>
+      <c r="P5" s="12">
+        <v>114</v>
       </c>
       <c r="Q5" s="16" t="s">
         <v>26</v>
@@ -1084,7 +1048,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B6" s="11" t="s">
         <v>2</v>
       </c>
@@ -1103,32 +1067,32 @@
       <c r="G6" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="H6" s="14" t="n">
-        <v>5384.0</v>
-      </c>
-      <c r="I6" s="14" t="n">
-        <v>6921.0</v>
-      </c>
-      <c r="J6" s="12" t="n">
-        <v>1.28547548</v>
+      <c r="H6" s="14">
+        <v>5384</v>
+      </c>
+      <c r="I6" s="14">
+        <v>6921</v>
+      </c>
+      <c r="J6" s="12">
+        <v>1.2854754799999999</v>
       </c>
       <c r="K6" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="L6" s="12" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="M6" s="15" t="n">
-        <v>116395.0</v>
-      </c>
-      <c r="N6" s="15" t="n">
+      <c r="L6" s="12">
+        <v>2</v>
+      </c>
+      <c r="M6" s="15">
+        <v>116395</v>
+      </c>
+      <c r="N6" s="15">
         <v>58197.5</v>
       </c>
-      <c r="O6" s="12" t="n">
-        <v>6046.0</v>
-      </c>
-      <c r="P6" s="12" t="n">
-        <v>114.0</v>
+      <c r="O6" s="12">
+        <v>6046</v>
+      </c>
+      <c r="P6" s="12">
+        <v>114</v>
       </c>
       <c r="Q6" s="16" t="s">
         <v>26</v>
@@ -1140,7 +1104,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B7" s="11" t="s">
         <v>2</v>
       </c>
@@ -1159,14 +1123,14 @@
       <c r="G7" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="H7" s="14" t="n">
-        <v>10291.0</v>
-      </c>
-      <c r="I7" s="14" t="n">
-        <v>12586.0</v>
-      </c>
-      <c r="J7" s="12" t="n">
-        <v>1.2230104</v>
+      <c r="H7" s="14">
+        <v>10291</v>
+      </c>
+      <c r="I7" s="14">
+        <v>12586</v>
+      </c>
+      <c r="J7" s="12">
+        <v>1.2230103999999999</v>
       </c>
       <c r="K7" s="12" t="s">
         <v>2</v>
@@ -1174,17 +1138,17 @@
       <c r="L7" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="M7" s="15" t="n">
-        <v>102910.0</v>
+      <c r="M7" s="15">
+        <v>102910</v>
       </c>
       <c r="N7" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="O7" s="12" t="n">
-        <v>10751.0</v>
-      </c>
-      <c r="P7" s="12" t="n">
-        <v>123.0</v>
+      <c r="O7" s="12">
+        <v>10751</v>
+      </c>
+      <c r="P7" s="12">
+        <v>123</v>
       </c>
       <c r="Q7" s="16" t="s">
         <v>29</v>
@@ -1196,7 +1160,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B8" s="11" t="s">
         <v>2</v>
       </c>
@@ -1215,14 +1179,14 @@
       <c r="G8" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="H8" s="14" t="n">
-        <v>10291.0</v>
-      </c>
-      <c r="I8" s="14" t="n">
-        <v>12586.0</v>
-      </c>
-      <c r="J8" s="12" t="n">
-        <v>1.2230104</v>
+      <c r="H8" s="14">
+        <v>10291</v>
+      </c>
+      <c r="I8" s="14">
+        <v>12586</v>
+      </c>
+      <c r="J8" s="12">
+        <v>1.2230103999999999</v>
       </c>
       <c r="K8" s="12" t="s">
         <v>2</v>
@@ -1230,17 +1194,17 @@
       <c r="L8" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="M8" s="15" t="n">
-        <v>102910.0</v>
+      <c r="M8" s="15">
+        <v>102910</v>
       </c>
       <c r="N8" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="O8" s="12" t="n">
-        <v>10751.0</v>
-      </c>
-      <c r="P8" s="12" t="n">
-        <v>123.0</v>
+      <c r="O8" s="12">
+        <v>10751</v>
+      </c>
+      <c r="P8" s="12">
+        <v>123</v>
       </c>
       <c r="Q8" s="16" t="s">
         <v>29</v>
@@ -1252,7 +1216,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B9" s="11" t="s">
         <v>2</v>
       </c>
@@ -1271,32 +1235,32 @@
       <c r="G9" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="H9" s="14" t="n">
-        <v>5423.0</v>
-      </c>
-      <c r="I9" s="14" t="n">
-        <v>6748.0</v>
-      </c>
-      <c r="J9" s="12" t="n">
-        <v>1.24432971</v>
+      <c r="H9" s="14">
+        <v>5423</v>
+      </c>
+      <c r="I9" s="14">
+        <v>6748</v>
+      </c>
+      <c r="J9" s="12">
+        <v>1.2443297099999999</v>
       </c>
       <c r="K9" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="L9" s="12" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="M9" s="15" t="n">
-        <v>77820.0</v>
-      </c>
-      <c r="N9" s="15" t="n">
-        <v>38910.0</v>
-      </c>
-      <c r="O9" s="12" t="n">
-        <v>6173.0</v>
-      </c>
-      <c r="P9" s="12" t="n">
-        <v>33.0</v>
+      <c r="L9" s="12">
+        <v>2</v>
+      </c>
+      <c r="M9" s="15">
+        <v>77820</v>
+      </c>
+      <c r="N9" s="15">
+        <v>38910</v>
+      </c>
+      <c r="O9" s="12">
+        <v>6173</v>
+      </c>
+      <c r="P9" s="12">
+        <v>33</v>
       </c>
       <c r="Q9" s="16" t="s">
         <v>30</v>
@@ -1308,7 +1272,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B10" s="11" t="s">
         <v>2</v>
       </c>
@@ -1327,32 +1291,32 @@
       <c r="G10" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="H10" s="14" t="n">
-        <v>5423.0</v>
-      </c>
-      <c r="I10" s="14" t="n">
-        <v>6748.0</v>
-      </c>
-      <c r="J10" s="12" t="n">
-        <v>1.24432971</v>
+      <c r="H10" s="14">
+        <v>5423</v>
+      </c>
+      <c r="I10" s="14">
+        <v>6748</v>
+      </c>
+      <c r="J10" s="12">
+        <v>1.2443297099999999</v>
       </c>
       <c r="K10" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="L10" s="12" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="M10" s="15" t="n">
-        <v>77820.0</v>
-      </c>
-      <c r="N10" s="15" t="n">
-        <v>38910.0</v>
-      </c>
-      <c r="O10" s="12" t="n">
-        <v>6173.0</v>
-      </c>
-      <c r="P10" s="12" t="n">
-        <v>33.0</v>
+      <c r="L10" s="12">
+        <v>2</v>
+      </c>
+      <c r="M10" s="15">
+        <v>77820</v>
+      </c>
+      <c r="N10" s="15">
+        <v>38910</v>
+      </c>
+      <c r="O10" s="12">
+        <v>6173</v>
+      </c>
+      <c r="P10" s="12">
+        <v>33</v>
       </c>
       <c r="Q10" s="16" t="s">
         <v>30</v>
@@ -1364,7 +1328,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B11" s="11" t="s">
         <v>2</v>
       </c>
@@ -1383,14 +1347,14 @@
       <c r="G11" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="H11" s="14" t="n">
-        <v>1143.0</v>
-      </c>
-      <c r="I11" s="14" t="n">
-        <v>1402.0</v>
-      </c>
-      <c r="J11" s="12" t="n">
-        <v>1.22659668</v>
+      <c r="H11" s="14">
+        <v>1143</v>
+      </c>
+      <c r="I11" s="14">
+        <v>1402</v>
+      </c>
+      <c r="J11" s="12">
+        <v>1.2265966800000001</v>
       </c>
       <c r="K11" s="12" t="s">
         <v>2</v>
@@ -1398,17 +1362,17 @@
       <c r="L11" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="M11" s="15" t="n">
-        <v>17415.0</v>
+      <c r="M11" s="15">
+        <v>17415</v>
       </c>
       <c r="N11" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="O11" s="12" t="n">
-        <v>1249.0</v>
-      </c>
-      <c r="P11" s="12" t="n">
-        <v>5.0</v>
+      <c r="O11" s="12">
+        <v>1249</v>
+      </c>
+      <c r="P11" s="12">
+        <v>5</v>
       </c>
       <c r="Q11" s="16" t="s">
         <v>31</v>
@@ -1420,7 +1384,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B12" s="11" t="s">
         <v>2</v>
       </c>
@@ -1439,14 +1403,14 @@
       <c r="G12" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="H12" s="14" t="n">
-        <v>1143.0</v>
-      </c>
-      <c r="I12" s="14" t="n">
-        <v>1402.0</v>
-      </c>
-      <c r="J12" s="12" t="n">
-        <v>1.22659668</v>
+      <c r="H12" s="14">
+        <v>1143</v>
+      </c>
+      <c r="I12" s="14">
+        <v>1402</v>
+      </c>
+      <c r="J12" s="12">
+        <v>1.2265966800000001</v>
       </c>
       <c r="K12" s="12" t="s">
         <v>2</v>
@@ -1454,17 +1418,17 @@
       <c r="L12" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="M12" s="15" t="n">
-        <v>17415.0</v>
+      <c r="M12" s="15">
+        <v>17415</v>
       </c>
       <c r="N12" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="O12" s="12" t="n">
-        <v>1249.0</v>
-      </c>
-      <c r="P12" s="12" t="n">
-        <v>5.0</v>
+      <c r="O12" s="12">
+        <v>1249</v>
+      </c>
+      <c r="P12" s="12">
+        <v>5</v>
       </c>
       <c r="Q12" s="16" t="s">
         <v>31</v>
@@ -1476,7 +1440,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B13" s="11" t="s">
         <v>2</v>
       </c>
@@ -1495,32 +1459,32 @@
       <c r="G13" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="H13" s="14" t="n">
-        <v>2339.0</v>
-      </c>
-      <c r="I13" s="14" t="n">
-        <v>3053.0</v>
-      </c>
-      <c r="J13" s="12" t="n">
+      <c r="H13" s="14">
+        <v>2339</v>
+      </c>
+      <c r="I13" s="14">
+        <v>3053</v>
+      </c>
+      <c r="J13" s="12">
         <v>1.30525866</v>
       </c>
       <c r="K13" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="L13" s="12" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="M13" s="15" t="n">
-        <v>79309.0</v>
-      </c>
-      <c r="N13" s="15" t="n">
-        <v>79309.0</v>
-      </c>
-      <c r="O13" s="12" t="n">
-        <v>2739.0</v>
-      </c>
-      <c r="P13" s="12" t="n">
-        <v>27.0</v>
+      <c r="L13" s="12">
+        <v>1</v>
+      </c>
+      <c r="M13" s="15">
+        <v>79309</v>
+      </c>
+      <c r="N13" s="15">
+        <v>79309</v>
+      </c>
+      <c r="O13" s="12">
+        <v>2739</v>
+      </c>
+      <c r="P13" s="12">
+        <v>27</v>
       </c>
       <c r="Q13" s="16" t="s">
         <v>32</v>
@@ -1532,7 +1496,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B14" s="11" t="s">
         <v>2</v>
       </c>
@@ -1551,32 +1515,32 @@
       <c r="G14" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="H14" s="14" t="n">
-        <v>2339.0</v>
-      </c>
-      <c r="I14" s="14" t="n">
-        <v>3053.0</v>
-      </c>
-      <c r="J14" s="12" t="n">
+      <c r="H14" s="14">
+        <v>2339</v>
+      </c>
+      <c r="I14" s="14">
+        <v>3053</v>
+      </c>
+      <c r="J14" s="12">
         <v>1.30525866</v>
       </c>
       <c r="K14" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="L14" s="12" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="M14" s="15" t="n">
-        <v>79309.0</v>
-      </c>
-      <c r="N14" s="15" t="n">
-        <v>79309.0</v>
-      </c>
-      <c r="O14" s="12" t="n">
-        <v>2739.0</v>
-      </c>
-      <c r="P14" s="12" t="n">
-        <v>27.0</v>
+      <c r="L14" s="12">
+        <v>1</v>
+      </c>
+      <c r="M14" s="15">
+        <v>79309</v>
+      </c>
+      <c r="N14" s="15">
+        <v>79309</v>
+      </c>
+      <c r="O14" s="12">
+        <v>2739</v>
+      </c>
+      <c r="P14" s="12">
+        <v>27</v>
       </c>
       <c r="Q14" s="16" t="s">
         <v>32</v>
@@ -1588,7 +1552,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B15" s="11" t="s">
         <v>2</v>
       </c>
@@ -1607,14 +1571,14 @@
       <c r="G15" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="H15" s="14" t="n">
-        <v>1073.0</v>
-      </c>
-      <c r="I15" s="14" t="n">
-        <v>1309.0</v>
-      </c>
-      <c r="J15" s="12" t="n">
-        <v>1.21994408</v>
+      <c r="H15" s="14">
+        <v>1073</v>
+      </c>
+      <c r="I15" s="14">
+        <v>1309</v>
+      </c>
+      <c r="J15" s="12">
+        <v>1.2199440800000001</v>
       </c>
       <c r="K15" s="12" t="s">
         <v>2</v>
@@ -1622,17 +1586,17 @@
       <c r="L15" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="M15" s="15" t="n">
-        <v>47369.0</v>
+      <c r="M15" s="15">
+        <v>47369</v>
       </c>
       <c r="N15" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="O15" s="12" t="n">
-        <v>1209.0</v>
-      </c>
-      <c r="P15" s="12" t="n">
-        <v>9.0</v>
+      <c r="O15" s="12">
+        <v>1209</v>
+      </c>
+      <c r="P15" s="12">
+        <v>9</v>
       </c>
       <c r="Q15" s="16" t="s">
         <v>33</v>
@@ -1644,7 +1608,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B16" s="11" t="s">
         <v>2</v>
       </c>
@@ -1663,14 +1627,14 @@
       <c r="G16" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="H16" s="14" t="n">
-        <v>1073.0</v>
-      </c>
-      <c r="I16" s="14" t="n">
-        <v>1309.0</v>
-      </c>
-      <c r="J16" s="12" t="n">
-        <v>1.21994408</v>
+      <c r="H16" s="14">
+        <v>1073</v>
+      </c>
+      <c r="I16" s="14">
+        <v>1309</v>
+      </c>
+      <c r="J16" s="12">
+        <v>1.2199440800000001</v>
       </c>
       <c r="K16" s="12" t="s">
         <v>2</v>
@@ -1678,17 +1642,17 @@
       <c r="L16" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="M16" s="15" t="n">
-        <v>47369.0</v>
+      <c r="M16" s="15">
+        <v>47369</v>
       </c>
       <c r="N16" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="O16" s="12" t="n">
-        <v>1209.0</v>
-      </c>
-      <c r="P16" s="12" t="n">
-        <v>9.0</v>
+      <c r="O16" s="12">
+        <v>1209</v>
+      </c>
+      <c r="P16" s="12">
+        <v>9</v>
       </c>
       <c r="Q16" s="16" t="s">
         <v>33</v>
@@ -1700,7 +1664,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B17" s="11" t="s">
         <v>2</v>
       </c>
@@ -1719,32 +1683,32 @@
       <c r="G17" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="H17" s="14" t="n">
-        <v>4401.0</v>
-      </c>
-      <c r="I17" s="14" t="n">
-        <v>5811.0</v>
-      </c>
-      <c r="J17" s="12" t="n">
+      <c r="H17" s="14">
+        <v>4401</v>
+      </c>
+      <c r="I17" s="14">
+        <v>5811</v>
+      </c>
+      <c r="J17" s="12">
         <v>1.32038173</v>
       </c>
       <c r="K17" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="L17" s="12" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="M17" s="15" t="n">
-        <v>135223.0</v>
-      </c>
-      <c r="N17" s="15" t="n">
-        <v>135223.0</v>
-      </c>
-      <c r="O17" s="12" t="n">
-        <v>5511.0</v>
-      </c>
-      <c r="P17" s="12" t="n">
-        <v>32.0</v>
+      <c r="L17" s="12">
+        <v>1</v>
+      </c>
+      <c r="M17" s="15">
+        <v>135223</v>
+      </c>
+      <c r="N17" s="15">
+        <v>635223</v>
+      </c>
+      <c r="O17" s="12">
+        <v>5511</v>
+      </c>
+      <c r="P17" s="12">
+        <v>32</v>
       </c>
       <c r="Q17" s="16" t="s">
         <v>34</v>
@@ -1756,7 +1720,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B18" s="11" t="s">
         <v>2</v>
       </c>
@@ -1775,32 +1739,32 @@
       <c r="G18" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="H18" s="14" t="n">
-        <v>4401.0</v>
-      </c>
-      <c r="I18" s="14" t="n">
-        <v>5811.0</v>
-      </c>
-      <c r="J18" s="12" t="n">
+      <c r="H18" s="14">
+        <v>4401</v>
+      </c>
+      <c r="I18" s="14">
+        <v>5811</v>
+      </c>
+      <c r="J18" s="12">
         <v>1.32038173</v>
       </c>
       <c r="K18" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="L18" s="12" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="M18" s="15" t="n">
-        <v>135223.0</v>
-      </c>
-      <c r="N18" s="15" t="n">
-        <v>135223.0</v>
-      </c>
-      <c r="O18" s="12" t="n">
-        <v>5511.0</v>
-      </c>
-      <c r="P18" s="12" t="n">
-        <v>32.0</v>
+      <c r="L18" s="12">
+        <v>1</v>
+      </c>
+      <c r="M18" s="15">
+        <v>135223</v>
+      </c>
+      <c r="N18" s="15">
+        <v>735223</v>
+      </c>
+      <c r="O18" s="12">
+        <v>5511</v>
+      </c>
+      <c r="P18" s="12">
+        <v>32</v>
       </c>
       <c r="Q18" s="16" t="s">
         <v>34</v>
@@ -1812,7 +1776,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B19" s="11" t="s">
         <v>2</v>
       </c>
@@ -1831,32 +1795,32 @@
       <c r="G19" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="H19" s="14" t="n">
-        <v>1442.0</v>
-      </c>
-      <c r="I19" s="14" t="n">
-        <v>2018.0</v>
-      </c>
-      <c r="J19" s="12" t="n">
-        <v>1.39944521</v>
+      <c r="H19" s="14">
+        <v>1442</v>
+      </c>
+      <c r="I19" s="14">
+        <v>2018</v>
+      </c>
+      <c r="J19" s="12">
+        <v>1.3994452100000001</v>
       </c>
       <c r="K19" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="L19" s="12" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="M19" s="15" t="n">
-        <v>98690.0</v>
-      </c>
-      <c r="N19" s="15" t="n">
-        <v>98690.0</v>
-      </c>
-      <c r="O19" s="12" t="n">
-        <v>1946.0</v>
-      </c>
-      <c r="P19" s="12" t="n">
-        <v>19.0</v>
+      <c r="L19" s="12">
+        <v>1</v>
+      </c>
+      <c r="M19" s="15">
+        <v>98690</v>
+      </c>
+      <c r="N19" s="15">
+        <v>98690</v>
+      </c>
+      <c r="O19" s="12">
+        <v>1946</v>
+      </c>
+      <c r="P19" s="12">
+        <v>19</v>
       </c>
       <c r="Q19" s="16" t="s">
         <v>35</v>
@@ -1868,7 +1832,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B20" s="11" t="s">
         <v>2</v>
       </c>
@@ -1887,32 +1851,32 @@
       <c r="G20" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="H20" s="14" t="n">
-        <v>1442.0</v>
-      </c>
-      <c r="I20" s="14" t="n">
-        <v>2018.0</v>
-      </c>
-      <c r="J20" s="12" t="n">
-        <v>1.39944521</v>
+      <c r="H20" s="14">
+        <v>1442</v>
+      </c>
+      <c r="I20" s="14">
+        <v>2018</v>
+      </c>
+      <c r="J20" s="12">
+        <v>1.3994452100000001</v>
       </c>
       <c r="K20" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="L20" s="12" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="M20" s="15" t="n">
-        <v>98690.0</v>
-      </c>
-      <c r="N20" s="15" t="n">
-        <v>98690.0</v>
-      </c>
-      <c r="O20" s="12" t="n">
-        <v>1946.0</v>
-      </c>
-      <c r="P20" s="12" t="n">
-        <v>19.0</v>
+      <c r="L20" s="12">
+        <v>1</v>
+      </c>
+      <c r="M20" s="15">
+        <v>98690</v>
+      </c>
+      <c r="N20" s="15">
+        <v>98690</v>
+      </c>
+      <c r="O20" s="12">
+        <v>1946</v>
+      </c>
+      <c r="P20" s="12">
+        <v>19</v>
       </c>
       <c r="Q20" s="16" t="s">
         <v>35</v>
@@ -1924,7 +1888,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B21" s="11" t="s">
         <v>2</v>
       </c>
@@ -1943,14 +1907,14 @@
       <c r="G21" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="H21" s="14" t="n">
-        <v>1410.0</v>
-      </c>
-      <c r="I21" s="14" t="n">
-        <v>1820.0</v>
-      </c>
-      <c r="J21" s="12" t="n">
-        <v>1.29078014</v>
+      <c r="H21" s="14">
+        <v>1410</v>
+      </c>
+      <c r="I21" s="14">
+        <v>1820</v>
+      </c>
+      <c r="J21" s="12">
+        <v>1.2907801400000001</v>
       </c>
       <c r="K21" s="12" t="s">
         <v>2</v>
@@ -1958,17 +1922,17 @@
       <c r="L21" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="M21" s="15" t="n">
-        <v>93493.0</v>
+      <c r="M21" s="15">
+        <v>93493</v>
       </c>
       <c r="N21" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="O21" s="12" t="n">
-        <v>1754.0</v>
-      </c>
-      <c r="P21" s="12" t="n">
-        <v>22.0</v>
+      <c r="O21" s="12">
+        <v>1754</v>
+      </c>
+      <c r="P21" s="12">
+        <v>22</v>
       </c>
       <c r="Q21" s="16" t="s">
         <v>36</v>
@@ -1980,7 +1944,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B22" s="11" t="s">
         <v>2</v>
       </c>
@@ -1999,14 +1963,14 @@
       <c r="G22" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="H22" s="14" t="n">
-        <v>1410.0</v>
-      </c>
-      <c r="I22" s="14" t="n">
-        <v>1820.0</v>
-      </c>
-      <c r="J22" s="12" t="n">
-        <v>1.29078014</v>
+      <c r="H22" s="14">
+        <v>1410</v>
+      </c>
+      <c r="I22" s="14">
+        <v>1820</v>
+      </c>
+      <c r="J22" s="12">
+        <v>1.2907801400000001</v>
       </c>
       <c r="K22" s="12" t="s">
         <v>2</v>
@@ -2014,17 +1978,17 @@
       <c r="L22" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="M22" s="15" t="n">
-        <v>93493.0</v>
+      <c r="M22" s="15">
+        <v>93493</v>
       </c>
       <c r="N22" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="O22" s="12" t="n">
-        <v>1754.0</v>
-      </c>
-      <c r="P22" s="12" t="n">
-        <v>22.0</v>
+      <c r="O22" s="12">
+        <v>1754</v>
+      </c>
+      <c r="P22" s="12">
+        <v>22</v>
       </c>
       <c r="Q22" s="16" t="s">
         <v>36</v>
@@ -2036,7 +2000,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B23" s="11" t="s">
         <v>2</v>
       </c>
@@ -2055,32 +2019,32 @@
       <c r="G23" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="H23" s="14" t="n">
-        <v>3364.0</v>
-      </c>
-      <c r="I23" s="14" t="n">
-        <v>4572.0</v>
-      </c>
-      <c r="J23" s="12" t="n">
+      <c r="H23" s="14">
+        <v>3364</v>
+      </c>
+      <c r="I23" s="14">
+        <v>4572</v>
+      </c>
+      <c r="J23" s="12">
         <v>1.35909631</v>
       </c>
       <c r="K23" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="L23" s="12" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="M23" s="15" t="n">
-        <v>148329.0</v>
-      </c>
-      <c r="N23" s="15" t="n">
-        <v>148329.0</v>
-      </c>
-      <c r="O23" s="12" t="n">
-        <v>4359.0</v>
-      </c>
-      <c r="P23" s="12" t="n">
-        <v>30.0</v>
+      <c r="L23" s="12">
+        <v>1</v>
+      </c>
+      <c r="M23" s="15">
+        <v>148329</v>
+      </c>
+      <c r="N23" s="15">
+        <v>148329</v>
+      </c>
+      <c r="O23" s="12">
+        <v>4359</v>
+      </c>
+      <c r="P23" s="12">
+        <v>30</v>
       </c>
       <c r="Q23" s="16" t="s">
         <v>37</v>
@@ -2092,7 +2056,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B24" s="11" t="s">
         <v>2</v>
       </c>
@@ -2111,32 +2075,32 @@
       <c r="G24" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="H24" s="14" t="n">
-        <v>3364.0</v>
-      </c>
-      <c r="I24" s="14" t="n">
-        <v>4572.0</v>
-      </c>
-      <c r="J24" s="12" t="n">
+      <c r="H24" s="14">
+        <v>3364</v>
+      </c>
+      <c r="I24" s="14">
+        <v>4572</v>
+      </c>
+      <c r="J24" s="12">
         <v>1.35909631</v>
       </c>
       <c r="K24" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="L24" s="12" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="M24" s="15" t="n">
-        <v>148329.0</v>
-      </c>
-      <c r="N24" s="15" t="n">
-        <v>148329.0</v>
-      </c>
-      <c r="O24" s="12" t="n">
-        <v>4359.0</v>
-      </c>
-      <c r="P24" s="12" t="n">
-        <v>30.0</v>
+      <c r="L24" s="12">
+        <v>1</v>
+      </c>
+      <c r="M24" s="15">
+        <v>148329</v>
+      </c>
+      <c r="N24" s="15">
+        <v>148329</v>
+      </c>
+      <c r="O24" s="12">
+        <v>4359</v>
+      </c>
+      <c r="P24" s="12">
+        <v>30</v>
       </c>
       <c r="Q24" s="16" t="s">
         <v>37</v>
@@ -2148,7 +2112,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B25" s="11" t="s">
         <v>2</v>
       </c>
@@ -2167,13 +2131,13 @@
       <c r="G25" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="H25" s="14" t="n">
-        <v>2402.0</v>
-      </c>
-      <c r="I25" s="14" t="n">
-        <v>3384.0</v>
-      </c>
-      <c r="J25" s="12" t="n">
+      <c r="H25" s="14">
+        <v>2402</v>
+      </c>
+      <c r="I25" s="14">
+        <v>3384</v>
+      </c>
+      <c r="J25" s="12">
         <v>1.40882598</v>
       </c>
       <c r="K25" s="12" t="s">
@@ -2182,17 +2146,17 @@
       <c r="L25" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="M25" s="15" t="n">
-        <v>100892.0</v>
+      <c r="M25" s="15">
+        <v>100892</v>
       </c>
       <c r="N25" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="O25" s="12" t="n">
-        <v>3046.0</v>
-      </c>
-      <c r="P25" s="12" t="n">
-        <v>22.0</v>
+      <c r="O25" s="12">
+        <v>3046</v>
+      </c>
+      <c r="P25" s="12">
+        <v>22</v>
       </c>
       <c r="Q25" s="16" t="s">
         <v>25</v>
@@ -2204,7 +2168,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B26" s="18" t="s">
         <v>2</v>
       </c>
@@ -2223,13 +2187,13 @@
       <c r="G26" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="H26" s="21" t="n">
-        <v>2402.0</v>
-      </c>
-      <c r="I26" s="21" t="n">
-        <v>3384.0</v>
-      </c>
-      <c r="J26" s="19" t="n">
+      <c r="H26" s="21">
+        <v>2402</v>
+      </c>
+      <c r="I26" s="21">
+        <v>3384</v>
+      </c>
+      <c r="J26" s="19">
         <v>1.40882598</v>
       </c>
       <c r="K26" s="19" t="s">
@@ -2238,17 +2202,17 @@
       <c r="L26" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="M26" s="22" t="n">
-        <v>100892.0</v>
+      <c r="M26" s="22">
+        <v>100892</v>
       </c>
       <c r="N26" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="O26" s="19" t="n">
-        <v>3046.0</v>
-      </c>
-      <c r="P26" s="19" t="n">
-        <v>22.0</v>
+      <c r="O26" s="19">
+        <v>3046</v>
+      </c>
+      <c r="P26" s="19">
+        <v>22</v>
       </c>
       <c r="Q26" s="23" t="s">
         <v>25</v>
@@ -2260,7 +2224,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B27" s="11" t="s">
         <v>38</v>
       </c>
@@ -2279,32 +2243,32 @@
       <c r="G27" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="H27" s="14" t="n">
-        <v>741.0</v>
-      </c>
-      <c r="I27" s="14" t="n">
-        <v>1096.0</v>
-      </c>
-      <c r="J27" s="12" t="n">
-        <v>1.47908232</v>
+      <c r="H27" s="14">
+        <v>741</v>
+      </c>
+      <c r="I27" s="14">
+        <v>1096</v>
+      </c>
+      <c r="J27" s="12">
+        <v>1.4790823200000001</v>
       </c>
       <c r="K27" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="L27" s="12" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="M27" s="15" t="n">
-        <v>76784.0</v>
-      </c>
-      <c r="N27" s="15" t="n">
-        <v>19196.0</v>
-      </c>
-      <c r="O27" s="12" t="n">
-        <v>1083.0</v>
-      </c>
-      <c r="P27" s="12" t="n">
-        <v>25.0</v>
+      <c r="L27" s="12">
+        <v>4</v>
+      </c>
+      <c r="M27" s="15">
+        <v>76784</v>
+      </c>
+      <c r="N27" s="15">
+        <v>19196</v>
+      </c>
+      <c r="O27" s="12">
+        <v>1083</v>
+      </c>
+      <c r="P27" s="12">
+        <v>25</v>
       </c>
       <c r="Q27" s="16" t="s">
         <v>25</v>
@@ -2316,7 +2280,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B28" s="11" t="s">
         <v>2</v>
       </c>
@@ -2335,32 +2299,32 @@
       <c r="G28" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="H28" s="14" t="n">
-        <v>216.0</v>
-      </c>
-      <c r="I28" s="14" t="n">
-        <v>308.0</v>
-      </c>
-      <c r="J28" s="12" t="n">
+      <c r="H28" s="14">
+        <v>216</v>
+      </c>
+      <c r="I28" s="14">
+        <v>308</v>
+      </c>
+      <c r="J28" s="12">
         <v>1.42592593</v>
       </c>
       <c r="K28" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="L28" s="12" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="M28" s="15" t="n">
-        <v>26578.0</v>
-      </c>
-      <c r="N28" s="15" t="n">
-        <v>8859.33333333</v>
-      </c>
-      <c r="O28" s="12" t="n">
-        <v>299.0</v>
-      </c>
-      <c r="P28" s="12" t="n">
-        <v>9.0</v>
+      <c r="L28" s="12">
+        <v>3</v>
+      </c>
+      <c r="M28" s="15">
+        <v>26578</v>
+      </c>
+      <c r="N28" s="15">
+        <v>8859.3333333299997</v>
+      </c>
+      <c r="O28" s="12">
+        <v>299</v>
+      </c>
+      <c r="P28" s="12">
+        <v>9</v>
       </c>
       <c r="Q28" s="16" t="s">
         <v>26</v>
@@ -2372,7 +2336,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B29" s="11" t="s">
         <v>2</v>
       </c>
@@ -2391,32 +2355,32 @@
       <c r="G29" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="H29" s="14" t="n">
-        <v>216.0</v>
-      </c>
-      <c r="I29" s="14" t="n">
-        <v>308.0</v>
-      </c>
-      <c r="J29" s="12" t="n">
+      <c r="H29" s="14">
+        <v>216</v>
+      </c>
+      <c r="I29" s="14">
+        <v>308</v>
+      </c>
+      <c r="J29" s="12">
         <v>1.42592593</v>
       </c>
       <c r="K29" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="L29" s="12" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="M29" s="15" t="n">
-        <v>26578.0</v>
-      </c>
-      <c r="N29" s="15" t="n">
-        <v>8859.33333333</v>
-      </c>
-      <c r="O29" s="12" t="n">
-        <v>299.0</v>
-      </c>
-      <c r="P29" s="12" t="n">
-        <v>9.0</v>
+      <c r="L29" s="12">
+        <v>3</v>
+      </c>
+      <c r="M29" s="15">
+        <v>26578</v>
+      </c>
+      <c r="N29" s="15">
+        <v>8859.3333333299997</v>
+      </c>
+      <c r="O29" s="12">
+        <v>299</v>
+      </c>
+      <c r="P29" s="12">
+        <v>9</v>
       </c>
       <c r="Q29" s="16" t="s">
         <v>26</v>
@@ -2428,7 +2392,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B30" s="11" t="s">
         <v>2</v>
       </c>
@@ -2447,32 +2411,32 @@
       <c r="G30" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="H30" s="14" t="n">
-        <v>291.0</v>
-      </c>
-      <c r="I30" s="14" t="n">
-        <v>371.0</v>
-      </c>
-      <c r="J30" s="12" t="n">
+      <c r="H30" s="14">
+        <v>291</v>
+      </c>
+      <c r="I30" s="14">
+        <v>371</v>
+      </c>
+      <c r="J30" s="12">
         <v>1.27491409</v>
       </c>
       <c r="K30" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="L30" s="12" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="M30" s="15" t="n">
-        <v>27404.0</v>
-      </c>
-      <c r="N30" s="15" t="n">
-        <v>27404.0</v>
-      </c>
-      <c r="O30" s="12" t="n">
-        <v>368.0</v>
-      </c>
-      <c r="P30" s="12" t="n">
-        <v>13.0</v>
+      <c r="L30" s="12">
+        <v>1</v>
+      </c>
+      <c r="M30" s="15">
+        <v>27404</v>
+      </c>
+      <c r="N30" s="15">
+        <v>27404</v>
+      </c>
+      <c r="O30" s="12">
+        <v>368</v>
+      </c>
+      <c r="P30" s="12">
+        <v>13</v>
       </c>
       <c r="Q30" s="16" t="s">
         <v>29</v>
@@ -2484,7 +2448,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B31" s="11" t="s">
         <v>2</v>
       </c>
@@ -2503,32 +2467,32 @@
       <c r="G31" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="H31" s="14" t="n">
-        <v>291.0</v>
-      </c>
-      <c r="I31" s="14" t="n">
-        <v>371.0</v>
-      </c>
-      <c r="J31" s="12" t="n">
+      <c r="H31" s="14">
+        <v>291</v>
+      </c>
+      <c r="I31" s="14">
+        <v>371</v>
+      </c>
+      <c r="J31" s="12">
         <v>1.27491409</v>
       </c>
       <c r="K31" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="L31" s="12" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="M31" s="15" t="n">
-        <v>27404.0</v>
-      </c>
-      <c r="N31" s="15" t="n">
-        <v>27404.0</v>
-      </c>
-      <c r="O31" s="12" t="n">
-        <v>368.0</v>
-      </c>
-      <c r="P31" s="12" t="n">
-        <v>13.0</v>
+      <c r="L31" s="12">
+        <v>1</v>
+      </c>
+      <c r="M31" s="15">
+        <v>27404</v>
+      </c>
+      <c r="N31" s="15">
+        <v>27404</v>
+      </c>
+      <c r="O31" s="12">
+        <v>368</v>
+      </c>
+      <c r="P31" s="12">
+        <v>13</v>
       </c>
       <c r="Q31" s="16" t="s">
         <v>29</v>
@@ -2540,7 +2504,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B32" s="11" t="s">
         <v>2</v>
       </c>
@@ -2559,14 +2523,14 @@
       <c r="G32" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="H32" s="14" t="n">
-        <v>362.0</v>
-      </c>
-      <c r="I32" s="14" t="n">
-        <v>417.0</v>
-      </c>
-      <c r="J32" s="12" t="n">
-        <v>1.1519337</v>
+      <c r="H32" s="14">
+        <v>362</v>
+      </c>
+      <c r="I32" s="14">
+        <v>417</v>
+      </c>
+      <c r="J32" s="12">
+        <v>1.1519337000000001</v>
       </c>
       <c r="K32" s="12" t="s">
         <v>2</v>
@@ -2574,17 +2538,17 @@
       <c r="L32" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="M32" s="15" t="n">
-        <v>22802.0</v>
+      <c r="M32" s="15">
+        <v>22802</v>
       </c>
       <c r="N32" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="O32" s="12" t="n">
-        <v>416.0</v>
-      </c>
-      <c r="P32" s="12" t="n">
-        <v>3.0</v>
+      <c r="O32" s="12">
+        <v>416</v>
+      </c>
+      <c r="P32" s="12">
+        <v>3</v>
       </c>
       <c r="Q32" s="16" t="s">
         <v>30</v>
@@ -2596,7 +2560,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B33" s="18" t="s">
         <v>2</v>
       </c>
@@ -2615,14 +2579,14 @@
       <c r="G33" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="H33" s="21" t="n">
-        <v>362.0</v>
-      </c>
-      <c r="I33" s="21" t="n">
-        <v>417.0</v>
-      </c>
-      <c r="J33" s="19" t="n">
-        <v>1.1519337</v>
+      <c r="H33" s="21">
+        <v>362</v>
+      </c>
+      <c r="I33" s="21">
+        <v>417</v>
+      </c>
+      <c r="J33" s="19">
+        <v>1.1519337000000001</v>
       </c>
       <c r="K33" s="19" t="s">
         <v>2</v>
@@ -2630,17 +2594,17 @@
       <c r="L33" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="M33" s="22" t="n">
-        <v>22802.0</v>
+      <c r="M33" s="22">
+        <v>22802</v>
       </c>
       <c r="N33" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="O33" s="19" t="n">
-        <v>416.0</v>
-      </c>
-      <c r="P33" s="19" t="n">
-        <v>3.0</v>
+      <c r="O33" s="19">
+        <v>416</v>
+      </c>
+      <c r="P33" s="19">
+        <v>3</v>
       </c>
       <c r="Q33" s="23" t="s">
         <v>30</v>
@@ -2654,40 +2618,25 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink location="" ref="C1"/>
+    <hyperlink ref="C1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R33"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetFormatPr defaultColWidth="12.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="19" max="16384" style="1" width="12.7109375"/>
-    <col min="18" max="18" style="1" width="23.4375" customWidth="true"/>
-    <col min="17" max="17" style="1" width="23.4375" customWidth="true"/>
-    <col min="16" max="16" style="1" width="23.4375" customWidth="true"/>
-    <col min="15" max="15" style="1" width="23.4375" customWidth="true"/>
-    <col min="14" max="14" style="1" width="23.4375" customWidth="true"/>
-    <col min="13" max="13" style="1" width="23.4375" customWidth="true"/>
-    <col min="12" max="12" style="1" width="23.4375" customWidth="true"/>
-    <col min="11" max="11" style="1" width="23.4375" customWidth="true"/>
-    <col min="10" max="10" style="1" width="23.4375" customWidth="true"/>
-    <col min="9" max="9" style="1" width="23.4375" customWidth="true"/>
-    <col min="8" max="8" style="1" width="23.4375" customWidth="true"/>
-    <col min="7" max="7" style="1" width="23.4375" customWidth="true"/>
-    <col min="6" max="6" style="1" width="23.4375" customWidth="true"/>
-    <col min="5" max="5" style="1" width="23.4375" customWidth="true"/>
-    <col min="4" max="4" style="1" width="23.4375" customWidth="true"/>
-    <col min="3" max="3" style="1" width="23.4375" customWidth="true"/>
-    <col min="2" max="2" style="1" width="58.59375" customWidth="true"/>
-    <col min="1" max="1" width="5.15625" style="1" customWidth="true"/>
+    <col min="1" max="1" width="5.1796875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="58.6328125" style="1" customWidth="1"/>
+    <col min="3" max="18" width="23.453125" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="12.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="33.0" customHeight="true" s="5" customFormat="true">
+    <row r="1" spans="1:18" s="5" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2"/>
       <c r="B1" s="3" t="s">
         <v>0</v>
@@ -2699,7 +2648,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B3" s="25" t="s">
         <v>3</v>
       </c>
@@ -2752,7 +2701,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B4" s="27" t="s">
         <v>20</v>
       </c>
@@ -2768,32 +2717,32 @@
       <c r="F4" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="G4" s="30" t="n">
-        <v>30124.0</v>
-      </c>
-      <c r="H4" s="30" t="n">
-        <v>49624.0</v>
-      </c>
-      <c r="I4" s="29" t="n">
-        <v>1.64732439</v>
+      <c r="G4" s="30">
+        <v>30124</v>
+      </c>
+      <c r="H4" s="30">
+        <v>49624</v>
+      </c>
+      <c r="I4" s="29">
+        <v>1.6473243900000001</v>
       </c>
       <c r="J4" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="K4" s="29" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="L4" s="31" t="n">
-        <v>1017845.0</v>
-      </c>
-      <c r="M4" s="31" t="n">
+      <c r="K4" s="29">
+        <v>8</v>
+      </c>
+      <c r="L4" s="31">
+        <v>1017845</v>
+      </c>
+      <c r="M4" s="31">
         <v>127230.625</v>
       </c>
-      <c r="N4" s="29" t="n">
-        <v>44783.0</v>
-      </c>
-      <c r="O4" s="29" t="n">
-        <v>436.0</v>
+      <c r="N4" s="29">
+        <v>44783</v>
+      </c>
+      <c r="O4" s="29">
+        <v>436</v>
       </c>
       <c r="P4" s="32" t="s">
         <v>25</v>
@@ -2805,7 +2754,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B5" s="27" t="s">
         <v>20</v>
       </c>
@@ -2821,32 +2770,32 @@
       <c r="F5" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="G5" s="30" t="n">
-        <v>5384.0</v>
-      </c>
-      <c r="H5" s="30" t="n">
-        <v>6921.0</v>
-      </c>
-      <c r="I5" s="29" t="n">
-        <v>1.28547548</v>
+      <c r="G5" s="30">
+        <v>5384</v>
+      </c>
+      <c r="H5" s="30">
+        <v>6921</v>
+      </c>
+      <c r="I5" s="29">
+        <v>1.2854754799999999</v>
       </c>
       <c r="J5" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="K5" s="29" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="L5" s="31" t="n">
-        <v>116395.0</v>
-      </c>
-      <c r="M5" s="31" t="n">
+      <c r="K5" s="29">
+        <v>2</v>
+      </c>
+      <c r="L5" s="31">
+        <v>116395</v>
+      </c>
+      <c r="M5" s="31">
         <v>58197.5</v>
       </c>
-      <c r="N5" s="29" t="n">
-        <v>6046.0</v>
-      </c>
-      <c r="O5" s="29" t="n">
-        <v>114.0</v>
+      <c r="N5" s="29">
+        <v>6046</v>
+      </c>
+      <c r="O5" s="29">
+        <v>114</v>
       </c>
       <c r="P5" s="32" t="s">
         <v>26</v>
@@ -2858,7 +2807,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B6" s="27" t="s">
         <v>20</v>
       </c>
@@ -2874,32 +2823,32 @@
       <c r="F6" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="G6" s="30" t="n">
-        <v>5384.0</v>
-      </c>
-      <c r="H6" s="30" t="n">
-        <v>6921.0</v>
-      </c>
-      <c r="I6" s="29" t="n">
-        <v>1.28547548</v>
+      <c r="G6" s="30">
+        <v>5384</v>
+      </c>
+      <c r="H6" s="30">
+        <v>6921</v>
+      </c>
+      <c r="I6" s="29">
+        <v>1.2854754799999999</v>
       </c>
       <c r="J6" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="K6" s="29" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="L6" s="31" t="n">
-        <v>116395.0</v>
-      </c>
-      <c r="M6" s="31" t="n">
+      <c r="K6" s="29">
+        <v>2</v>
+      </c>
+      <c r="L6" s="31">
+        <v>116395</v>
+      </c>
+      <c r="M6" s="31">
         <v>58197.5</v>
       </c>
-      <c r="N6" s="29" t="n">
-        <v>6046.0</v>
-      </c>
-      <c r="O6" s="29" t="n">
-        <v>114.0</v>
+      <c r="N6" s="29">
+        <v>6046</v>
+      </c>
+      <c r="O6" s="29">
+        <v>114</v>
       </c>
       <c r="P6" s="32" t="s">
         <v>26</v>
@@ -2911,7 +2860,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B7" s="27" t="s">
         <v>20</v>
       </c>
@@ -2927,14 +2876,14 @@
       <c r="F7" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="G7" s="30" t="n">
-        <v>10291.0</v>
-      </c>
-      <c r="H7" s="30" t="n">
-        <v>12586.0</v>
-      </c>
-      <c r="I7" s="29" t="n">
-        <v>1.2230104</v>
+      <c r="G7" s="30">
+        <v>10291</v>
+      </c>
+      <c r="H7" s="30">
+        <v>12586</v>
+      </c>
+      <c r="I7" s="29">
+        <v>1.2230103999999999</v>
       </c>
       <c r="J7" s="29" t="s">
         <v>2</v>
@@ -2942,17 +2891,17 @@
       <c r="K7" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="L7" s="31" t="n">
-        <v>102910.0</v>
+      <c r="L7" s="31">
+        <v>102910</v>
       </c>
       <c r="M7" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="N7" s="29" t="n">
-        <v>10751.0</v>
-      </c>
-      <c r="O7" s="29" t="n">
-        <v>123.0</v>
+      <c r="N7" s="29">
+        <v>10751</v>
+      </c>
+      <c r="O7" s="29">
+        <v>123</v>
       </c>
       <c r="P7" s="32" t="s">
         <v>29</v>
@@ -2964,7 +2913,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B8" s="27" t="s">
         <v>20</v>
       </c>
@@ -2980,14 +2929,14 @@
       <c r="F8" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="G8" s="30" t="n">
-        <v>10291.0</v>
-      </c>
-      <c r="H8" s="30" t="n">
-        <v>12586.0</v>
-      </c>
-      <c r="I8" s="29" t="n">
-        <v>1.2230104</v>
+      <c r="G8" s="30">
+        <v>10291</v>
+      </c>
+      <c r="H8" s="30">
+        <v>12586</v>
+      </c>
+      <c r="I8" s="29">
+        <v>1.2230103999999999</v>
       </c>
       <c r="J8" s="29" t="s">
         <v>2</v>
@@ -2995,17 +2944,17 @@
       <c r="K8" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="L8" s="31" t="n">
-        <v>102910.0</v>
+      <c r="L8" s="31">
+        <v>102910</v>
       </c>
       <c r="M8" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="N8" s="29" t="n">
-        <v>10751.0</v>
-      </c>
-      <c r="O8" s="29" t="n">
-        <v>123.0</v>
+      <c r="N8" s="29">
+        <v>10751</v>
+      </c>
+      <c r="O8" s="29">
+        <v>123</v>
       </c>
       <c r="P8" s="32" t="s">
         <v>29</v>
@@ -3017,7 +2966,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B9" s="27" t="s">
         <v>20</v>
       </c>
@@ -3033,32 +2982,32 @@
       <c r="F9" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="G9" s="30" t="n">
-        <v>5423.0</v>
-      </c>
-      <c r="H9" s="30" t="n">
-        <v>6748.0</v>
-      </c>
-      <c r="I9" s="29" t="n">
-        <v>1.24432971</v>
+      <c r="G9" s="30">
+        <v>5423</v>
+      </c>
+      <c r="H9" s="30">
+        <v>6748</v>
+      </c>
+      <c r="I9" s="29">
+        <v>1.2443297099999999</v>
       </c>
       <c r="J9" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="K9" s="29" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="L9" s="31" t="n">
-        <v>77820.0</v>
-      </c>
-      <c r="M9" s="31" t="n">
-        <v>38910.0</v>
-      </c>
-      <c r="N9" s="29" t="n">
-        <v>6173.0</v>
-      </c>
-      <c r="O9" s="29" t="n">
-        <v>33.0</v>
+      <c r="K9" s="29">
+        <v>2</v>
+      </c>
+      <c r="L9" s="31">
+        <v>77820</v>
+      </c>
+      <c r="M9" s="31">
+        <v>38910</v>
+      </c>
+      <c r="N9" s="29">
+        <v>6173</v>
+      </c>
+      <c r="O9" s="29">
+        <v>33</v>
       </c>
       <c r="P9" s="32" t="s">
         <v>30</v>
@@ -3070,7 +3019,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B10" s="27" t="s">
         <v>20</v>
       </c>
@@ -3086,32 +3035,32 @@
       <c r="F10" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="G10" s="30" t="n">
-        <v>5423.0</v>
-      </c>
-      <c r="H10" s="30" t="n">
-        <v>6748.0</v>
-      </c>
-      <c r="I10" s="29" t="n">
-        <v>1.24432971</v>
+      <c r="G10" s="30">
+        <v>5423</v>
+      </c>
+      <c r="H10" s="30">
+        <v>6748</v>
+      </c>
+      <c r="I10" s="29">
+        <v>1.2443297099999999</v>
       </c>
       <c r="J10" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="K10" s="29" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="L10" s="31" t="n">
-        <v>77820.0</v>
-      </c>
-      <c r="M10" s="31" t="n">
-        <v>38910.0</v>
-      </c>
-      <c r="N10" s="29" t="n">
-        <v>6173.0</v>
-      </c>
-      <c r="O10" s="29" t="n">
-        <v>33.0</v>
+      <c r="K10" s="29">
+        <v>2</v>
+      </c>
+      <c r="L10" s="31">
+        <v>77820</v>
+      </c>
+      <c r="M10" s="31">
+        <v>38910</v>
+      </c>
+      <c r="N10" s="29">
+        <v>6173</v>
+      </c>
+      <c r="O10" s="29">
+        <v>33</v>
       </c>
       <c r="P10" s="32" t="s">
         <v>30</v>
@@ -3123,7 +3072,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B11" s="27" t="s">
         <v>20</v>
       </c>
@@ -3139,14 +3088,14 @@
       <c r="F11" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="G11" s="30" t="n">
-        <v>1143.0</v>
-      </c>
-      <c r="H11" s="30" t="n">
-        <v>1402.0</v>
-      </c>
-      <c r="I11" s="29" t="n">
-        <v>1.22659668</v>
+      <c r="G11" s="30">
+        <v>1143</v>
+      </c>
+      <c r="H11" s="30">
+        <v>1402</v>
+      </c>
+      <c r="I11" s="29">
+        <v>1.2265966800000001</v>
       </c>
       <c r="J11" s="29" t="s">
         <v>2</v>
@@ -3154,17 +3103,17 @@
       <c r="K11" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="L11" s="31" t="n">
-        <v>17415.0</v>
+      <c r="L11" s="31">
+        <v>17415</v>
       </c>
       <c r="M11" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="N11" s="29" t="n">
-        <v>1249.0</v>
-      </c>
-      <c r="O11" s="29" t="n">
-        <v>5.0</v>
+      <c r="N11" s="29">
+        <v>1249</v>
+      </c>
+      <c r="O11" s="29">
+        <v>5</v>
       </c>
       <c r="P11" s="32" t="s">
         <v>31</v>
@@ -3176,7 +3125,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B12" s="27" t="s">
         <v>20</v>
       </c>
@@ -3192,14 +3141,14 @@
       <c r="F12" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="G12" s="30" t="n">
-        <v>1143.0</v>
-      </c>
-      <c r="H12" s="30" t="n">
-        <v>1402.0</v>
-      </c>
-      <c r="I12" s="29" t="n">
-        <v>1.22659668</v>
+      <c r="G12" s="30">
+        <v>1143</v>
+      </c>
+      <c r="H12" s="30">
+        <v>1402</v>
+      </c>
+      <c r="I12" s="29">
+        <v>1.2265966800000001</v>
       </c>
       <c r="J12" s="29" t="s">
         <v>2</v>
@@ -3207,17 +3156,17 @@
       <c r="K12" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="L12" s="31" t="n">
-        <v>17415.0</v>
+      <c r="L12" s="31">
+        <v>17415</v>
       </c>
       <c r="M12" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="N12" s="29" t="n">
-        <v>1249.0</v>
-      </c>
-      <c r="O12" s="29" t="n">
-        <v>5.0</v>
+      <c r="N12" s="29">
+        <v>1249</v>
+      </c>
+      <c r="O12" s="29">
+        <v>5</v>
       </c>
       <c r="P12" s="32" t="s">
         <v>31</v>
@@ -3229,7 +3178,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B13" s="27" t="s">
         <v>20</v>
       </c>
@@ -3245,32 +3194,32 @@
       <c r="F13" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="G13" s="30" t="n">
-        <v>2339.0</v>
-      </c>
-      <c r="H13" s="30" t="n">
-        <v>3053.0</v>
-      </c>
-      <c r="I13" s="29" t="n">
+      <c r="G13" s="30">
+        <v>2339</v>
+      </c>
+      <c r="H13" s="30">
+        <v>3053</v>
+      </c>
+      <c r="I13" s="29">
         <v>1.30525866</v>
       </c>
       <c r="J13" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="K13" s="29" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="L13" s="31" t="n">
-        <v>79309.0</v>
-      </c>
-      <c r="M13" s="31" t="n">
-        <v>79309.0</v>
-      </c>
-      <c r="N13" s="29" t="n">
-        <v>2739.0</v>
-      </c>
-      <c r="O13" s="29" t="n">
-        <v>27.0</v>
+      <c r="K13" s="29">
+        <v>1</v>
+      </c>
+      <c r="L13" s="31">
+        <v>79309</v>
+      </c>
+      <c r="M13" s="31">
+        <v>79309</v>
+      </c>
+      <c r="N13" s="29">
+        <v>2739</v>
+      </c>
+      <c r="O13" s="29">
+        <v>27</v>
       </c>
       <c r="P13" s="32" t="s">
         <v>32</v>
@@ -3282,7 +3231,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B14" s="27" t="s">
         <v>20</v>
       </c>
@@ -3298,32 +3247,32 @@
       <c r="F14" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="G14" s="30" t="n">
-        <v>2339.0</v>
-      </c>
-      <c r="H14" s="30" t="n">
-        <v>3053.0</v>
-      </c>
-      <c r="I14" s="29" t="n">
+      <c r="G14" s="30">
+        <v>2339</v>
+      </c>
+      <c r="H14" s="30">
+        <v>3053</v>
+      </c>
+      <c r="I14" s="29">
         <v>1.30525866</v>
       </c>
       <c r="J14" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="K14" s="29" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="L14" s="31" t="n">
-        <v>79309.0</v>
-      </c>
-      <c r="M14" s="31" t="n">
-        <v>79309.0</v>
-      </c>
-      <c r="N14" s="29" t="n">
-        <v>2739.0</v>
-      </c>
-      <c r="O14" s="29" t="n">
-        <v>27.0</v>
+      <c r="K14" s="29">
+        <v>1</v>
+      </c>
+      <c r="L14" s="31">
+        <v>79309</v>
+      </c>
+      <c r="M14" s="31">
+        <v>79309</v>
+      </c>
+      <c r="N14" s="29">
+        <v>2739</v>
+      </c>
+      <c r="O14" s="29">
+        <v>27</v>
       </c>
       <c r="P14" s="32" t="s">
         <v>32</v>
@@ -3335,7 +3284,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B15" s="27" t="s">
         <v>20</v>
       </c>
@@ -3351,14 +3300,14 @@
       <c r="F15" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="G15" s="30" t="n">
-        <v>1073.0</v>
-      </c>
-      <c r="H15" s="30" t="n">
-        <v>1309.0</v>
-      </c>
-      <c r="I15" s="29" t="n">
-        <v>1.21994408</v>
+      <c r="G15" s="30">
+        <v>1073</v>
+      </c>
+      <c r="H15" s="30">
+        <v>1309</v>
+      </c>
+      <c r="I15" s="29">
+        <v>1.2199440800000001</v>
       </c>
       <c r="J15" s="29" t="s">
         <v>2</v>
@@ -3366,17 +3315,17 @@
       <c r="K15" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="L15" s="31" t="n">
-        <v>47369.0</v>
+      <c r="L15" s="31">
+        <v>47369</v>
       </c>
       <c r="M15" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="N15" s="29" t="n">
-        <v>1209.0</v>
-      </c>
-      <c r="O15" s="29" t="n">
-        <v>9.0</v>
+      <c r="N15" s="29">
+        <v>1209</v>
+      </c>
+      <c r="O15" s="29">
+        <v>9</v>
       </c>
       <c r="P15" s="32" t="s">
         <v>33</v>
@@ -3388,7 +3337,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B16" s="27" t="s">
         <v>20</v>
       </c>
@@ -3404,14 +3353,14 @@
       <c r="F16" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="G16" s="30" t="n">
-        <v>1073.0</v>
-      </c>
-      <c r="H16" s="30" t="n">
-        <v>1309.0</v>
-      </c>
-      <c r="I16" s="29" t="n">
-        <v>1.21994408</v>
+      <c r="G16" s="30">
+        <v>1073</v>
+      </c>
+      <c r="H16" s="30">
+        <v>1309</v>
+      </c>
+      <c r="I16" s="29">
+        <v>1.2199440800000001</v>
       </c>
       <c r="J16" s="29" t="s">
         <v>2</v>
@@ -3419,17 +3368,17 @@
       <c r="K16" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="L16" s="31" t="n">
-        <v>47369.0</v>
+      <c r="L16" s="31">
+        <v>47369</v>
       </c>
       <c r="M16" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="N16" s="29" t="n">
-        <v>1209.0</v>
-      </c>
-      <c r="O16" s="29" t="n">
-        <v>9.0</v>
+      <c r="N16" s="29">
+        <v>1209</v>
+      </c>
+      <c r="O16" s="29">
+        <v>9</v>
       </c>
       <c r="P16" s="32" t="s">
         <v>33</v>
@@ -3441,7 +3390,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B17" s="27" t="s">
         <v>20</v>
       </c>
@@ -3457,32 +3406,32 @@
       <c r="F17" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="G17" s="30" t="n">
-        <v>4401.0</v>
-      </c>
-      <c r="H17" s="30" t="n">
-        <v>5811.0</v>
-      </c>
-      <c r="I17" s="29" t="n">
+      <c r="G17" s="30">
+        <v>4401</v>
+      </c>
+      <c r="H17" s="30">
+        <v>5811</v>
+      </c>
+      <c r="I17" s="29">
         <v>1.32038173</v>
       </c>
       <c r="J17" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="K17" s="29" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="L17" s="31" t="n">
-        <v>135223.0</v>
-      </c>
-      <c r="M17" s="31" t="n">
-        <v>135223.0</v>
-      </c>
-      <c r="N17" s="29" t="n">
-        <v>5511.0</v>
-      </c>
-      <c r="O17" s="29" t="n">
-        <v>32.0</v>
+      <c r="K17" s="29">
+        <v>1</v>
+      </c>
+      <c r="L17" s="31">
+        <v>135223</v>
+      </c>
+      <c r="M17" s="31">
+        <v>135223</v>
+      </c>
+      <c r="N17" s="29">
+        <v>5511</v>
+      </c>
+      <c r="O17" s="29">
+        <v>32</v>
       </c>
       <c r="P17" s="32" t="s">
         <v>34</v>
@@ -3494,7 +3443,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B18" s="27" t="s">
         <v>20</v>
       </c>
@@ -3510,32 +3459,32 @@
       <c r="F18" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="G18" s="30" t="n">
-        <v>4401.0</v>
-      </c>
-      <c r="H18" s="30" t="n">
-        <v>5811.0</v>
-      </c>
-      <c r="I18" s="29" t="n">
+      <c r="G18" s="30">
+        <v>4401</v>
+      </c>
+      <c r="H18" s="30">
+        <v>5811</v>
+      </c>
+      <c r="I18" s="29">
         <v>1.32038173</v>
       </c>
       <c r="J18" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="K18" s="29" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="L18" s="31" t="n">
-        <v>135223.0</v>
-      </c>
-      <c r="M18" s="31" t="n">
-        <v>135223.0</v>
-      </c>
-      <c r="N18" s="29" t="n">
-        <v>5511.0</v>
-      </c>
-      <c r="O18" s="29" t="n">
-        <v>32.0</v>
+      <c r="K18" s="29">
+        <v>1</v>
+      </c>
+      <c r="L18" s="31">
+        <v>135223</v>
+      </c>
+      <c r="M18" s="31">
+        <v>135223</v>
+      </c>
+      <c r="N18" s="29">
+        <v>5511</v>
+      </c>
+      <c r="O18" s="29">
+        <v>32</v>
       </c>
       <c r="P18" s="32" t="s">
         <v>34</v>
@@ -3547,7 +3496,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B19" s="27" t="s">
         <v>20</v>
       </c>
@@ -3563,32 +3512,32 @@
       <c r="F19" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="G19" s="30" t="n">
-        <v>1442.0</v>
-      </c>
-      <c r="H19" s="30" t="n">
-        <v>2018.0</v>
-      </c>
-      <c r="I19" s="29" t="n">
-        <v>1.39944521</v>
+      <c r="G19" s="30">
+        <v>1442</v>
+      </c>
+      <c r="H19" s="30">
+        <v>2018</v>
+      </c>
+      <c r="I19" s="29">
+        <v>1.3994452100000001</v>
       </c>
       <c r="J19" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="K19" s="29" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="L19" s="31" t="n">
-        <v>98690.0</v>
-      </c>
-      <c r="M19" s="31" t="n">
-        <v>98690.0</v>
-      </c>
-      <c r="N19" s="29" t="n">
-        <v>1946.0</v>
-      </c>
-      <c r="O19" s="29" t="n">
-        <v>19.0</v>
+      <c r="K19" s="29">
+        <v>1</v>
+      </c>
+      <c r="L19" s="31">
+        <v>98690</v>
+      </c>
+      <c r="M19" s="31">
+        <v>98690</v>
+      </c>
+      <c r="N19" s="29">
+        <v>1946</v>
+      </c>
+      <c r="O19" s="29">
+        <v>19</v>
       </c>
       <c r="P19" s="32" t="s">
         <v>35</v>
@@ -3600,7 +3549,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B20" s="27" t="s">
         <v>20</v>
       </c>
@@ -3616,32 +3565,32 @@
       <c r="F20" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="G20" s="30" t="n">
-        <v>1442.0</v>
-      </c>
-      <c r="H20" s="30" t="n">
-        <v>2018.0</v>
-      </c>
-      <c r="I20" s="29" t="n">
-        <v>1.39944521</v>
+      <c r="G20" s="30">
+        <v>1442</v>
+      </c>
+      <c r="H20" s="30">
+        <v>2018</v>
+      </c>
+      <c r="I20" s="29">
+        <v>1.3994452100000001</v>
       </c>
       <c r="J20" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="K20" s="29" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="L20" s="31" t="n">
-        <v>98690.0</v>
-      </c>
-      <c r="M20" s="31" t="n">
-        <v>98690.0</v>
-      </c>
-      <c r="N20" s="29" t="n">
-        <v>1946.0</v>
-      </c>
-      <c r="O20" s="29" t="n">
-        <v>19.0</v>
+      <c r="K20" s="29">
+        <v>1</v>
+      </c>
+      <c r="L20" s="31">
+        <v>98690</v>
+      </c>
+      <c r="M20" s="31">
+        <v>98690</v>
+      </c>
+      <c r="N20" s="29">
+        <v>1946</v>
+      </c>
+      <c r="O20" s="29">
+        <v>19</v>
       </c>
       <c r="P20" s="32" t="s">
         <v>35</v>
@@ -3653,7 +3602,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B21" s="27" t="s">
         <v>20</v>
       </c>
@@ -3669,14 +3618,14 @@
       <c r="F21" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="G21" s="30" t="n">
-        <v>1410.0</v>
-      </c>
-      <c r="H21" s="30" t="n">
-        <v>1820.0</v>
-      </c>
-      <c r="I21" s="29" t="n">
-        <v>1.29078014</v>
+      <c r="G21" s="30">
+        <v>1410</v>
+      </c>
+      <c r="H21" s="30">
+        <v>1820</v>
+      </c>
+      <c r="I21" s="29">
+        <v>1.2907801400000001</v>
       </c>
       <c r="J21" s="29" t="s">
         <v>2</v>
@@ -3684,17 +3633,17 @@
       <c r="K21" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="L21" s="31" t="n">
-        <v>93493.0</v>
+      <c r="L21" s="31">
+        <v>93493</v>
       </c>
       <c r="M21" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="N21" s="29" t="n">
-        <v>1754.0</v>
-      </c>
-      <c r="O21" s="29" t="n">
-        <v>22.0</v>
+      <c r="N21" s="29">
+        <v>1754</v>
+      </c>
+      <c r="O21" s="29">
+        <v>22</v>
       </c>
       <c r="P21" s="32" t="s">
         <v>36</v>
@@ -3706,7 +3655,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B22" s="27" t="s">
         <v>20</v>
       </c>
@@ -3722,14 +3671,14 @@
       <c r="F22" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="G22" s="30" t="n">
-        <v>1410.0</v>
-      </c>
-      <c r="H22" s="30" t="n">
-        <v>1820.0</v>
-      </c>
-      <c r="I22" s="29" t="n">
-        <v>1.29078014</v>
+      <c r="G22" s="30">
+        <v>1410</v>
+      </c>
+      <c r="H22" s="30">
+        <v>1820</v>
+      </c>
+      <c r="I22" s="29">
+        <v>1.2907801400000001</v>
       </c>
       <c r="J22" s="29" t="s">
         <v>2</v>
@@ -3737,17 +3686,17 @@
       <c r="K22" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="L22" s="31" t="n">
-        <v>93493.0</v>
+      <c r="L22" s="31">
+        <v>93493</v>
       </c>
       <c r="M22" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="N22" s="29" t="n">
-        <v>1754.0</v>
-      </c>
-      <c r="O22" s="29" t="n">
-        <v>22.0</v>
+      <c r="N22" s="29">
+        <v>1754</v>
+      </c>
+      <c r="O22" s="29">
+        <v>22</v>
       </c>
       <c r="P22" s="32" t="s">
         <v>36</v>
@@ -3759,7 +3708,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B23" s="27" t="s">
         <v>20</v>
       </c>
@@ -3775,32 +3724,32 @@
       <c r="F23" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="G23" s="30" t="n">
-        <v>3364.0</v>
-      </c>
-      <c r="H23" s="30" t="n">
-        <v>4572.0</v>
-      </c>
-      <c r="I23" s="29" t="n">
+      <c r="G23" s="30">
+        <v>3364</v>
+      </c>
+      <c r="H23" s="30">
+        <v>4572</v>
+      </c>
+      <c r="I23" s="29">
         <v>1.35909631</v>
       </c>
       <c r="J23" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="K23" s="29" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="L23" s="31" t="n">
-        <v>148329.0</v>
-      </c>
-      <c r="M23" s="31" t="n">
-        <v>148329.0</v>
-      </c>
-      <c r="N23" s="29" t="n">
-        <v>4359.0</v>
-      </c>
-      <c r="O23" s="29" t="n">
-        <v>30.0</v>
+      <c r="K23" s="29">
+        <v>1</v>
+      </c>
+      <c r="L23" s="31">
+        <v>148329</v>
+      </c>
+      <c r="M23" s="31">
+        <v>148329</v>
+      </c>
+      <c r="N23" s="29">
+        <v>4359</v>
+      </c>
+      <c r="O23" s="29">
+        <v>30</v>
       </c>
       <c r="P23" s="32" t="s">
         <v>37</v>
@@ -3812,7 +3761,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B24" s="27" t="s">
         <v>20</v>
       </c>
@@ -3828,32 +3777,32 @@
       <c r="F24" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="G24" s="30" t="n">
-        <v>3364.0</v>
-      </c>
-      <c r="H24" s="30" t="n">
-        <v>4572.0</v>
-      </c>
-      <c r="I24" s="29" t="n">
+      <c r="G24" s="30">
+        <v>3364</v>
+      </c>
+      <c r="H24" s="30">
+        <v>4572</v>
+      </c>
+      <c r="I24" s="29">
         <v>1.35909631</v>
       </c>
       <c r="J24" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="K24" s="29" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="L24" s="31" t="n">
-        <v>148329.0</v>
-      </c>
-      <c r="M24" s="31" t="n">
-        <v>148329.0</v>
-      </c>
-      <c r="N24" s="29" t="n">
-        <v>4359.0</v>
-      </c>
-      <c r="O24" s="29" t="n">
-        <v>30.0</v>
+      <c r="K24" s="29">
+        <v>1</v>
+      </c>
+      <c r="L24" s="31">
+        <v>148329</v>
+      </c>
+      <c r="M24" s="31">
+        <v>148329</v>
+      </c>
+      <c r="N24" s="29">
+        <v>4359</v>
+      </c>
+      <c r="O24" s="29">
+        <v>30</v>
       </c>
       <c r="P24" s="32" t="s">
         <v>37</v>
@@ -3865,7 +3814,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B25" s="27" t="s">
         <v>20</v>
       </c>
@@ -3881,13 +3830,13 @@
       <c r="F25" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="G25" s="30" t="n">
-        <v>2402.0</v>
-      </c>
-      <c r="H25" s="30" t="n">
-        <v>3384.0</v>
-      </c>
-      <c r="I25" s="29" t="n">
+      <c r="G25" s="30">
+        <v>2402</v>
+      </c>
+      <c r="H25" s="30">
+        <v>3384</v>
+      </c>
+      <c r="I25" s="29">
         <v>1.40882598</v>
       </c>
       <c r="J25" s="29" t="s">
@@ -3896,17 +3845,17 @@
       <c r="K25" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="L25" s="31" t="n">
-        <v>100892.0</v>
+      <c r="L25" s="31">
+        <v>100892</v>
       </c>
       <c r="M25" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="N25" s="29" t="n">
-        <v>3046.0</v>
-      </c>
-      <c r="O25" s="29" t="n">
-        <v>22.0</v>
+      <c r="N25" s="29">
+        <v>3046</v>
+      </c>
+      <c r="O25" s="29">
+        <v>22</v>
       </c>
       <c r="P25" s="32" t="s">
         <v>25</v>
@@ -3918,7 +3867,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B26" s="27" t="s">
         <v>20</v>
       </c>
@@ -3934,13 +3883,13 @@
       <c r="F26" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="G26" s="30" t="n">
-        <v>2402.0</v>
-      </c>
-      <c r="H26" s="30" t="n">
-        <v>3384.0</v>
-      </c>
-      <c r="I26" s="29" t="n">
+      <c r="G26" s="30">
+        <v>2402</v>
+      </c>
+      <c r="H26" s="30">
+        <v>3384</v>
+      </c>
+      <c r="I26" s="29">
         <v>1.40882598</v>
       </c>
       <c r="J26" s="29" t="s">
@@ -3949,17 +3898,17 @@
       <c r="K26" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="L26" s="31" t="n">
-        <v>100892.0</v>
+      <c r="L26" s="31">
+        <v>100892</v>
       </c>
       <c r="M26" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="N26" s="29" t="n">
-        <v>3046.0</v>
-      </c>
-      <c r="O26" s="29" t="n">
-        <v>22.0</v>
+      <c r="N26" s="29">
+        <v>3046</v>
+      </c>
+      <c r="O26" s="29">
+        <v>22</v>
       </c>
       <c r="P26" s="32" t="s">
         <v>25</v>
@@ -3971,7 +3920,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B27" s="27" t="s">
         <v>38</v>
       </c>
@@ -3987,32 +3936,32 @@
       <c r="F27" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="G27" s="30" t="n">
-        <v>741.0</v>
-      </c>
-      <c r="H27" s="30" t="n">
-        <v>1096.0</v>
-      </c>
-      <c r="I27" s="29" t="n">
-        <v>1.47908232</v>
+      <c r="G27" s="30">
+        <v>741</v>
+      </c>
+      <c r="H27" s="30">
+        <v>1096</v>
+      </c>
+      <c r="I27" s="29">
+        <v>1.4790823200000001</v>
       </c>
       <c r="J27" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="K27" s="29" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="L27" s="31" t="n">
-        <v>76784.0</v>
-      </c>
-      <c r="M27" s="31" t="n">
-        <v>19196.0</v>
-      </c>
-      <c r="N27" s="29" t="n">
-        <v>1083.0</v>
-      </c>
-      <c r="O27" s="29" t="n">
-        <v>25.0</v>
+      <c r="K27" s="29">
+        <v>4</v>
+      </c>
+      <c r="L27" s="31">
+        <v>76784</v>
+      </c>
+      <c r="M27" s="31">
+        <v>19196</v>
+      </c>
+      <c r="N27" s="29">
+        <v>1083</v>
+      </c>
+      <c r="O27" s="29">
+        <v>25</v>
       </c>
       <c r="P27" s="32" t="s">
         <v>25</v>
@@ -4024,7 +3973,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B28" s="27" t="s">
         <v>38</v>
       </c>
@@ -4040,32 +3989,32 @@
       <c r="F28" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="G28" s="30" t="n">
-        <v>216.0</v>
-      </c>
-      <c r="H28" s="30" t="n">
-        <v>308.0</v>
-      </c>
-      <c r="I28" s="29" t="n">
+      <c r="G28" s="30">
+        <v>216</v>
+      </c>
+      <c r="H28" s="30">
+        <v>308</v>
+      </c>
+      <c r="I28" s="29">
         <v>1.42592593</v>
       </c>
       <c r="J28" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="K28" s="29" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="L28" s="31" t="n">
-        <v>26578.0</v>
-      </c>
-      <c r="M28" s="31" t="n">
-        <v>8859.33333333</v>
-      </c>
-      <c r="N28" s="29" t="n">
-        <v>299.0</v>
-      </c>
-      <c r="O28" s="29" t="n">
-        <v>9.0</v>
+      <c r="K28" s="29">
+        <v>3</v>
+      </c>
+      <c r="L28" s="31">
+        <v>26578</v>
+      </c>
+      <c r="M28" s="31">
+        <v>8859.3333333299997</v>
+      </c>
+      <c r="N28" s="29">
+        <v>299</v>
+      </c>
+      <c r="O28" s="29">
+        <v>9</v>
       </c>
       <c r="P28" s="32" t="s">
         <v>26</v>
@@ -4077,7 +4026,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B29" s="27" t="s">
         <v>38</v>
       </c>
@@ -4093,32 +4042,32 @@
       <c r="F29" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="G29" s="30" t="n">
-        <v>216.0</v>
-      </c>
-      <c r="H29" s="30" t="n">
-        <v>308.0</v>
-      </c>
-      <c r="I29" s="29" t="n">
+      <c r="G29" s="30">
+        <v>216</v>
+      </c>
+      <c r="H29" s="30">
+        <v>308</v>
+      </c>
+      <c r="I29" s="29">
         <v>1.42592593</v>
       </c>
       <c r="J29" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="K29" s="29" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="L29" s="31" t="n">
-        <v>26578.0</v>
-      </c>
-      <c r="M29" s="31" t="n">
-        <v>8859.33333333</v>
-      </c>
-      <c r="N29" s="29" t="n">
-        <v>299.0</v>
-      </c>
-      <c r="O29" s="29" t="n">
-        <v>9.0</v>
+      <c r="K29" s="29">
+        <v>3</v>
+      </c>
+      <c r="L29" s="31">
+        <v>26578</v>
+      </c>
+      <c r="M29" s="31">
+        <v>8859.3333333299997</v>
+      </c>
+      <c r="N29" s="29">
+        <v>299</v>
+      </c>
+      <c r="O29" s="29">
+        <v>9</v>
       </c>
       <c r="P29" s="32" t="s">
         <v>26</v>
@@ -4130,7 +4079,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B30" s="27" t="s">
         <v>38</v>
       </c>
@@ -4146,32 +4095,32 @@
       <c r="F30" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="G30" s="30" t="n">
-        <v>291.0</v>
-      </c>
-      <c r="H30" s="30" t="n">
-        <v>371.0</v>
-      </c>
-      <c r="I30" s="29" t="n">
+      <c r="G30" s="30">
+        <v>291</v>
+      </c>
+      <c r="H30" s="30">
+        <v>371</v>
+      </c>
+      <c r="I30" s="29">
         <v>1.27491409</v>
       </c>
       <c r="J30" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="K30" s="29" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="L30" s="31" t="n">
-        <v>27404.0</v>
-      </c>
-      <c r="M30" s="31" t="n">
-        <v>27404.0</v>
-      </c>
-      <c r="N30" s="29" t="n">
-        <v>368.0</v>
-      </c>
-      <c r="O30" s="29" t="n">
-        <v>13.0</v>
+      <c r="K30" s="29">
+        <v>1</v>
+      </c>
+      <c r="L30" s="31">
+        <v>27404</v>
+      </c>
+      <c r="M30" s="31">
+        <v>27404</v>
+      </c>
+      <c r="N30" s="29">
+        <v>368</v>
+      </c>
+      <c r="O30" s="29">
+        <v>13</v>
       </c>
       <c r="P30" s="32" t="s">
         <v>29</v>
@@ -4183,7 +4132,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B31" s="27" t="s">
         <v>38</v>
       </c>
@@ -4199,32 +4148,32 @@
       <c r="F31" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="G31" s="30" t="n">
-        <v>291.0</v>
-      </c>
-      <c r="H31" s="30" t="n">
-        <v>371.0</v>
-      </c>
-      <c r="I31" s="29" t="n">
+      <c r="G31" s="30">
+        <v>291</v>
+      </c>
+      <c r="H31" s="30">
+        <v>371</v>
+      </c>
+      <c r="I31" s="29">
         <v>1.27491409</v>
       </c>
       <c r="J31" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="K31" s="29" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="L31" s="31" t="n">
-        <v>27404.0</v>
-      </c>
-      <c r="M31" s="31" t="n">
-        <v>27404.0</v>
-      </c>
-      <c r="N31" s="29" t="n">
-        <v>368.0</v>
-      </c>
-      <c r="O31" s="29" t="n">
-        <v>13.0</v>
+      <c r="K31" s="29">
+        <v>1</v>
+      </c>
+      <c r="L31" s="31">
+        <v>27404</v>
+      </c>
+      <c r="M31" s="31">
+        <v>27404</v>
+      </c>
+      <c r="N31" s="29">
+        <v>368</v>
+      </c>
+      <c r="O31" s="29">
+        <v>13</v>
       </c>
       <c r="P31" s="32" t="s">
         <v>29</v>
@@ -4236,7 +4185,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B32" s="27" t="s">
         <v>38</v>
       </c>
@@ -4252,14 +4201,14 @@
       <c r="F32" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="G32" s="30" t="n">
-        <v>362.0</v>
-      </c>
-      <c r="H32" s="30" t="n">
-        <v>417.0</v>
-      </c>
-      <c r="I32" s="29" t="n">
-        <v>1.1519337</v>
+      <c r="G32" s="30">
+        <v>362</v>
+      </c>
+      <c r="H32" s="30">
+        <v>417</v>
+      </c>
+      <c r="I32" s="29">
+        <v>1.1519337000000001</v>
       </c>
       <c r="J32" s="29" t="s">
         <v>2</v>
@@ -4267,17 +4216,17 @@
       <c r="K32" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="L32" s="31" t="n">
-        <v>22802.0</v>
+      <c r="L32" s="31">
+        <v>22802</v>
       </c>
       <c r="M32" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="N32" s="29" t="n">
-        <v>416.0</v>
-      </c>
-      <c r="O32" s="29" t="n">
-        <v>3.0</v>
+      <c r="N32" s="29">
+        <v>416</v>
+      </c>
+      <c r="O32" s="29">
+        <v>3</v>
       </c>
       <c r="P32" s="32" t="s">
         <v>30</v>
@@ -4289,7 +4238,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B33" s="27" t="s">
         <v>38</v>
       </c>
@@ -4305,14 +4254,14 @@
       <c r="F33" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="G33" s="30" t="n">
-        <v>362.0</v>
-      </c>
-      <c r="H33" s="30" t="n">
-        <v>417.0</v>
-      </c>
-      <c r="I33" s="29" t="n">
-        <v>1.1519337</v>
+      <c r="G33" s="30">
+        <v>362</v>
+      </c>
+      <c r="H33" s="30">
+        <v>417</v>
+      </c>
+      <c r="I33" s="29">
+        <v>1.1519337000000001</v>
       </c>
       <c r="J33" s="29" t="s">
         <v>2</v>
@@ -4320,17 +4269,17 @@
       <c r="K33" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="L33" s="31" t="n">
-        <v>22802.0</v>
+      <c r="L33" s="31">
+        <v>22802</v>
       </c>
       <c r="M33" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="N33" s="29" t="n">
-        <v>416.0</v>
-      </c>
-      <c r="O33" s="29" t="n">
-        <v>3.0</v>
+      <c r="N33" s="29">
+        <v>416</v>
+      </c>
+      <c r="O33" s="29">
+        <v>3</v>
       </c>
       <c r="P33" s="32" t="s">
         <v>30</v>
@@ -4344,9 +4293,9 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink location="'Formatted Report'!A1" ref="C1"/>
+    <hyperlink ref="C1" location="'Formatted Report'!A1" display="This is raw data. See Sheet 1 for a formatted report." xr:uid="{00000000-0004-0000-0100-000000000000}"/>
   </hyperlinks>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/back/storage/app/ads/2026-10/meta-okt-Format.xlsx
+++ b/back/storage/app/ads/2026-10/meta-okt-Format.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\projects\pulse-kembaliapps\ads-performance\back\storage\app\ads\2026-10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1889F0B6-8660-4E6B-B539-3B9BEFC263EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE70D114-4137-4367-B488-BFAB83FA0BE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -974,7 +974,7 @@
         <v>1017845</v>
       </c>
       <c r="N4" s="15">
-        <v>227230.625</v>
+        <v>327230.625</v>
       </c>
       <c r="O4" s="12">
         <v>44783</v>

--- a/back/storage/app/ads/2026-10/meta-okt-Format.xlsx
+++ b/back/storage/app/ads/2026-10/meta-okt-Format.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\projects\pulse-kembaliapps\ads-performance\back\storage\app\ads\2026-10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE70D114-4137-4367-B488-BFAB83FA0BE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E911E1EB-4D6F-43AD-B3FC-E3B7BD0AAA6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -971,7 +971,7 @@
         <v>8</v>
       </c>
       <c r="M4" s="15">
-        <v>1017845</v>
+        <v>2017845</v>
       </c>
       <c r="N4" s="15">
         <v>327230.625</v>
@@ -1027,7 +1027,7 @@
         <v>2</v>
       </c>
       <c r="M5" s="15">
-        <v>116395</v>
+        <v>126395</v>
       </c>
       <c r="N5" s="15">
         <v>58197.5</v>

--- a/back/storage/app/ads/2026-10/meta-okt-Format.xlsx
+++ b/back/storage/app/ads/2026-10/meta-okt-Format.xlsx
@@ -1,14 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr date1904="false"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\projects\pulse-kembaliapps\ads-performance\back\storage\app\ads\2026-10\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7ACE688-B823-419D-A36B-35DDC40FFC2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Formatted Report" r:id="rId3" sheetId="1"/>
-    <sheet name="Raw Data Report" r:id="rId4" sheetId="2" state="hidden"/>
+    <sheet name="Formatted Report" sheetId="1" r:id="rId1"/>
+    <sheet name="Raw Data Report" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -165,85 +173,70 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="d/m"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color indexed="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <sz val="11.0"/>
-      <color rgb="FF000000"/>
-      <u val="none"/>
     </font>
     <font>
+      <sz val="18"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-      <sz val="11.0"/>
-      <color rgb="FF000000"/>
-      <u val="none"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-      <sz val="18.0"/>
-      <color rgb="FFFFFFFF"/>
-      <u val="none"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-      <sz val="11.0"/>
-      <color rgb="FFFFFFFF"/>
-      <u val="none"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <sz val="11.0"/>
-      <color rgb="FFFFFFFF"/>
-      <u val="single"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <color rgb="FF000000"/>
-      <b val="true"/>
-      <u val="none"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="darkGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
-      <patternFill patternType="none">
-        <fgColor rgb="FFFFFF"/>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF"/>
+        <fgColor rgb="FF41596C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="41596C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="A0B0BA"/>
+        <fgColor rgb="FFA0B0BA"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="32">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -254,423 +247,123 @@
     <border>
       <left/>
       <right/>
-      <top>
-        <color rgb="000000"/>
-      </top>
+      <top/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top>
-        <color rgb="000000"/>
+      <top style="thin">
+        <color rgb="FF000000"/>
       </top>
-      <bottom>
-        <color rgb="000000"/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right>
-        <color rgb="000000"/>
-      </right>
-      <top>
-        <color rgb="000000"/>
-      </top>
-      <bottom>
-        <color rgb="000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left>
-        <color rgb="000000"/>
-      </left>
-      <right>
-        <color rgb="000000"/>
-      </right>
-      <top>
-        <color rgb="000000"/>
-      </top>
-      <bottom>
-        <color rgb="000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left>
-        <color rgb="000000"/>
-      </left>
-      <right>
-        <color rgb="000000"/>
-      </right>
-      <bottom>
-        <color rgb="000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left>
-        <color rgb="000000"/>
-      </left>
-      <right>
-        <color rgb="000000"/>
-      </right>
-      <top>
-        <color rgb="000000"/>
-      </top>
-      <diagonal/>
-    </border>
-    <border>
-      <left>
-        <color rgb="000000"/>
-      </left>
-      <top>
-        <color rgb="000000"/>
-      </top>
-      <bottom>
-        <color rgb="000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left>
-        <color rgb="000000"/>
-      </left>
-      <right>
-        <color rgb="000000"/>
+      <right style="thin">
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color rgb="000000"/>
-      </top>
-      <bottom>
-        <color rgb="000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left>
-        <color rgb="000000"/>
-      </left>
-      <right>
-        <color rgb="000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="000000"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color rgb="000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left>
-        <color rgb="000000"/>
-      </left>
-      <top style="thin">
-        <color rgb="000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="000000"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="000000"/>
+        <color rgb="FF000000"/>
       </left>
-      <right>
-        <color rgb="000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="000000"/>
-      </bottom>
+      <right/>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
-      <right>
-        <color rgb="000000"/>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
       </right>
-      <top style="thin">
-        <color rgb="000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="000000"/>
-      </bottom>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left>
-        <color rgb="000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="000000"/>
-      </top>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
-        <color rgb="000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <right style="thin">
-        <color rgb="000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="000000"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="000000"/>
+        <color rgb="FF000000"/>
       </left>
-      <right>
-        <color rgb="000000"/>
-      </right>
-      <top>
-        <color rgb="000000"/>
-      </top>
-      <bottom>
-        <color rgb="000000"/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left>
-        <color rgb="000000"/>
-      </left>
+      <left/>
       <right style="thin">
-        <color rgb="000000"/>
+        <color rgb="FF000000"/>
       </right>
-      <top>
-        <color rgb="000000"/>
-      </top>
-      <bottom>
-        <color rgb="000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <right style="thin">
-        <color rgb="000000"/>
-      </right>
-      <top>
-        <color rgb="000000"/>
-      </top>
-      <bottom>
-        <color rgb="000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left>
-        <color rgb="000000"/>
-      </left>
-      <right>
-        <color rgb="000000"/>
-      </right>
-      <top>
-        <color rgb="000000"/>
-      </top>
+      <top/>
       <bottom style="thin">
-        <color rgb="000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left>
-        <color rgb="000000"/>
-      </left>
-      <top>
-        <color rgb="000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="000000"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="000000"/>
+        <color rgb="FF90949C"/>
       </left>
-      <right>
-        <color rgb="000000"/>
+      <right style="thin">
+        <color rgb="FF90949C"/>
       </right>
-      <top>
-        <color rgb="000000"/>
+      <top style="thin">
+        <color rgb="FF90949C"/>
       </top>
       <bottom style="thin">
-        <color rgb="000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <right>
-        <color rgb="000000"/>
-      </right>
-      <top>
-        <color rgb="000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left>
-        <color rgb="000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="000000"/>
-      </right>
-      <top>
-        <color rgb="000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <right style="thin">
-        <color rgb="000000"/>
-      </right>
-      <top>
-        <color rgb="000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left>
-        <color rgb="000000"/>
-      </left>
-      <right>
-        <color rgb="000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="90949C"/>
-      </top>
-      <bottom>
-        <color rgb="000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left>
-        <color rgb="000000"/>
-      </left>
-      <right>
-        <color rgb="000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="90949C"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left>
-        <color rgb="000000"/>
-      </left>
-      <right>
-        <color rgb="000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="90949C"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="90949C"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left>
-        <color rgb="000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="90949C"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="90949C"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left>
-        <color rgb="000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="90949C"/>
-      </right>
-      <top style="thin">
-        <color rgb="90949C"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="90949C"/>
+        <color rgb="FF90949C"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="000000"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color rgb="90949C"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color rgb="90949C"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color rgb="90949C"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="90949C"/>
-      </left>
-      <right style="thin">
-        <color rgb="90949C"/>
-      </right>
-      <top style="thin">
-        <color rgb="90949C"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="90949C"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="000000"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -679,145 +372,123 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="33">
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="9" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="3" borderId="15" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="3" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="3" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="3" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="3" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="3" borderId="16" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="3" borderId="20" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="3" borderId="18" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="3" borderId="18" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="3" borderId="18" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="3" borderId="18" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="18" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="3" borderId="22" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="3" borderId="30" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="3" borderId="30" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="31" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="3" borderId="31" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="3" borderId="31" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="31" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <xdr:twoCellAnchor editAs="twoCell">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>95250</xdr:colOff>
@@ -832,13 +503,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="Picture 1" descr="Picture"/>
+        <xdr:cNvPr id="2" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="true"/>
+          <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -859,8 +536,8 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <xdr:twoCellAnchor editAs="twoCell">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>95250</xdr:colOff>
@@ -875,13 +552,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="Picture 1" descr="Picture"/>
+        <xdr:cNvPr id="2" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="true"/>
+          <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -901,34 +584,318 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4472C4"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:S49"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetFormatPr defaultColWidth="12.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="20" max="16384" style="1" width="12.7109375"/>
-    <col min="19" max="19" style="1" width="23.4375" customWidth="true"/>
-    <col min="18" max="18" style="1" width="23.4375" customWidth="true"/>
-    <col min="17" max="17" style="1" width="23.4375" customWidth="true"/>
-    <col min="16" max="16" style="1" width="23.4375" customWidth="true"/>
-    <col min="15" max="15" style="1" width="23.4375" customWidth="true"/>
-    <col min="14" max="14" style="1" width="23.4375" customWidth="true"/>
-    <col min="13" max="13" style="1" width="23.4375" customWidth="true"/>
-    <col min="12" max="12" style="1" width="23.4375" customWidth="true"/>
-    <col min="11" max="11" style="1" width="23.4375" customWidth="true"/>
-    <col min="10" max="10" style="1" width="23.4375" customWidth="true"/>
-    <col min="9" max="9" style="1" width="23.4375" customWidth="true"/>
-    <col min="8" max="8" style="1" width="23.4375" customWidth="true"/>
-    <col min="7" max="7" style="1" width="23.4375" customWidth="true"/>
-    <col min="6" max="6" style="1" width="23.4375" customWidth="true"/>
-    <col min="5" max="5" style="1" width="1.953125" customWidth="true"/>
-    <col min="4" max="4" style="1" width="23.4375" customWidth="true"/>
-    <col min="3" max="3" style="1" width="23.4375" customWidth="true"/>
-    <col min="2" max="2" style="1" width="58.59375" customWidth="true"/>
-    <col min="1" max="1" width="5.15625" style="1" customWidth="true"/>
+    <col min="1" max="1" width="5.1796875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="58.6328125" style="1" customWidth="1"/>
+    <col min="3" max="4" width="23.453125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="1.08984375" style="1" customWidth="1"/>
+    <col min="6" max="8" width="23.453125" style="1" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="4.1796875" style="1" hidden="1" customWidth="1"/>
+    <col min="10" max="12" width="23.453125" style="1" hidden="1" customWidth="1"/>
+    <col min="13" max="19" width="23.453125" style="1" customWidth="1"/>
+    <col min="20" max="16384" width="12.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="33.0" customHeight="true" s="5" customFormat="true">
+    <row r="1" spans="1:19" s="5" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2"/>
       <c r="B1" s="3" t="s">
         <v>0</v>
@@ -940,7 +907,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B3" s="7" t="s">
         <v>3</v>
       </c>
@@ -996,7 +963,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B4" s="11" t="s">
         <v>20</v>
       </c>
@@ -1015,32 +982,32 @@
       <c r="G4" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="H4" s="14" t="n">
-        <v>42735.0</v>
-      </c>
-      <c r="I4" s="14" t="n">
-        <v>68942.0</v>
-      </c>
-      <c r="J4" s="12" t="n">
-        <v>1.61324441</v>
+      <c r="H4" s="14">
+        <v>42735</v>
+      </c>
+      <c r="I4" s="14">
+        <v>68942</v>
+      </c>
+      <c r="J4" s="12">
+        <v>1.6132444100000001</v>
       </c>
       <c r="K4" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="L4" s="12" t="n">
-        <v>19.0</v>
-      </c>
-      <c r="M4" s="15" t="n">
-        <v>1437864.0</v>
-      </c>
-      <c r="N4" s="15" t="n">
-        <v>75677.05263158</v>
-      </c>
-      <c r="O4" s="12" t="n">
-        <v>63183.0</v>
-      </c>
-      <c r="P4" s="12" t="n">
-        <v>695.0</v>
+      <c r="L4" s="12">
+        <v>19</v>
+      </c>
+      <c r="M4" s="15">
+        <v>1437864</v>
+      </c>
+      <c r="N4" s="15">
+        <v>75677.052631579994</v>
+      </c>
+      <c r="O4" s="12">
+        <v>63183</v>
+      </c>
+      <c r="P4" s="12">
+        <v>695</v>
       </c>
       <c r="Q4" s="16" t="s">
         <v>25</v>
@@ -1052,7 +1019,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B5" s="11" t="s">
         <v>2</v>
       </c>
@@ -1071,32 +1038,32 @@
       <c r="G5" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="H5" s="14" t="n">
-        <v>3445.0</v>
-      </c>
-      <c r="I5" s="14" t="n">
-        <v>4025.0</v>
-      </c>
-      <c r="J5" s="12" t="n">
+      <c r="H5" s="14">
+        <v>3445</v>
+      </c>
+      <c r="I5" s="14">
+        <v>4025</v>
+      </c>
+      <c r="J5" s="12">
         <v>1.16835994</v>
       </c>
       <c r="K5" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="L5" s="12" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="M5" s="15" t="n">
-        <v>117403.0</v>
-      </c>
-      <c r="N5" s="15" t="n">
-        <v>117403.0</v>
-      </c>
-      <c r="O5" s="12" t="n">
-        <v>3868.0</v>
-      </c>
-      <c r="P5" s="12" t="n">
-        <v>41.0</v>
+      <c r="L5" s="12">
+        <v>1</v>
+      </c>
+      <c r="M5" s="15">
+        <v>117403</v>
+      </c>
+      <c r="N5" s="15">
+        <v>117403</v>
+      </c>
+      <c r="O5" s="12">
+        <v>3868</v>
+      </c>
+      <c r="P5" s="12">
+        <v>41</v>
       </c>
       <c r="Q5" s="16" t="s">
         <v>26</v>
@@ -1108,7 +1075,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B6" s="11" t="s">
         <v>2</v>
       </c>
@@ -1127,14 +1094,14 @@
       <c r="G6" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="H6" s="14" t="n">
-        <v>2654.0</v>
-      </c>
-      <c r="I6" s="14" t="n">
-        <v>2851.0</v>
-      </c>
-      <c r="J6" s="12" t="n">
-        <v>1.07422758</v>
+      <c r="H6" s="14">
+        <v>2654</v>
+      </c>
+      <c r="I6" s="14">
+        <v>2851</v>
+      </c>
+      <c r="J6" s="12">
+        <v>1.0742275800000001</v>
       </c>
       <c r="K6" s="12" t="s">
         <v>2</v>
@@ -1142,17 +1109,17 @@
       <c r="L6" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="M6" s="15" t="n">
-        <v>54224.0</v>
+      <c r="M6" s="15">
+        <v>354224</v>
       </c>
       <c r="N6" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="O6" s="12" t="n">
-        <v>2752.0</v>
-      </c>
-      <c r="P6" s="12" t="n">
-        <v>24.0</v>
+      <c r="O6" s="12">
+        <v>2752</v>
+      </c>
+      <c r="P6" s="12">
+        <v>24</v>
       </c>
       <c r="Q6" s="16" t="s">
         <v>26</v>
@@ -1164,7 +1131,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B7" s="11" t="s">
         <v>2</v>
       </c>
@@ -1183,32 +1150,32 @@
       <c r="G7" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="H7" s="14" t="n">
-        <v>846.0</v>
-      </c>
-      <c r="I7" s="14" t="n">
-        <v>1120.0</v>
-      </c>
-      <c r="J7" s="12" t="n">
+      <c r="H7" s="14">
+        <v>846</v>
+      </c>
+      <c r="I7" s="14">
+        <v>1120</v>
+      </c>
+      <c r="J7" s="12">
         <v>1.32387707</v>
       </c>
       <c r="K7" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="L7" s="12" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="M7" s="15" t="n">
-        <v>60983.0</v>
-      </c>
-      <c r="N7" s="15" t="n">
-        <v>60983.0</v>
-      </c>
-      <c r="O7" s="12" t="n">
-        <v>1066.0</v>
-      </c>
-      <c r="P7" s="12" t="n">
-        <v>8.0</v>
+      <c r="L7" s="12">
+        <v>1</v>
+      </c>
+      <c r="M7" s="15">
+        <v>760983</v>
+      </c>
+      <c r="N7" s="15">
+        <v>60983</v>
+      </c>
+      <c r="O7" s="12">
+        <v>1066</v>
+      </c>
+      <c r="P7" s="12">
+        <v>8</v>
       </c>
       <c r="Q7" s="16" t="s">
         <v>26</v>
@@ -1220,7 +1187,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B8" s="11" t="s">
         <v>2</v>
       </c>
@@ -1239,13 +1206,13 @@
       <c r="G8" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="H8" s="14" t="n">
-        <v>47.0</v>
-      </c>
-      <c r="I8" s="14" t="n">
-        <v>54.0</v>
-      </c>
-      <c r="J8" s="12" t="n">
+      <c r="H8" s="14">
+        <v>47</v>
+      </c>
+      <c r="I8" s="14">
+        <v>54</v>
+      </c>
+      <c r="J8" s="12">
         <v>1.14893617</v>
       </c>
       <c r="K8" s="12" t="s">
@@ -1254,17 +1221,17 @@
       <c r="L8" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="M8" s="15" t="n">
-        <v>2196.0</v>
+      <c r="M8" s="15">
+        <v>2196</v>
       </c>
       <c r="N8" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="O8" s="12" t="n">
-        <v>50.0</v>
-      </c>
-      <c r="P8" s="12" t="n">
-        <v>9.0</v>
+      <c r="O8" s="12">
+        <v>50</v>
+      </c>
+      <c r="P8" s="12">
+        <v>9</v>
       </c>
       <c r="Q8" s="16" t="s">
         <v>26</v>
@@ -1276,7 +1243,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B9" s="11" t="s">
         <v>2</v>
       </c>
@@ -1295,32 +1262,32 @@
       <c r="G9" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="H9" s="14" t="n">
-        <v>7739.0</v>
-      </c>
-      <c r="I9" s="14" t="n">
-        <v>9209.0</v>
-      </c>
-      <c r="J9" s="12" t="n">
+      <c r="H9" s="14">
+        <v>7739</v>
+      </c>
+      <c r="I9" s="14">
+        <v>9209</v>
+      </c>
+      <c r="J9" s="12">
         <v>1.18994702</v>
       </c>
       <c r="K9" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="L9" s="12" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="M9" s="15" t="n">
-        <v>208929.0</v>
-      </c>
-      <c r="N9" s="15" t="n">
+      <c r="L9" s="12">
+        <v>8</v>
+      </c>
+      <c r="M9" s="15">
+        <v>208929</v>
+      </c>
+      <c r="N9" s="15">
         <v>26116.125</v>
       </c>
-      <c r="O9" s="12" t="n">
-        <v>9239.0</v>
-      </c>
-      <c r="P9" s="12" t="n">
-        <v>95.0</v>
+      <c r="O9" s="12">
+        <v>9239</v>
+      </c>
+      <c r="P9" s="12">
+        <v>95</v>
       </c>
       <c r="Q9" s="16" t="s">
         <v>31</v>
@@ -1332,7 +1299,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B10" s="11" t="s">
         <v>2</v>
       </c>
@@ -1351,32 +1318,32 @@
       <c r="G10" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="H10" s="14" t="n">
-        <v>4620.0</v>
-      </c>
-      <c r="I10" s="14" t="n">
-        <v>4979.0</v>
-      </c>
-      <c r="J10" s="12" t="n">
-        <v>1.07770563</v>
+      <c r="H10" s="14">
+        <v>4620</v>
+      </c>
+      <c r="I10" s="14">
+        <v>4979</v>
+      </c>
+      <c r="J10" s="12">
+        <v>1.0777056300000001</v>
       </c>
       <c r="K10" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="L10" s="12" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="M10" s="15" t="n">
-        <v>90311.0</v>
-      </c>
-      <c r="N10" s="15" t="n">
+      <c r="L10" s="12">
+        <v>5</v>
+      </c>
+      <c r="M10" s="15">
+        <v>90311</v>
+      </c>
+      <c r="N10" s="15">
         <v>18062.2</v>
       </c>
-      <c r="O10" s="12" t="n">
-        <v>5019.0</v>
-      </c>
-      <c r="P10" s="12" t="n">
-        <v>59.0</v>
+      <c r="O10" s="12">
+        <v>5019</v>
+      </c>
+      <c r="P10" s="12">
+        <v>59</v>
       </c>
       <c r="Q10" s="16" t="s">
         <v>31</v>
@@ -1388,7 +1355,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B11" s="11" t="s">
         <v>2</v>
       </c>
@@ -1407,32 +1374,32 @@
       <c r="G11" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="H11" s="14" t="n">
-        <v>3330.0</v>
-      </c>
-      <c r="I11" s="14" t="n">
-        <v>3948.0</v>
-      </c>
-      <c r="J11" s="12" t="n">
-        <v>1.18558559</v>
+      <c r="H11" s="14">
+        <v>3330</v>
+      </c>
+      <c r="I11" s="14">
+        <v>3948</v>
+      </c>
+      <c r="J11" s="12">
+        <v>1.1855855900000001</v>
       </c>
       <c r="K11" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="L11" s="12" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="M11" s="15" t="n">
-        <v>113822.0</v>
-      </c>
-      <c r="N11" s="15" t="n">
-        <v>37940.66666667</v>
-      </c>
-      <c r="O11" s="12" t="n">
-        <v>3962.0</v>
-      </c>
-      <c r="P11" s="12" t="n">
-        <v>34.0</v>
+      <c r="L11" s="12">
+        <v>3</v>
+      </c>
+      <c r="M11" s="15">
+        <v>113822</v>
+      </c>
+      <c r="N11" s="15">
+        <v>37940.666666669997</v>
+      </c>
+      <c r="O11" s="12">
+        <v>3962</v>
+      </c>
+      <c r="P11" s="12">
+        <v>34</v>
       </c>
       <c r="Q11" s="16" t="s">
         <v>31</v>
@@ -1444,7 +1411,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B12" s="11" t="s">
         <v>2</v>
       </c>
@@ -1463,14 +1430,14 @@
       <c r="G12" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="H12" s="14" t="n">
-        <v>250.0</v>
-      </c>
-      <c r="I12" s="14" t="n">
-        <v>282.0</v>
-      </c>
-      <c r="J12" s="12" t="n">
-        <v>1.128</v>
+      <c r="H12" s="14">
+        <v>250</v>
+      </c>
+      <c r="I12" s="14">
+        <v>282</v>
+      </c>
+      <c r="J12" s="12">
+        <v>1.1279999999999999</v>
       </c>
       <c r="K12" s="12" t="s">
         <v>2</v>
@@ -1478,17 +1445,17 @@
       <c r="L12" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="M12" s="15" t="n">
-        <v>4796.0</v>
+      <c r="M12" s="15">
+        <v>4796</v>
       </c>
       <c r="N12" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="O12" s="12" t="n">
-        <v>258.0</v>
-      </c>
-      <c r="P12" s="12" t="n">
-        <v>2.0</v>
+      <c r="O12" s="12">
+        <v>258</v>
+      </c>
+      <c r="P12" s="12">
+        <v>2</v>
       </c>
       <c r="Q12" s="16" t="s">
         <v>31</v>
@@ -1500,7 +1467,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B13" s="11" t="s">
         <v>2</v>
       </c>
@@ -1519,13 +1486,13 @@
       <c r="G13" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="H13" s="14" t="n">
-        <v>638.0</v>
-      </c>
-      <c r="I13" s="14" t="n">
-        <v>672.0</v>
-      </c>
-      <c r="J13" s="12" t="n">
+      <c r="H13" s="14">
+        <v>638</v>
+      </c>
+      <c r="I13" s="14">
+        <v>672</v>
+      </c>
+      <c r="J13" s="12">
         <v>1.05329154</v>
       </c>
       <c r="K13" s="12" t="s">
@@ -1534,17 +1501,17 @@
       <c r="L13" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="M13" s="15" t="n">
-        <v>5575.0</v>
+      <c r="M13" s="15">
+        <v>5575</v>
       </c>
       <c r="N13" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="O13" s="12" t="n">
-        <v>581.0</v>
-      </c>
-      <c r="P13" s="12" t="n">
-        <v>21.0</v>
+      <c r="O13" s="12">
+        <v>581</v>
+      </c>
+      <c r="P13" s="12">
+        <v>21</v>
       </c>
       <c r="Q13" s="16" t="s">
         <v>32</v>
@@ -1556,7 +1523,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B14" s="11" t="s">
         <v>2</v>
       </c>
@@ -1575,13 +1542,13 @@
       <c r="G14" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="H14" s="14" t="n">
-        <v>638.0</v>
-      </c>
-      <c r="I14" s="14" t="n">
-        <v>672.0</v>
-      </c>
-      <c r="J14" s="12" t="n">
+      <c r="H14" s="14">
+        <v>638</v>
+      </c>
+      <c r="I14" s="14">
+        <v>672</v>
+      </c>
+      <c r="J14" s="12">
         <v>1.05329154</v>
       </c>
       <c r="K14" s="12" t="s">
@@ -1590,17 +1557,17 @@
       <c r="L14" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="M14" s="15" t="n">
-        <v>5575.0</v>
+      <c r="M14" s="15">
+        <v>5575</v>
       </c>
       <c r="N14" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="O14" s="12" t="n">
-        <v>581.0</v>
-      </c>
-      <c r="P14" s="12" t="n">
-        <v>21.0</v>
+      <c r="O14" s="12">
+        <v>581</v>
+      </c>
+      <c r="P14" s="12">
+        <v>21</v>
       </c>
       <c r="Q14" s="16" t="s">
         <v>32</v>
@@ -1612,7 +1579,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B15" s="11" t="s">
         <v>2</v>
       </c>
@@ -1631,32 +1598,32 @@
       <c r="G15" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="H15" s="14" t="n">
-        <v>4425.0</v>
-      </c>
-      <c r="I15" s="14" t="n">
-        <v>5405.0</v>
-      </c>
-      <c r="J15" s="12" t="n">
-        <v>1.22146893</v>
+      <c r="H15" s="14">
+        <v>4425</v>
+      </c>
+      <c r="I15" s="14">
+        <v>5405</v>
+      </c>
+      <c r="J15" s="12">
+        <v>1.2214689299999999</v>
       </c>
       <c r="K15" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="L15" s="12" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="M15" s="15" t="n">
-        <v>88004.0</v>
-      </c>
-      <c r="N15" s="15" t="n">
-        <v>44002.0</v>
-      </c>
-      <c r="O15" s="12" t="n">
-        <v>4705.0</v>
-      </c>
-      <c r="P15" s="12" t="n">
-        <v>102.0</v>
+      <c r="L15" s="12">
+        <v>2</v>
+      </c>
+      <c r="M15" s="15">
+        <v>88004</v>
+      </c>
+      <c r="N15" s="15">
+        <v>44002</v>
+      </c>
+      <c r="O15" s="12">
+        <v>4705</v>
+      </c>
+      <c r="P15" s="12">
+        <v>102</v>
       </c>
       <c r="Q15" s="16" t="s">
         <v>33</v>
@@ -1668,7 +1635,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B16" s="11" t="s">
         <v>2</v>
       </c>
@@ -1687,32 +1654,32 @@
       <c r="G16" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="H16" s="14" t="n">
-        <v>4425.0</v>
-      </c>
-      <c r="I16" s="14" t="n">
-        <v>5405.0</v>
-      </c>
-      <c r="J16" s="12" t="n">
-        <v>1.22146893</v>
+      <c r="H16" s="14">
+        <v>4425</v>
+      </c>
+      <c r="I16" s="14">
+        <v>5405</v>
+      </c>
+      <c r="J16" s="12">
+        <v>1.2214689299999999</v>
       </c>
       <c r="K16" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="L16" s="12" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="M16" s="15" t="n">
-        <v>88004.0</v>
-      </c>
-      <c r="N16" s="15" t="n">
-        <v>44002.0</v>
-      </c>
-      <c r="O16" s="12" t="n">
-        <v>4705.0</v>
-      </c>
-      <c r="P16" s="12" t="n">
-        <v>102.0</v>
+      <c r="L16" s="12">
+        <v>2</v>
+      </c>
+      <c r="M16" s="15">
+        <v>88004</v>
+      </c>
+      <c r="N16" s="15">
+        <v>44002</v>
+      </c>
+      <c r="O16" s="12">
+        <v>4705</v>
+      </c>
+      <c r="P16" s="12">
+        <v>102</v>
       </c>
       <c r="Q16" s="16" t="s">
         <v>33</v>
@@ -1724,7 +1691,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B17" s="11" t="s">
         <v>2</v>
       </c>
@@ -1743,32 +1710,32 @@
       <c r="G17" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="H17" s="14" t="n">
-        <v>5384.0</v>
-      </c>
-      <c r="I17" s="14" t="n">
-        <v>6927.0</v>
-      </c>
-      <c r="J17" s="12" t="n">
-        <v>1.2865899</v>
+      <c r="H17" s="14">
+        <v>5384</v>
+      </c>
+      <c r="I17" s="14">
+        <v>6927</v>
+      </c>
+      <c r="J17" s="12">
+        <v>1.2865899000000001</v>
       </c>
       <c r="K17" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="L17" s="12" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="M17" s="15" t="n">
-        <v>116503.0</v>
-      </c>
-      <c r="N17" s="15" t="n">
+      <c r="L17" s="12">
+        <v>2</v>
+      </c>
+      <c r="M17" s="15">
+        <v>116503</v>
+      </c>
+      <c r="N17" s="15">
         <v>58251.5</v>
       </c>
-      <c r="O17" s="12" t="n">
-        <v>6052.0</v>
-      </c>
-      <c r="P17" s="12" t="n">
-        <v>114.0</v>
+      <c r="O17" s="12">
+        <v>6052</v>
+      </c>
+      <c r="P17" s="12">
+        <v>114</v>
       </c>
       <c r="Q17" s="16" t="s">
         <v>34</v>
@@ -1780,7 +1747,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B18" s="11" t="s">
         <v>2</v>
       </c>
@@ -1799,32 +1766,32 @@
       <c r="G18" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="H18" s="14" t="n">
-        <v>5384.0</v>
-      </c>
-      <c r="I18" s="14" t="n">
-        <v>6927.0</v>
-      </c>
-      <c r="J18" s="12" t="n">
-        <v>1.2865899</v>
+      <c r="H18" s="14">
+        <v>5384</v>
+      </c>
+      <c r="I18" s="14">
+        <v>6927</v>
+      </c>
+      <c r="J18" s="12">
+        <v>1.2865899000000001</v>
       </c>
       <c r="K18" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="L18" s="12" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="M18" s="15" t="n">
-        <v>116503.0</v>
-      </c>
-      <c r="N18" s="15" t="n">
+      <c r="L18" s="12">
+        <v>2</v>
+      </c>
+      <c r="M18" s="15">
+        <v>116503</v>
+      </c>
+      <c r="N18" s="15">
         <v>58251.5</v>
       </c>
-      <c r="O18" s="12" t="n">
-        <v>6052.0</v>
-      </c>
-      <c r="P18" s="12" t="n">
-        <v>114.0</v>
+      <c r="O18" s="12">
+        <v>6052</v>
+      </c>
+      <c r="P18" s="12">
+        <v>114</v>
       </c>
       <c r="Q18" s="16" t="s">
         <v>34</v>
@@ -1836,7 +1803,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B19" s="11" t="s">
         <v>2</v>
       </c>
@@ -1855,13 +1822,13 @@
       <c r="G19" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="H19" s="14" t="n">
-        <v>10291.0</v>
-      </c>
-      <c r="I19" s="14" t="n">
-        <v>12587.0</v>
-      </c>
-      <c r="J19" s="12" t="n">
+      <c r="H19" s="14">
+        <v>10291</v>
+      </c>
+      <c r="I19" s="14">
+        <v>12587</v>
+      </c>
+      <c r="J19" s="12">
         <v>1.22310757</v>
       </c>
       <c r="K19" s="12" t="s">
@@ -1870,17 +1837,17 @@
       <c r="L19" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="M19" s="15" t="n">
-        <v>102910.0</v>
+      <c r="M19" s="15">
+        <v>102910</v>
       </c>
       <c r="N19" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="O19" s="12" t="n">
-        <v>10752.0</v>
-      </c>
-      <c r="P19" s="12" t="n">
-        <v>123.0</v>
+      <c r="O19" s="12">
+        <v>10752</v>
+      </c>
+      <c r="P19" s="12">
+        <v>123</v>
       </c>
       <c r="Q19" s="16" t="s">
         <v>35</v>
@@ -1892,7 +1859,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B20" s="11" t="s">
         <v>2</v>
       </c>
@@ -1911,13 +1878,13 @@
       <c r="G20" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="H20" s="14" t="n">
-        <v>10291.0</v>
-      </c>
-      <c r="I20" s="14" t="n">
-        <v>12587.0</v>
-      </c>
-      <c r="J20" s="12" t="n">
+      <c r="H20" s="14">
+        <v>10291</v>
+      </c>
+      <c r="I20" s="14">
+        <v>12587</v>
+      </c>
+      <c r="J20" s="12">
         <v>1.22310757</v>
       </c>
       <c r="K20" s="12" t="s">
@@ -1926,17 +1893,17 @@
       <c r="L20" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="M20" s="15" t="n">
-        <v>102910.0</v>
+      <c r="M20" s="15">
+        <v>102910</v>
       </c>
       <c r="N20" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="O20" s="12" t="n">
-        <v>10752.0</v>
-      </c>
-      <c r="P20" s="12" t="n">
-        <v>123.0</v>
+      <c r="O20" s="12">
+        <v>10752</v>
+      </c>
+      <c r="P20" s="12">
+        <v>123</v>
       </c>
       <c r="Q20" s="16" t="s">
         <v>35</v>
@@ -1948,7 +1915,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B21" s="11" t="s">
         <v>2</v>
       </c>
@@ -1967,32 +1934,32 @@
       <c r="G21" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="H21" s="14" t="n">
-        <v>5423.0</v>
-      </c>
-      <c r="I21" s="14" t="n">
-        <v>6748.0</v>
-      </c>
-      <c r="J21" s="12" t="n">
-        <v>1.24432971</v>
+      <c r="H21" s="14">
+        <v>5423</v>
+      </c>
+      <c r="I21" s="14">
+        <v>6748</v>
+      </c>
+      <c r="J21" s="12">
+        <v>1.2443297099999999</v>
       </c>
       <c r="K21" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="L21" s="12" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="M21" s="15" t="n">
-        <v>77820.0</v>
-      </c>
-      <c r="N21" s="15" t="n">
-        <v>38910.0</v>
-      </c>
-      <c r="O21" s="12" t="n">
-        <v>6173.0</v>
-      </c>
-      <c r="P21" s="12" t="n">
-        <v>33.0</v>
+      <c r="L21" s="12">
+        <v>2</v>
+      </c>
+      <c r="M21" s="15">
+        <v>77820</v>
+      </c>
+      <c r="N21" s="15">
+        <v>38910</v>
+      </c>
+      <c r="O21" s="12">
+        <v>6173</v>
+      </c>
+      <c r="P21" s="12">
+        <v>33</v>
       </c>
       <c r="Q21" s="16" t="s">
         <v>36</v>
@@ -2004,7 +1971,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B22" s="11" t="s">
         <v>2</v>
       </c>
@@ -2023,32 +1990,32 @@
       <c r="G22" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="H22" s="14" t="n">
-        <v>5423.0</v>
-      </c>
-      <c r="I22" s="14" t="n">
-        <v>6748.0</v>
-      </c>
-      <c r="J22" s="12" t="n">
-        <v>1.24432971</v>
+      <c r="H22" s="14">
+        <v>5423</v>
+      </c>
+      <c r="I22" s="14">
+        <v>6748</v>
+      </c>
+      <c r="J22" s="12">
+        <v>1.2443297099999999</v>
       </c>
       <c r="K22" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="L22" s="12" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="M22" s="15" t="n">
-        <v>77820.0</v>
-      </c>
-      <c r="N22" s="15" t="n">
-        <v>38910.0</v>
-      </c>
-      <c r="O22" s="12" t="n">
-        <v>6173.0</v>
-      </c>
-      <c r="P22" s="12" t="n">
-        <v>33.0</v>
+      <c r="L22" s="12">
+        <v>2</v>
+      </c>
+      <c r="M22" s="15">
+        <v>77820</v>
+      </c>
+      <c r="N22" s="15">
+        <v>38910</v>
+      </c>
+      <c r="O22" s="12">
+        <v>6173</v>
+      </c>
+      <c r="P22" s="12">
+        <v>33</v>
       </c>
       <c r="Q22" s="16" t="s">
         <v>36</v>
@@ -2060,7 +2027,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B23" s="11" t="s">
         <v>2</v>
       </c>
@@ -2079,14 +2046,14 @@
       <c r="G23" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="H23" s="14" t="n">
-        <v>1143.0</v>
-      </c>
-      <c r="I23" s="14" t="n">
-        <v>1402.0</v>
-      </c>
-      <c r="J23" s="12" t="n">
-        <v>1.22659668</v>
+      <c r="H23" s="14">
+        <v>1143</v>
+      </c>
+      <c r="I23" s="14">
+        <v>1402</v>
+      </c>
+      <c r="J23" s="12">
+        <v>1.2265966800000001</v>
       </c>
       <c r="K23" s="12" t="s">
         <v>2</v>
@@ -2094,17 +2061,17 @@
       <c r="L23" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="M23" s="15" t="n">
-        <v>17415.0</v>
+      <c r="M23" s="15">
+        <v>17415</v>
       </c>
       <c r="N23" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="O23" s="12" t="n">
-        <v>1249.0</v>
-      </c>
-      <c r="P23" s="12" t="n">
-        <v>5.0</v>
+      <c r="O23" s="12">
+        <v>1249</v>
+      </c>
+      <c r="P23" s="12">
+        <v>5</v>
       </c>
       <c r="Q23" s="16" t="s">
         <v>37</v>
@@ -2116,7 +2083,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B24" s="11" t="s">
         <v>2</v>
       </c>
@@ -2135,14 +2102,14 @@
       <c r="G24" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="H24" s="14" t="n">
-        <v>1143.0</v>
-      </c>
-      <c r="I24" s="14" t="n">
-        <v>1402.0</v>
-      </c>
-      <c r="J24" s="12" t="n">
-        <v>1.22659668</v>
+      <c r="H24" s="14">
+        <v>1143</v>
+      </c>
+      <c r="I24" s="14">
+        <v>1402</v>
+      </c>
+      <c r="J24" s="12">
+        <v>1.2265966800000001</v>
       </c>
       <c r="K24" s="12" t="s">
         <v>2</v>
@@ -2150,17 +2117,17 @@
       <c r="L24" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="M24" s="15" t="n">
-        <v>17415.0</v>
+      <c r="M24" s="15">
+        <v>17415</v>
       </c>
       <c r="N24" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="O24" s="12" t="n">
-        <v>1249.0</v>
-      </c>
-      <c r="P24" s="12" t="n">
-        <v>5.0</v>
+      <c r="O24" s="12">
+        <v>1249</v>
+      </c>
+      <c r="P24" s="12">
+        <v>5</v>
       </c>
       <c r="Q24" s="16" t="s">
         <v>37</v>
@@ -2172,7 +2139,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B25" s="11" t="s">
         <v>2</v>
       </c>
@@ -2191,32 +2158,32 @@
       <c r="G25" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="H25" s="14" t="n">
-        <v>2339.0</v>
-      </c>
-      <c r="I25" s="14" t="n">
-        <v>3053.0</v>
-      </c>
-      <c r="J25" s="12" t="n">
+      <c r="H25" s="14">
+        <v>2339</v>
+      </c>
+      <c r="I25" s="14">
+        <v>3053</v>
+      </c>
+      <c r="J25" s="12">
         <v>1.30525866</v>
       </c>
       <c r="K25" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="L25" s="12" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="M25" s="15" t="n">
-        <v>79309.0</v>
-      </c>
-      <c r="N25" s="15" t="n">
-        <v>79309.0</v>
-      </c>
-      <c r="O25" s="12" t="n">
-        <v>2739.0</v>
-      </c>
-      <c r="P25" s="12" t="n">
-        <v>27.0</v>
+      <c r="L25" s="12">
+        <v>1</v>
+      </c>
+      <c r="M25" s="15">
+        <v>79309</v>
+      </c>
+      <c r="N25" s="15">
+        <v>79309</v>
+      </c>
+      <c r="O25" s="12">
+        <v>2739</v>
+      </c>
+      <c r="P25" s="12">
+        <v>27</v>
       </c>
       <c r="Q25" s="16" t="s">
         <v>38</v>
@@ -2228,7 +2195,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B26" s="11" t="s">
         <v>2</v>
       </c>
@@ -2247,32 +2214,32 @@
       <c r="G26" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="H26" s="14" t="n">
-        <v>2339.0</v>
-      </c>
-      <c r="I26" s="14" t="n">
-        <v>3053.0</v>
-      </c>
-      <c r="J26" s="12" t="n">
+      <c r="H26" s="14">
+        <v>2339</v>
+      </c>
+      <c r="I26" s="14">
+        <v>3053</v>
+      </c>
+      <c r="J26" s="12">
         <v>1.30525866</v>
       </c>
       <c r="K26" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="L26" s="12" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="M26" s="15" t="n">
-        <v>79309.0</v>
-      </c>
-      <c r="N26" s="15" t="n">
-        <v>79309.0</v>
-      </c>
-      <c r="O26" s="12" t="n">
-        <v>2739.0</v>
-      </c>
-      <c r="P26" s="12" t="n">
-        <v>27.0</v>
+      <c r="L26" s="12">
+        <v>1</v>
+      </c>
+      <c r="M26" s="15">
+        <v>79309</v>
+      </c>
+      <c r="N26" s="15">
+        <v>79309</v>
+      </c>
+      <c r="O26" s="12">
+        <v>2739</v>
+      </c>
+      <c r="P26" s="12">
+        <v>27</v>
       </c>
       <c r="Q26" s="16" t="s">
         <v>38</v>
@@ -2284,7 +2251,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B27" s="11" t="s">
         <v>2</v>
       </c>
@@ -2303,14 +2270,14 @@
       <c r="G27" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="H27" s="14" t="n">
-        <v>1073.0</v>
-      </c>
-      <c r="I27" s="14" t="n">
-        <v>1309.0</v>
-      </c>
-      <c r="J27" s="12" t="n">
-        <v>1.21994408</v>
+      <c r="H27" s="14">
+        <v>1073</v>
+      </c>
+      <c r="I27" s="14">
+        <v>1309</v>
+      </c>
+      <c r="J27" s="12">
+        <v>1.2199440800000001</v>
       </c>
       <c r="K27" s="12" t="s">
         <v>2</v>
@@ -2318,17 +2285,17 @@
       <c r="L27" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="M27" s="15" t="n">
-        <v>47369.0</v>
+      <c r="M27" s="15">
+        <v>47369</v>
       </c>
       <c r="N27" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="O27" s="12" t="n">
-        <v>1209.0</v>
-      </c>
-      <c r="P27" s="12" t="n">
-        <v>9.0</v>
+      <c r="O27" s="12">
+        <v>1209</v>
+      </c>
+      <c r="P27" s="12">
+        <v>9</v>
       </c>
       <c r="Q27" s="16" t="s">
         <v>39</v>
@@ -2340,7 +2307,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B28" s="11" t="s">
         <v>2</v>
       </c>
@@ -2359,14 +2326,14 @@
       <c r="G28" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="H28" s="14" t="n">
-        <v>1073.0</v>
-      </c>
-      <c r="I28" s="14" t="n">
-        <v>1309.0</v>
-      </c>
-      <c r="J28" s="12" t="n">
-        <v>1.21994408</v>
+      <c r="H28" s="14">
+        <v>1073</v>
+      </c>
+      <c r="I28" s="14">
+        <v>1309</v>
+      </c>
+      <c r="J28" s="12">
+        <v>1.2199440800000001</v>
       </c>
       <c r="K28" s="12" t="s">
         <v>2</v>
@@ -2374,17 +2341,17 @@
       <c r="L28" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="M28" s="15" t="n">
-        <v>47369.0</v>
+      <c r="M28" s="15">
+        <v>47369</v>
       </c>
       <c r="N28" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="O28" s="12" t="n">
-        <v>1209.0</v>
-      </c>
-      <c r="P28" s="12" t="n">
-        <v>9.0</v>
+      <c r="O28" s="12">
+        <v>1209</v>
+      </c>
+      <c r="P28" s="12">
+        <v>9</v>
       </c>
       <c r="Q28" s="16" t="s">
         <v>39</v>
@@ -2396,7 +2363,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B29" s="11" t="s">
         <v>2</v>
       </c>
@@ -2415,32 +2382,32 @@
       <c r="G29" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="H29" s="14" t="n">
-        <v>4401.0</v>
-      </c>
-      <c r="I29" s="14" t="n">
-        <v>5811.0</v>
-      </c>
-      <c r="J29" s="12" t="n">
+      <c r="H29" s="14">
+        <v>4401</v>
+      </c>
+      <c r="I29" s="14">
+        <v>5811</v>
+      </c>
+      <c r="J29" s="12">
         <v>1.32038173</v>
       </c>
       <c r="K29" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="L29" s="12" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="M29" s="15" t="n">
-        <v>135223.0</v>
-      </c>
-      <c r="N29" s="15" t="n">
-        <v>135223.0</v>
-      </c>
-      <c r="O29" s="12" t="n">
-        <v>5511.0</v>
-      </c>
-      <c r="P29" s="12" t="n">
-        <v>32.0</v>
+      <c r="L29" s="12">
+        <v>1</v>
+      </c>
+      <c r="M29" s="15">
+        <v>135223</v>
+      </c>
+      <c r="N29" s="15">
+        <v>135223</v>
+      </c>
+      <c r="O29" s="12">
+        <v>5511</v>
+      </c>
+      <c r="P29" s="12">
+        <v>32</v>
       </c>
       <c r="Q29" s="16" t="s">
         <v>40</v>
@@ -2452,7 +2419,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B30" s="11" t="s">
         <v>2</v>
       </c>
@@ -2471,32 +2438,32 @@
       <c r="G30" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="H30" s="14" t="n">
-        <v>4401.0</v>
-      </c>
-      <c r="I30" s="14" t="n">
-        <v>5811.0</v>
-      </c>
-      <c r="J30" s="12" t="n">
+      <c r="H30" s="14">
+        <v>4401</v>
+      </c>
+      <c r="I30" s="14">
+        <v>5811</v>
+      </c>
+      <c r="J30" s="12">
         <v>1.32038173</v>
       </c>
       <c r="K30" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="L30" s="12" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="M30" s="15" t="n">
-        <v>135223.0</v>
-      </c>
-      <c r="N30" s="15" t="n">
-        <v>135223.0</v>
-      </c>
-      <c r="O30" s="12" t="n">
-        <v>5511.0</v>
-      </c>
-      <c r="P30" s="12" t="n">
-        <v>32.0</v>
+      <c r="L30" s="12">
+        <v>1</v>
+      </c>
+      <c r="M30" s="15">
+        <v>135223</v>
+      </c>
+      <c r="N30" s="15">
+        <v>135223</v>
+      </c>
+      <c r="O30" s="12">
+        <v>5511</v>
+      </c>
+      <c r="P30" s="12">
+        <v>32</v>
       </c>
       <c r="Q30" s="16" t="s">
         <v>40</v>
@@ -2508,7 +2475,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B31" s="11" t="s">
         <v>2</v>
       </c>
@@ -2527,32 +2494,32 @@
       <c r="G31" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="H31" s="14" t="n">
-        <v>1442.0</v>
-      </c>
-      <c r="I31" s="14" t="n">
-        <v>2018.0</v>
-      </c>
-      <c r="J31" s="12" t="n">
-        <v>1.39944521</v>
+      <c r="H31" s="14">
+        <v>1442</v>
+      </c>
+      <c r="I31" s="14">
+        <v>2018</v>
+      </c>
+      <c r="J31" s="12">
+        <v>1.3994452100000001</v>
       </c>
       <c r="K31" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="L31" s="12" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="M31" s="15" t="n">
-        <v>98690.0</v>
-      </c>
-      <c r="N31" s="15" t="n">
-        <v>98690.0</v>
-      </c>
-      <c r="O31" s="12" t="n">
-        <v>1946.0</v>
-      </c>
-      <c r="P31" s="12" t="n">
-        <v>19.0</v>
+      <c r="L31" s="12">
+        <v>1</v>
+      </c>
+      <c r="M31" s="15">
+        <v>98690</v>
+      </c>
+      <c r="N31" s="15">
+        <v>98690</v>
+      </c>
+      <c r="O31" s="12">
+        <v>1946</v>
+      </c>
+      <c r="P31" s="12">
+        <v>19</v>
       </c>
       <c r="Q31" s="16" t="s">
         <v>41</v>
@@ -2564,7 +2531,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B32" s="11" t="s">
         <v>2</v>
       </c>
@@ -2583,32 +2550,32 @@
       <c r="G32" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="H32" s="14" t="n">
-        <v>1442.0</v>
-      </c>
-      <c r="I32" s="14" t="n">
-        <v>2018.0</v>
-      </c>
-      <c r="J32" s="12" t="n">
-        <v>1.39944521</v>
+      <c r="H32" s="14">
+        <v>1442</v>
+      </c>
+      <c r="I32" s="14">
+        <v>2018</v>
+      </c>
+      <c r="J32" s="12">
+        <v>1.3994452100000001</v>
       </c>
       <c r="K32" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="L32" s="12" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="M32" s="15" t="n">
-        <v>98690.0</v>
-      </c>
-      <c r="N32" s="15" t="n">
-        <v>98690.0</v>
-      </c>
-      <c r="O32" s="12" t="n">
-        <v>1946.0</v>
-      </c>
-      <c r="P32" s="12" t="n">
-        <v>19.0</v>
+      <c r="L32" s="12">
+        <v>1</v>
+      </c>
+      <c r="M32" s="15">
+        <v>98690</v>
+      </c>
+      <c r="N32" s="15">
+        <v>98690</v>
+      </c>
+      <c r="O32" s="12">
+        <v>1946</v>
+      </c>
+      <c r="P32" s="12">
+        <v>19</v>
       </c>
       <c r="Q32" s="16" t="s">
         <v>41</v>
@@ -2620,7 +2587,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B33" s="11" t="s">
         <v>2</v>
       </c>
@@ -2639,14 +2606,14 @@
       <c r="G33" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="H33" s="14" t="n">
-        <v>1410.0</v>
-      </c>
-      <c r="I33" s="14" t="n">
-        <v>1820.0</v>
-      </c>
-      <c r="J33" s="12" t="n">
-        <v>1.29078014</v>
+      <c r="H33" s="14">
+        <v>1410</v>
+      </c>
+      <c r="I33" s="14">
+        <v>1820</v>
+      </c>
+      <c r="J33" s="12">
+        <v>1.2907801400000001</v>
       </c>
       <c r="K33" s="12" t="s">
         <v>2</v>
@@ -2654,17 +2621,17 @@
       <c r="L33" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="M33" s="15" t="n">
-        <v>93493.0</v>
+      <c r="M33" s="15">
+        <v>93493</v>
       </c>
       <c r="N33" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="O33" s="12" t="n">
-        <v>1754.0</v>
-      </c>
-      <c r="P33" s="12" t="n">
-        <v>22.0</v>
+      <c r="O33" s="12">
+        <v>1754</v>
+      </c>
+      <c r="P33" s="12">
+        <v>22</v>
       </c>
       <c r="Q33" s="16" t="s">
         <v>42</v>
@@ -2676,7 +2643,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B34" s="11" t="s">
         <v>2</v>
       </c>
@@ -2695,14 +2662,14 @@
       <c r="G34" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="H34" s="14" t="n">
-        <v>1410.0</v>
-      </c>
-      <c r="I34" s="14" t="n">
-        <v>1820.0</v>
-      </c>
-      <c r="J34" s="12" t="n">
-        <v>1.29078014</v>
+      <c r="H34" s="14">
+        <v>1410</v>
+      </c>
+      <c r="I34" s="14">
+        <v>1820</v>
+      </c>
+      <c r="J34" s="12">
+        <v>1.2907801400000001</v>
       </c>
       <c r="K34" s="12" t="s">
         <v>2</v>
@@ -2710,17 +2677,17 @@
       <c r="L34" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="M34" s="15" t="n">
-        <v>93493.0</v>
+      <c r="M34" s="15">
+        <v>93493</v>
       </c>
       <c r="N34" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="O34" s="12" t="n">
-        <v>1754.0</v>
-      </c>
-      <c r="P34" s="12" t="n">
-        <v>22.0</v>
+      <c r="O34" s="12">
+        <v>1754</v>
+      </c>
+      <c r="P34" s="12">
+        <v>22</v>
       </c>
       <c r="Q34" s="16" t="s">
         <v>42</v>
@@ -2732,7 +2699,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B35" s="11" t="s">
         <v>2</v>
       </c>
@@ -2751,32 +2718,32 @@
       <c r="G35" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="H35" s="14" t="n">
-        <v>3364.0</v>
-      </c>
-      <c r="I35" s="14" t="n">
-        <v>4572.0</v>
-      </c>
-      <c r="J35" s="12" t="n">
+      <c r="H35" s="14">
+        <v>3364</v>
+      </c>
+      <c r="I35" s="14">
+        <v>4572</v>
+      </c>
+      <c r="J35" s="12">
         <v>1.35909631</v>
       </c>
       <c r="K35" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="L35" s="12" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="M35" s="15" t="n">
-        <v>148329.0</v>
-      </c>
-      <c r="N35" s="15" t="n">
-        <v>148329.0</v>
-      </c>
-      <c r="O35" s="12" t="n">
-        <v>4359.0</v>
-      </c>
-      <c r="P35" s="12" t="n">
-        <v>30.0</v>
+      <c r="L35" s="12">
+        <v>1</v>
+      </c>
+      <c r="M35" s="15">
+        <v>148329</v>
+      </c>
+      <c r="N35" s="15">
+        <v>148329</v>
+      </c>
+      <c r="O35" s="12">
+        <v>4359</v>
+      </c>
+      <c r="P35" s="12">
+        <v>30</v>
       </c>
       <c r="Q35" s="16" t="s">
         <v>43</v>
@@ -2788,7 +2755,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B36" s="11" t="s">
         <v>2</v>
       </c>
@@ -2807,32 +2774,32 @@
       <c r="G36" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="H36" s="14" t="n">
-        <v>3364.0</v>
-      </c>
-      <c r="I36" s="14" t="n">
-        <v>4572.0</v>
-      </c>
-      <c r="J36" s="12" t="n">
+      <c r="H36" s="14">
+        <v>3364</v>
+      </c>
+      <c r="I36" s="14">
+        <v>4572</v>
+      </c>
+      <c r="J36" s="12">
         <v>1.35909631</v>
       </c>
       <c r="K36" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="L36" s="12" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="M36" s="15" t="n">
-        <v>148329.0</v>
-      </c>
-      <c r="N36" s="15" t="n">
-        <v>148329.0</v>
-      </c>
-      <c r="O36" s="12" t="n">
-        <v>4359.0</v>
-      </c>
-      <c r="P36" s="12" t="n">
-        <v>30.0</v>
+      <c r="L36" s="12">
+        <v>1</v>
+      </c>
+      <c r="M36" s="15">
+        <v>148329</v>
+      </c>
+      <c r="N36" s="15">
+        <v>148329</v>
+      </c>
+      <c r="O36" s="12">
+        <v>4359</v>
+      </c>
+      <c r="P36" s="12">
+        <v>30</v>
       </c>
       <c r="Q36" s="16" t="s">
         <v>43</v>
@@ -2844,7 +2811,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B37" s="11" t="s">
         <v>2</v>
       </c>
@@ -2863,13 +2830,13 @@
       <c r="G37" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="H37" s="14" t="n">
-        <v>2402.0</v>
-      </c>
-      <c r="I37" s="14" t="n">
-        <v>3384.0</v>
-      </c>
-      <c r="J37" s="12" t="n">
+      <c r="H37" s="14">
+        <v>2402</v>
+      </c>
+      <c r="I37" s="14">
+        <v>3384</v>
+      </c>
+      <c r="J37" s="12">
         <v>1.40882598</v>
       </c>
       <c r="K37" s="12" t="s">
@@ -2878,17 +2845,17 @@
       <c r="L37" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="M37" s="15" t="n">
-        <v>100892.0</v>
+      <c r="M37" s="15">
+        <v>100892</v>
       </c>
       <c r="N37" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="O37" s="12" t="n">
-        <v>3046.0</v>
-      </c>
-      <c r="P37" s="12" t="n">
-        <v>22.0</v>
+      <c r="O37" s="12">
+        <v>3046</v>
+      </c>
+      <c r="P37" s="12">
+        <v>22</v>
       </c>
       <c r="Q37" s="16" t="s">
         <v>25</v>
@@ -2900,7 +2867,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B38" s="18" t="s">
         <v>2</v>
       </c>
@@ -2919,13 +2886,13 @@
       <c r="G38" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="H38" s="21" t="n">
-        <v>2402.0</v>
-      </c>
-      <c r="I38" s="21" t="n">
-        <v>3384.0</v>
-      </c>
-      <c r="J38" s="19" t="n">
+      <c r="H38" s="21">
+        <v>2402</v>
+      </c>
+      <c r="I38" s="21">
+        <v>3384</v>
+      </c>
+      <c r="J38" s="19">
         <v>1.40882598</v>
       </c>
       <c r="K38" s="19" t="s">
@@ -2934,17 +2901,17 @@
       <c r="L38" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="M38" s="22" t="n">
-        <v>100892.0</v>
+      <c r="M38" s="22">
+        <v>100892</v>
       </c>
       <c r="N38" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="O38" s="19" t="n">
-        <v>3046.0</v>
-      </c>
-      <c r="P38" s="19" t="n">
-        <v>22.0</v>
+      <c r="O38" s="19">
+        <v>3046</v>
+      </c>
+      <c r="P38" s="19">
+        <v>22</v>
       </c>
       <c r="Q38" s="23" t="s">
         <v>25</v>
@@ -2956,7 +2923,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B39" s="11" t="s">
         <v>44</v>
       </c>
@@ -2975,32 +2942,32 @@
       <c r="G39" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="H39" s="14" t="n">
-        <v>995.0</v>
-      </c>
-      <c r="I39" s="14" t="n">
-        <v>1599.0</v>
-      </c>
-      <c r="J39" s="12" t="n">
+      <c r="H39" s="14">
+        <v>995</v>
+      </c>
+      <c r="I39" s="14">
+        <v>1599</v>
+      </c>
+      <c r="J39" s="12">
         <v>1.60703518</v>
       </c>
       <c r="K39" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="L39" s="12" t="n">
-        <v>6.0</v>
-      </c>
-      <c r="M39" s="15" t="n">
-        <v>104684.0</v>
-      </c>
-      <c r="N39" s="15" t="n">
+      <c r="L39" s="12">
+        <v>6</v>
+      </c>
+      <c r="M39" s="15">
+        <v>104684</v>
+      </c>
+      <c r="N39" s="15">
         <v>17447.33333333</v>
       </c>
-      <c r="O39" s="12" t="n">
-        <v>1590.0</v>
-      </c>
-      <c r="P39" s="12" t="n">
-        <v>31.0</v>
+      <c r="O39" s="12">
+        <v>1590</v>
+      </c>
+      <c r="P39" s="12">
+        <v>31</v>
       </c>
       <c r="Q39" s="16" t="s">
         <v>25</v>
@@ -3012,7 +2979,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B40" s="11" t="s">
         <v>2</v>
       </c>
@@ -3031,13 +2998,13 @@
       <c r="G40" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="H40" s="14" t="n">
-        <v>83.0</v>
-      </c>
-      <c r="I40" s="14" t="n">
-        <v>95.0</v>
-      </c>
-      <c r="J40" s="12" t="n">
+      <c r="H40" s="14">
+        <v>83</v>
+      </c>
+      <c r="I40" s="14">
+        <v>95</v>
+      </c>
+      <c r="J40" s="12">
         <v>1.14457831</v>
       </c>
       <c r="K40" s="12" t="s">
@@ -3046,17 +3013,17 @@
       <c r="L40" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="M40" s="15" t="n">
-        <v>3893.0</v>
+      <c r="M40" s="15">
+        <v>3893</v>
       </c>
       <c r="N40" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="O40" s="12" t="n">
-        <v>92.0</v>
-      </c>
-      <c r="P40" s="12" t="n">
-        <v>1.0</v>
+      <c r="O40" s="12">
+        <v>92</v>
+      </c>
+      <c r="P40" s="12">
+        <v>1</v>
       </c>
       <c r="Q40" s="16" t="s">
         <v>32</v>
@@ -3068,7 +3035,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B41" s="11" t="s">
         <v>2</v>
       </c>
@@ -3087,13 +3054,13 @@
       <c r="G41" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="H41" s="14" t="n">
-        <v>83.0</v>
-      </c>
-      <c r="I41" s="14" t="n">
-        <v>95.0</v>
-      </c>
-      <c r="J41" s="12" t="n">
+      <c r="H41" s="14">
+        <v>83</v>
+      </c>
+      <c r="I41" s="14">
+        <v>95</v>
+      </c>
+      <c r="J41" s="12">
         <v>1.14457831</v>
       </c>
       <c r="K41" s="12" t="s">
@@ -3102,17 +3069,17 @@
       <c r="L41" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="M41" s="15" t="n">
-        <v>3893.0</v>
+      <c r="M41" s="15">
+        <v>3893</v>
       </c>
       <c r="N41" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="O41" s="12" t="n">
-        <v>92.0</v>
-      </c>
-      <c r="P41" s="12" t="n">
-        <v>1.0</v>
+      <c r="O41" s="12">
+        <v>92</v>
+      </c>
+      <c r="P41" s="12">
+        <v>1</v>
       </c>
       <c r="Q41" s="16" t="s">
         <v>32</v>
@@ -3124,7 +3091,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B42" s="11" t="s">
         <v>2</v>
       </c>
@@ -3143,32 +3110,32 @@
       <c r="G42" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="H42" s="14" t="n">
-        <v>305.0</v>
-      </c>
-      <c r="I42" s="14" t="n">
-        <v>408.0</v>
-      </c>
-      <c r="J42" s="12" t="n">
+      <c r="H42" s="14">
+        <v>305</v>
+      </c>
+      <c r="I42" s="14">
+        <v>408</v>
+      </c>
+      <c r="J42" s="12">
         <v>1.33770492</v>
       </c>
       <c r="K42" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="L42" s="12" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="M42" s="15" t="n">
-        <v>24007.0</v>
-      </c>
-      <c r="N42" s="15" t="n">
+      <c r="L42" s="12">
+        <v>2</v>
+      </c>
+      <c r="M42" s="15">
+        <v>24007</v>
+      </c>
+      <c r="N42" s="15">
         <v>12003.5</v>
       </c>
-      <c r="O42" s="12" t="n">
-        <v>415.0</v>
-      </c>
-      <c r="P42" s="12" t="n">
-        <v>5.0</v>
+      <c r="O42" s="12">
+        <v>415</v>
+      </c>
+      <c r="P42" s="12">
+        <v>5</v>
       </c>
       <c r="Q42" s="16" t="s">
         <v>33</v>
@@ -3180,7 +3147,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B43" s="11" t="s">
         <v>2</v>
       </c>
@@ -3199,32 +3166,32 @@
       <c r="G43" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="H43" s="14" t="n">
-        <v>305.0</v>
-      </c>
-      <c r="I43" s="14" t="n">
-        <v>408.0</v>
-      </c>
-      <c r="J43" s="12" t="n">
+      <c r="H43" s="14">
+        <v>305</v>
+      </c>
+      <c r="I43" s="14">
+        <v>408</v>
+      </c>
+      <c r="J43" s="12">
         <v>1.33770492</v>
       </c>
       <c r="K43" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="L43" s="12" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="M43" s="15" t="n">
-        <v>24007.0</v>
-      </c>
-      <c r="N43" s="15" t="n">
+      <c r="L43" s="12">
+        <v>2</v>
+      </c>
+      <c r="M43" s="15">
+        <v>24007</v>
+      </c>
+      <c r="N43" s="15">
         <v>12003.5</v>
       </c>
-      <c r="O43" s="12" t="n">
-        <v>415.0</v>
-      </c>
-      <c r="P43" s="12" t="n">
-        <v>5.0</v>
+      <c r="O43" s="12">
+        <v>415</v>
+      </c>
+      <c r="P43" s="12">
+        <v>5</v>
       </c>
       <c r="Q43" s="16" t="s">
         <v>33</v>
@@ -3236,7 +3203,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B44" s="11" t="s">
         <v>2</v>
       </c>
@@ -3255,32 +3222,32 @@
       <c r="G44" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="H44" s="14" t="n">
-        <v>216.0</v>
-      </c>
-      <c r="I44" s="14" t="n">
-        <v>308.0</v>
-      </c>
-      <c r="J44" s="12" t="n">
+      <c r="H44" s="14">
+        <v>216</v>
+      </c>
+      <c r="I44" s="14">
+        <v>308</v>
+      </c>
+      <c r="J44" s="12">
         <v>1.42592593</v>
       </c>
       <c r="K44" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="L44" s="12" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="M44" s="15" t="n">
-        <v>26578.0</v>
-      </c>
-      <c r="N44" s="15" t="n">
-        <v>8859.33333333</v>
-      </c>
-      <c r="O44" s="12" t="n">
-        <v>299.0</v>
-      </c>
-      <c r="P44" s="12" t="n">
-        <v>9.0</v>
+      <c r="L44" s="12">
+        <v>3</v>
+      </c>
+      <c r="M44" s="15">
+        <v>26578</v>
+      </c>
+      <c r="N44" s="15">
+        <v>8859.3333333299997</v>
+      </c>
+      <c r="O44" s="12">
+        <v>299</v>
+      </c>
+      <c r="P44" s="12">
+        <v>9</v>
       </c>
       <c r="Q44" s="16" t="s">
         <v>34</v>
@@ -3292,7 +3259,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B45" s="11" t="s">
         <v>2</v>
       </c>
@@ -3311,32 +3278,32 @@
       <c r="G45" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="H45" s="14" t="n">
-        <v>216.0</v>
-      </c>
-      <c r="I45" s="14" t="n">
-        <v>308.0</v>
-      </c>
-      <c r="J45" s="12" t="n">
+      <c r="H45" s="14">
+        <v>216</v>
+      </c>
+      <c r="I45" s="14">
+        <v>308</v>
+      </c>
+      <c r="J45" s="12">
         <v>1.42592593</v>
       </c>
       <c r="K45" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="L45" s="12" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="M45" s="15" t="n">
-        <v>26578.0</v>
-      </c>
-      <c r="N45" s="15" t="n">
-        <v>8859.33333333</v>
-      </c>
-      <c r="O45" s="12" t="n">
-        <v>299.0</v>
-      </c>
-      <c r="P45" s="12" t="n">
-        <v>9.0</v>
+      <c r="L45" s="12">
+        <v>3</v>
+      </c>
+      <c r="M45" s="15">
+        <v>26578</v>
+      </c>
+      <c r="N45" s="15">
+        <v>8859.3333333299997</v>
+      </c>
+      <c r="O45" s="12">
+        <v>299</v>
+      </c>
+      <c r="P45" s="12">
+        <v>9</v>
       </c>
       <c r="Q45" s="16" t="s">
         <v>34</v>
@@ -3348,7 +3315,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B46" s="11" t="s">
         <v>2</v>
       </c>
@@ -3367,32 +3334,32 @@
       <c r="G46" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="H46" s="14" t="n">
-        <v>291.0</v>
-      </c>
-      <c r="I46" s="14" t="n">
-        <v>371.0</v>
-      </c>
-      <c r="J46" s="12" t="n">
+      <c r="H46" s="14">
+        <v>291</v>
+      </c>
+      <c r="I46" s="14">
+        <v>371</v>
+      </c>
+      <c r="J46" s="12">
         <v>1.27491409</v>
       </c>
       <c r="K46" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="L46" s="12" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="M46" s="15" t="n">
-        <v>27404.0</v>
-      </c>
-      <c r="N46" s="15" t="n">
-        <v>27404.0</v>
-      </c>
-      <c r="O46" s="12" t="n">
-        <v>368.0</v>
-      </c>
-      <c r="P46" s="12" t="n">
-        <v>13.0</v>
+      <c r="L46" s="12">
+        <v>1</v>
+      </c>
+      <c r="M46" s="15">
+        <v>27404</v>
+      </c>
+      <c r="N46" s="15">
+        <v>27404</v>
+      </c>
+      <c r="O46" s="12">
+        <v>368</v>
+      </c>
+      <c r="P46" s="12">
+        <v>13</v>
       </c>
       <c r="Q46" s="16" t="s">
         <v>35</v>
@@ -3404,7 +3371,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B47" s="11" t="s">
         <v>2</v>
       </c>
@@ -3423,32 +3390,32 @@
       <c r="G47" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="H47" s="14" t="n">
-        <v>291.0</v>
-      </c>
-      <c r="I47" s="14" t="n">
-        <v>371.0</v>
-      </c>
-      <c r="J47" s="12" t="n">
+      <c r="H47" s="14">
+        <v>291</v>
+      </c>
+      <c r="I47" s="14">
+        <v>371</v>
+      </c>
+      <c r="J47" s="12">
         <v>1.27491409</v>
       </c>
       <c r="K47" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="L47" s="12" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="M47" s="15" t="n">
-        <v>27404.0</v>
-      </c>
-      <c r="N47" s="15" t="n">
-        <v>27404.0</v>
-      </c>
-      <c r="O47" s="12" t="n">
-        <v>368.0</v>
-      </c>
-      <c r="P47" s="12" t="n">
-        <v>13.0</v>
+      <c r="L47" s="12">
+        <v>1</v>
+      </c>
+      <c r="M47" s="15">
+        <v>27404</v>
+      </c>
+      <c r="N47" s="15">
+        <v>27404</v>
+      </c>
+      <c r="O47" s="12">
+        <v>368</v>
+      </c>
+      <c r="P47" s="12">
+        <v>13</v>
       </c>
       <c r="Q47" s="16" t="s">
         <v>35</v>
@@ -3460,7 +3427,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B48" s="11" t="s">
         <v>2</v>
       </c>
@@ -3479,14 +3446,14 @@
       <c r="G48" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="H48" s="14" t="n">
-        <v>362.0</v>
-      </c>
-      <c r="I48" s="14" t="n">
-        <v>417.0</v>
-      </c>
-      <c r="J48" s="12" t="n">
-        <v>1.1519337</v>
+      <c r="H48" s="14">
+        <v>362</v>
+      </c>
+      <c r="I48" s="14">
+        <v>417</v>
+      </c>
+      <c r="J48" s="12">
+        <v>1.1519337000000001</v>
       </c>
       <c r="K48" s="12" t="s">
         <v>2</v>
@@ -3494,17 +3461,17 @@
       <c r="L48" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="M48" s="15" t="n">
-        <v>22802.0</v>
+      <c r="M48" s="15">
+        <v>22802</v>
       </c>
       <c r="N48" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="O48" s="12" t="n">
-        <v>416.0</v>
-      </c>
-      <c r="P48" s="12" t="n">
-        <v>3.0</v>
+      <c r="O48" s="12">
+        <v>416</v>
+      </c>
+      <c r="P48" s="12">
+        <v>3</v>
       </c>
       <c r="Q48" s="16" t="s">
         <v>36</v>
@@ -3516,7 +3483,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B49" s="18" t="s">
         <v>2</v>
       </c>
@@ -3535,14 +3502,14 @@
       <c r="G49" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="H49" s="21" t="n">
-        <v>362.0</v>
-      </c>
-      <c r="I49" s="21" t="n">
-        <v>417.0</v>
-      </c>
-      <c r="J49" s="19" t="n">
-        <v>1.1519337</v>
+      <c r="H49" s="21">
+        <v>362</v>
+      </c>
+      <c r="I49" s="21">
+        <v>417</v>
+      </c>
+      <c r="J49" s="19">
+        <v>1.1519337000000001</v>
       </c>
       <c r="K49" s="19" t="s">
         <v>2</v>
@@ -3550,17 +3517,17 @@
       <c r="L49" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="M49" s="22" t="n">
-        <v>22802.0</v>
+      <c r="M49" s="22">
+        <v>22802</v>
       </c>
       <c r="N49" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="O49" s="19" t="n">
-        <v>416.0</v>
-      </c>
-      <c r="P49" s="19" t="n">
-        <v>3.0</v>
+      <c r="O49" s="19">
+        <v>416</v>
+      </c>
+      <c r="P49" s="19">
+        <v>3</v>
       </c>
       <c r="Q49" s="23" t="s">
         <v>36</v>
@@ -3574,40 +3541,25 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink location="" ref="C1"/>
+    <hyperlink ref="C1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R49"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetFormatPr defaultColWidth="12.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="19" max="16384" style="1" width="12.7109375"/>
-    <col min="18" max="18" style="1" width="23.4375" customWidth="true"/>
-    <col min="17" max="17" style="1" width="23.4375" customWidth="true"/>
-    <col min="16" max="16" style="1" width="23.4375" customWidth="true"/>
-    <col min="15" max="15" style="1" width="23.4375" customWidth="true"/>
-    <col min="14" max="14" style="1" width="23.4375" customWidth="true"/>
-    <col min="13" max="13" style="1" width="23.4375" customWidth="true"/>
-    <col min="12" max="12" style="1" width="23.4375" customWidth="true"/>
-    <col min="11" max="11" style="1" width="23.4375" customWidth="true"/>
-    <col min="10" max="10" style="1" width="23.4375" customWidth="true"/>
-    <col min="9" max="9" style="1" width="23.4375" customWidth="true"/>
-    <col min="8" max="8" style="1" width="23.4375" customWidth="true"/>
-    <col min="7" max="7" style="1" width="23.4375" customWidth="true"/>
-    <col min="6" max="6" style="1" width="23.4375" customWidth="true"/>
-    <col min="5" max="5" style="1" width="23.4375" customWidth="true"/>
-    <col min="4" max="4" style="1" width="23.4375" customWidth="true"/>
-    <col min="3" max="3" style="1" width="23.4375" customWidth="true"/>
-    <col min="2" max="2" style="1" width="58.59375" customWidth="true"/>
-    <col min="1" max="1" width="5.15625" style="1" customWidth="true"/>
+    <col min="1" max="1" width="5.1796875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="58.6328125" style="1" customWidth="1"/>
+    <col min="3" max="18" width="23.453125" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="12.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="33.0" customHeight="true" s="5" customFormat="true">
+    <row r="1" spans="1:18" s="5" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2"/>
       <c r="B1" s="3" t="s">
         <v>0</v>
@@ -3619,7 +3571,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B3" s="25" t="s">
         <v>3</v>
       </c>
@@ -3672,7 +3624,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B4" s="27" t="s">
         <v>20</v>
       </c>
@@ -3688,32 +3640,32 @@
       <c r="F4" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="G4" s="30" t="n">
-        <v>42735.0</v>
-      </c>
-      <c r="H4" s="30" t="n">
-        <v>68942.0</v>
-      </c>
-      <c r="I4" s="29" t="n">
-        <v>1.61324441</v>
+      <c r="G4" s="30">
+        <v>42735</v>
+      </c>
+      <c r="H4" s="30">
+        <v>68942</v>
+      </c>
+      <c r="I4" s="29">
+        <v>1.6132444100000001</v>
       </c>
       <c r="J4" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="K4" s="29" t="n">
-        <v>19.0</v>
-      </c>
-      <c r="L4" s="31" t="n">
-        <v>1437864.0</v>
-      </c>
-      <c r="M4" s="31" t="n">
-        <v>75677.05263158</v>
-      </c>
-      <c r="N4" s="29" t="n">
-        <v>63183.0</v>
-      </c>
-      <c r="O4" s="29" t="n">
-        <v>695.0</v>
+      <c r="K4" s="29">
+        <v>19</v>
+      </c>
+      <c r="L4" s="31">
+        <v>1437864</v>
+      </c>
+      <c r="M4" s="31">
+        <v>75677.052631579994</v>
+      </c>
+      <c r="N4" s="29">
+        <v>63183</v>
+      </c>
+      <c r="O4" s="29">
+        <v>695</v>
       </c>
       <c r="P4" s="32" t="s">
         <v>25</v>
@@ -3725,7 +3677,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B5" s="27" t="s">
         <v>20</v>
       </c>
@@ -3741,32 +3693,32 @@
       <c r="F5" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="G5" s="30" t="n">
-        <v>3445.0</v>
-      </c>
-      <c r="H5" s="30" t="n">
-        <v>4025.0</v>
-      </c>
-      <c r="I5" s="29" t="n">
+      <c r="G5" s="30">
+        <v>3445</v>
+      </c>
+      <c r="H5" s="30">
+        <v>4025</v>
+      </c>
+      <c r="I5" s="29">
         <v>1.16835994</v>
       </c>
       <c r="J5" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="K5" s="29" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="L5" s="31" t="n">
-        <v>117403.0</v>
-      </c>
-      <c r="M5" s="31" t="n">
-        <v>117403.0</v>
-      </c>
-      <c r="N5" s="29" t="n">
-        <v>3868.0</v>
-      </c>
-      <c r="O5" s="29" t="n">
-        <v>41.0</v>
+      <c r="K5" s="29">
+        <v>1</v>
+      </c>
+      <c r="L5" s="31">
+        <v>117403</v>
+      </c>
+      <c r="M5" s="31">
+        <v>117403</v>
+      </c>
+      <c r="N5" s="29">
+        <v>3868</v>
+      </c>
+      <c r="O5" s="29">
+        <v>41</v>
       </c>
       <c r="P5" s="32" t="s">
         <v>26</v>
@@ -3778,7 +3730,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B6" s="27" t="s">
         <v>20</v>
       </c>
@@ -3794,14 +3746,14 @@
       <c r="F6" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="G6" s="30" t="n">
-        <v>2654.0</v>
-      </c>
-      <c r="H6" s="30" t="n">
-        <v>2851.0</v>
-      </c>
-      <c r="I6" s="29" t="n">
-        <v>1.07422758</v>
+      <c r="G6" s="30">
+        <v>2654</v>
+      </c>
+      <c r="H6" s="30">
+        <v>2851</v>
+      </c>
+      <c r="I6" s="29">
+        <v>1.0742275800000001</v>
       </c>
       <c r="J6" s="29" t="s">
         <v>2</v>
@@ -3809,17 +3761,17 @@
       <c r="K6" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="L6" s="31" t="n">
-        <v>54224.0</v>
+      <c r="L6" s="31">
+        <v>54224</v>
       </c>
       <c r="M6" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="N6" s="29" t="n">
-        <v>2752.0</v>
-      </c>
-      <c r="O6" s="29" t="n">
-        <v>24.0</v>
+      <c r="N6" s="29">
+        <v>2752</v>
+      </c>
+      <c r="O6" s="29">
+        <v>24</v>
       </c>
       <c r="P6" s="32" t="s">
         <v>26</v>
@@ -3831,7 +3783,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B7" s="27" t="s">
         <v>20</v>
       </c>
@@ -3847,32 +3799,32 @@
       <c r="F7" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="G7" s="30" t="n">
-        <v>846.0</v>
-      </c>
-      <c r="H7" s="30" t="n">
-        <v>1120.0</v>
-      </c>
-      <c r="I7" s="29" t="n">
+      <c r="G7" s="30">
+        <v>846</v>
+      </c>
+      <c r="H7" s="30">
+        <v>1120</v>
+      </c>
+      <c r="I7" s="29">
         <v>1.32387707</v>
       </c>
       <c r="J7" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="K7" s="29" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="L7" s="31" t="n">
-        <v>60983.0</v>
-      </c>
-      <c r="M7" s="31" t="n">
-        <v>60983.0</v>
-      </c>
-      <c r="N7" s="29" t="n">
-        <v>1066.0</v>
-      </c>
-      <c r="O7" s="29" t="n">
-        <v>8.0</v>
+      <c r="K7" s="29">
+        <v>1</v>
+      </c>
+      <c r="L7" s="31">
+        <v>60983</v>
+      </c>
+      <c r="M7" s="31">
+        <v>60983</v>
+      </c>
+      <c r="N7" s="29">
+        <v>1066</v>
+      </c>
+      <c r="O7" s="29">
+        <v>8</v>
       </c>
       <c r="P7" s="32" t="s">
         <v>26</v>
@@ -3884,7 +3836,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B8" s="27" t="s">
         <v>20</v>
       </c>
@@ -3900,13 +3852,13 @@
       <c r="F8" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="G8" s="30" t="n">
-        <v>47.0</v>
-      </c>
-      <c r="H8" s="30" t="n">
-        <v>54.0</v>
-      </c>
-      <c r="I8" s="29" t="n">
+      <c r="G8" s="30">
+        <v>47</v>
+      </c>
+      <c r="H8" s="30">
+        <v>54</v>
+      </c>
+      <c r="I8" s="29">
         <v>1.14893617</v>
       </c>
       <c r="J8" s="29" t="s">
@@ -3915,17 +3867,17 @@
       <c r="K8" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="L8" s="31" t="n">
-        <v>2196.0</v>
+      <c r="L8" s="31">
+        <v>2196</v>
       </c>
       <c r="M8" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="N8" s="29" t="n">
-        <v>50.0</v>
-      </c>
-      <c r="O8" s="29" t="n">
-        <v>9.0</v>
+      <c r="N8" s="29">
+        <v>50</v>
+      </c>
+      <c r="O8" s="29">
+        <v>9</v>
       </c>
       <c r="P8" s="32" t="s">
         <v>26</v>
@@ -3937,7 +3889,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B9" s="27" t="s">
         <v>20</v>
       </c>
@@ -3953,32 +3905,32 @@
       <c r="F9" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="G9" s="30" t="n">
-        <v>7739.0</v>
-      </c>
-      <c r="H9" s="30" t="n">
-        <v>9209.0</v>
-      </c>
-      <c r="I9" s="29" t="n">
+      <c r="G9" s="30">
+        <v>7739</v>
+      </c>
+      <c r="H9" s="30">
+        <v>9209</v>
+      </c>
+      <c r="I9" s="29">
         <v>1.18994702</v>
       </c>
       <c r="J9" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="K9" s="29" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="L9" s="31" t="n">
-        <v>208929.0</v>
-      </c>
-      <c r="M9" s="31" t="n">
+      <c r="K9" s="29">
+        <v>8</v>
+      </c>
+      <c r="L9" s="31">
+        <v>208929</v>
+      </c>
+      <c r="M9" s="31">
         <v>26116.125</v>
       </c>
-      <c r="N9" s="29" t="n">
-        <v>9239.0</v>
-      </c>
-      <c r="O9" s="29" t="n">
-        <v>95.0</v>
+      <c r="N9" s="29">
+        <v>9239</v>
+      </c>
+      <c r="O9" s="29">
+        <v>95</v>
       </c>
       <c r="P9" s="32" t="s">
         <v>31</v>
@@ -3990,7 +3942,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B10" s="27" t="s">
         <v>20</v>
       </c>
@@ -4006,32 +3958,32 @@
       <c r="F10" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="G10" s="30" t="n">
-        <v>4620.0</v>
-      </c>
-      <c r="H10" s="30" t="n">
-        <v>4979.0</v>
-      </c>
-      <c r="I10" s="29" t="n">
-        <v>1.07770563</v>
+      <c r="G10" s="30">
+        <v>4620</v>
+      </c>
+      <c r="H10" s="30">
+        <v>4979</v>
+      </c>
+      <c r="I10" s="29">
+        <v>1.0777056300000001</v>
       </c>
       <c r="J10" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="K10" s="29" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="L10" s="31" t="n">
-        <v>90311.0</v>
-      </c>
-      <c r="M10" s="31" t="n">
+      <c r="K10" s="29">
+        <v>5</v>
+      </c>
+      <c r="L10" s="31">
+        <v>90311</v>
+      </c>
+      <c r="M10" s="31">
         <v>18062.2</v>
       </c>
-      <c r="N10" s="29" t="n">
-        <v>5019.0</v>
-      </c>
-      <c r="O10" s="29" t="n">
-        <v>59.0</v>
+      <c r="N10" s="29">
+        <v>5019</v>
+      </c>
+      <c r="O10" s="29">
+        <v>59</v>
       </c>
       <c r="P10" s="32" t="s">
         <v>31</v>
@@ -4043,7 +3995,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B11" s="27" t="s">
         <v>20</v>
       </c>
@@ -4059,32 +4011,32 @@
       <c r="F11" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="G11" s="30" t="n">
-        <v>3330.0</v>
-      </c>
-      <c r="H11" s="30" t="n">
-        <v>3948.0</v>
-      </c>
-      <c r="I11" s="29" t="n">
-        <v>1.18558559</v>
+      <c r="G11" s="30">
+        <v>3330</v>
+      </c>
+      <c r="H11" s="30">
+        <v>3948</v>
+      </c>
+      <c r="I11" s="29">
+        <v>1.1855855900000001</v>
       </c>
       <c r="J11" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="K11" s="29" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="L11" s="31" t="n">
-        <v>113822.0</v>
-      </c>
-      <c r="M11" s="31" t="n">
-        <v>37940.66666667</v>
-      </c>
-      <c r="N11" s="29" t="n">
-        <v>3962.0</v>
-      </c>
-      <c r="O11" s="29" t="n">
-        <v>34.0</v>
+      <c r="K11" s="29">
+        <v>3</v>
+      </c>
+      <c r="L11" s="31">
+        <v>113822</v>
+      </c>
+      <c r="M11" s="31">
+        <v>37940.666666669997</v>
+      </c>
+      <c r="N11" s="29">
+        <v>3962</v>
+      </c>
+      <c r="O11" s="29">
+        <v>34</v>
       </c>
       <c r="P11" s="32" t="s">
         <v>31</v>
@@ -4096,7 +4048,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B12" s="27" t="s">
         <v>20</v>
       </c>
@@ -4112,14 +4064,14 @@
       <c r="F12" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="G12" s="30" t="n">
-        <v>250.0</v>
-      </c>
-      <c r="H12" s="30" t="n">
-        <v>282.0</v>
-      </c>
-      <c r="I12" s="29" t="n">
-        <v>1.128</v>
+      <c r="G12" s="30">
+        <v>250</v>
+      </c>
+      <c r="H12" s="30">
+        <v>282</v>
+      </c>
+      <c r="I12" s="29">
+        <v>1.1279999999999999</v>
       </c>
       <c r="J12" s="29" t="s">
         <v>2</v>
@@ -4127,17 +4079,17 @@
       <c r="K12" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="L12" s="31" t="n">
-        <v>4796.0</v>
+      <c r="L12" s="31">
+        <v>4796</v>
       </c>
       <c r="M12" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="N12" s="29" t="n">
-        <v>258.0</v>
-      </c>
-      <c r="O12" s="29" t="n">
-        <v>2.0</v>
+      <c r="N12" s="29">
+        <v>258</v>
+      </c>
+      <c r="O12" s="29">
+        <v>2</v>
       </c>
       <c r="P12" s="32" t="s">
         <v>31</v>
@@ -4149,7 +4101,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B13" s="27" t="s">
         <v>20</v>
       </c>
@@ -4165,13 +4117,13 @@
       <c r="F13" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="G13" s="30" t="n">
-        <v>638.0</v>
-      </c>
-      <c r="H13" s="30" t="n">
-        <v>672.0</v>
-      </c>
-      <c r="I13" s="29" t="n">
+      <c r="G13" s="30">
+        <v>638</v>
+      </c>
+      <c r="H13" s="30">
+        <v>672</v>
+      </c>
+      <c r="I13" s="29">
         <v>1.05329154</v>
       </c>
       <c r="J13" s="29" t="s">
@@ -4180,17 +4132,17 @@
       <c r="K13" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="L13" s="31" t="n">
-        <v>5575.0</v>
+      <c r="L13" s="31">
+        <v>5575</v>
       </c>
       <c r="M13" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="N13" s="29" t="n">
-        <v>581.0</v>
-      </c>
-      <c r="O13" s="29" t="n">
-        <v>21.0</v>
+      <c r="N13" s="29">
+        <v>581</v>
+      </c>
+      <c r="O13" s="29">
+        <v>21</v>
       </c>
       <c r="P13" s="32" t="s">
         <v>32</v>
@@ -4202,7 +4154,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B14" s="27" t="s">
         <v>20</v>
       </c>
@@ -4218,13 +4170,13 @@
       <c r="F14" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="G14" s="30" t="n">
-        <v>638.0</v>
-      </c>
-      <c r="H14" s="30" t="n">
-        <v>672.0</v>
-      </c>
-      <c r="I14" s="29" t="n">
+      <c r="G14" s="30">
+        <v>638</v>
+      </c>
+      <c r="H14" s="30">
+        <v>672</v>
+      </c>
+      <c r="I14" s="29">
         <v>1.05329154</v>
       </c>
       <c r="J14" s="29" t="s">
@@ -4233,17 +4185,17 @@
       <c r="K14" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="L14" s="31" t="n">
-        <v>5575.0</v>
+      <c r="L14" s="31">
+        <v>5575</v>
       </c>
       <c r="M14" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="N14" s="29" t="n">
-        <v>581.0</v>
-      </c>
-      <c r="O14" s="29" t="n">
-        <v>21.0</v>
+      <c r="N14" s="29">
+        <v>581</v>
+      </c>
+      <c r="O14" s="29">
+        <v>21</v>
       </c>
       <c r="P14" s="32" t="s">
         <v>32</v>
@@ -4255,7 +4207,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B15" s="27" t="s">
         <v>20</v>
       </c>
@@ -4271,32 +4223,32 @@
       <c r="F15" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="G15" s="30" t="n">
-        <v>4425.0</v>
-      </c>
-      <c r="H15" s="30" t="n">
-        <v>5405.0</v>
-      </c>
-      <c r="I15" s="29" t="n">
-        <v>1.22146893</v>
+      <c r="G15" s="30">
+        <v>4425</v>
+      </c>
+      <c r="H15" s="30">
+        <v>5405</v>
+      </c>
+      <c r="I15" s="29">
+        <v>1.2214689299999999</v>
       </c>
       <c r="J15" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="K15" s="29" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="L15" s="31" t="n">
-        <v>88004.0</v>
-      </c>
-      <c r="M15" s="31" t="n">
-        <v>44002.0</v>
-      </c>
-      <c r="N15" s="29" t="n">
-        <v>4705.0</v>
-      </c>
-      <c r="O15" s="29" t="n">
-        <v>102.0</v>
+      <c r="K15" s="29">
+        <v>2</v>
+      </c>
+      <c r="L15" s="31">
+        <v>88004</v>
+      </c>
+      <c r="M15" s="31">
+        <v>44002</v>
+      </c>
+      <c r="N15" s="29">
+        <v>4705</v>
+      </c>
+      <c r="O15" s="29">
+        <v>102</v>
       </c>
       <c r="P15" s="32" t="s">
         <v>33</v>
@@ -4308,7 +4260,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B16" s="27" t="s">
         <v>20</v>
       </c>
@@ -4324,32 +4276,32 @@
       <c r="F16" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="G16" s="30" t="n">
-        <v>4425.0</v>
-      </c>
-      <c r="H16" s="30" t="n">
-        <v>5405.0</v>
-      </c>
-      <c r="I16" s="29" t="n">
-        <v>1.22146893</v>
+      <c r="G16" s="30">
+        <v>4425</v>
+      </c>
+      <c r="H16" s="30">
+        <v>5405</v>
+      </c>
+      <c r="I16" s="29">
+        <v>1.2214689299999999</v>
       </c>
       <c r="J16" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="K16" s="29" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="L16" s="31" t="n">
-        <v>88004.0</v>
-      </c>
-      <c r="M16" s="31" t="n">
-        <v>44002.0</v>
-      </c>
-      <c r="N16" s="29" t="n">
-        <v>4705.0</v>
-      </c>
-      <c r="O16" s="29" t="n">
-        <v>102.0</v>
+      <c r="K16" s="29">
+        <v>2</v>
+      </c>
+      <c r="L16" s="31">
+        <v>88004</v>
+      </c>
+      <c r="M16" s="31">
+        <v>44002</v>
+      </c>
+      <c r="N16" s="29">
+        <v>4705</v>
+      </c>
+      <c r="O16" s="29">
+        <v>102</v>
       </c>
       <c r="P16" s="32" t="s">
         <v>33</v>
@@ -4361,7 +4313,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B17" s="27" t="s">
         <v>20</v>
       </c>
@@ -4377,32 +4329,32 @@
       <c r="F17" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="G17" s="30" t="n">
-        <v>5384.0</v>
-      </c>
-      <c r="H17" s="30" t="n">
-        <v>6927.0</v>
-      </c>
-      <c r="I17" s="29" t="n">
-        <v>1.2865899</v>
+      <c r="G17" s="30">
+        <v>5384</v>
+      </c>
+      <c r="H17" s="30">
+        <v>6927</v>
+      </c>
+      <c r="I17" s="29">
+        <v>1.2865899000000001</v>
       </c>
       <c r="J17" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="K17" s="29" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="L17" s="31" t="n">
-        <v>116503.0</v>
-      </c>
-      <c r="M17" s="31" t="n">
+      <c r="K17" s="29">
+        <v>2</v>
+      </c>
+      <c r="L17" s="31">
+        <v>116503</v>
+      </c>
+      <c r="M17" s="31">
         <v>58251.5</v>
       </c>
-      <c r="N17" s="29" t="n">
-        <v>6052.0</v>
-      </c>
-      <c r="O17" s="29" t="n">
-        <v>114.0</v>
+      <c r="N17" s="29">
+        <v>6052</v>
+      </c>
+      <c r="O17" s="29">
+        <v>114</v>
       </c>
       <c r="P17" s="32" t="s">
         <v>34</v>
@@ -4414,7 +4366,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B18" s="27" t="s">
         <v>20</v>
       </c>
@@ -4430,32 +4382,32 @@
       <c r="F18" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="G18" s="30" t="n">
-        <v>5384.0</v>
-      </c>
-      <c r="H18" s="30" t="n">
-        <v>6927.0</v>
-      </c>
-      <c r="I18" s="29" t="n">
-        <v>1.2865899</v>
+      <c r="G18" s="30">
+        <v>5384</v>
+      </c>
+      <c r="H18" s="30">
+        <v>6927</v>
+      </c>
+      <c r="I18" s="29">
+        <v>1.2865899000000001</v>
       </c>
       <c r="J18" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="K18" s="29" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="L18" s="31" t="n">
-        <v>116503.0</v>
-      </c>
-      <c r="M18" s="31" t="n">
+      <c r="K18" s="29">
+        <v>2</v>
+      </c>
+      <c r="L18" s="31">
+        <v>116503</v>
+      </c>
+      <c r="M18" s="31">
         <v>58251.5</v>
       </c>
-      <c r="N18" s="29" t="n">
-        <v>6052.0</v>
-      </c>
-      <c r="O18" s="29" t="n">
-        <v>114.0</v>
+      <c r="N18" s="29">
+        <v>6052</v>
+      </c>
+      <c r="O18" s="29">
+        <v>114</v>
       </c>
       <c r="P18" s="32" t="s">
         <v>34</v>
@@ -4467,7 +4419,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B19" s="27" t="s">
         <v>20</v>
       </c>
@@ -4483,13 +4435,13 @@
       <c r="F19" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="G19" s="30" t="n">
-        <v>10291.0</v>
-      </c>
-      <c r="H19" s="30" t="n">
-        <v>12587.0</v>
-      </c>
-      <c r="I19" s="29" t="n">
+      <c r="G19" s="30">
+        <v>10291</v>
+      </c>
+      <c r="H19" s="30">
+        <v>12587</v>
+      </c>
+      <c r="I19" s="29">
         <v>1.22310757</v>
       </c>
       <c r="J19" s="29" t="s">
@@ -4498,17 +4450,17 @@
       <c r="K19" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="L19" s="31" t="n">
-        <v>102910.0</v>
+      <c r="L19" s="31">
+        <v>102910</v>
       </c>
       <c r="M19" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="N19" s="29" t="n">
-        <v>10752.0</v>
-      </c>
-      <c r="O19" s="29" t="n">
-        <v>123.0</v>
+      <c r="N19" s="29">
+        <v>10752</v>
+      </c>
+      <c r="O19" s="29">
+        <v>123</v>
       </c>
       <c r="P19" s="32" t="s">
         <v>35</v>
@@ -4520,7 +4472,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B20" s="27" t="s">
         <v>20</v>
       </c>
@@ -4536,13 +4488,13 @@
       <c r="F20" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="G20" s="30" t="n">
-        <v>10291.0</v>
-      </c>
-      <c r="H20" s="30" t="n">
-        <v>12587.0</v>
-      </c>
-      <c r="I20" s="29" t="n">
+      <c r="G20" s="30">
+        <v>10291</v>
+      </c>
+      <c r="H20" s="30">
+        <v>12587</v>
+      </c>
+      <c r="I20" s="29">
         <v>1.22310757</v>
       </c>
       <c r="J20" s="29" t="s">
@@ -4551,17 +4503,17 @@
       <c r="K20" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="L20" s="31" t="n">
-        <v>102910.0</v>
+      <c r="L20" s="31">
+        <v>102910</v>
       </c>
       <c r="M20" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="N20" s="29" t="n">
-        <v>10752.0</v>
-      </c>
-      <c r="O20" s="29" t="n">
-        <v>123.0</v>
+      <c r="N20" s="29">
+        <v>10752</v>
+      </c>
+      <c r="O20" s="29">
+        <v>123</v>
       </c>
       <c r="P20" s="32" t="s">
         <v>35</v>
@@ -4573,7 +4525,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B21" s="27" t="s">
         <v>20</v>
       </c>
@@ -4589,32 +4541,32 @@
       <c r="F21" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="G21" s="30" t="n">
-        <v>5423.0</v>
-      </c>
-      <c r="H21" s="30" t="n">
-        <v>6748.0</v>
-      </c>
-      <c r="I21" s="29" t="n">
-        <v>1.24432971</v>
+      <c r="G21" s="30">
+        <v>5423</v>
+      </c>
+      <c r="H21" s="30">
+        <v>6748</v>
+      </c>
+      <c r="I21" s="29">
+        <v>1.2443297099999999</v>
       </c>
       <c r="J21" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="K21" s="29" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="L21" s="31" t="n">
-        <v>77820.0</v>
-      </c>
-      <c r="M21" s="31" t="n">
-        <v>38910.0</v>
-      </c>
-      <c r="N21" s="29" t="n">
-        <v>6173.0</v>
-      </c>
-      <c r="O21" s="29" t="n">
-        <v>33.0</v>
+      <c r="K21" s="29">
+        <v>2</v>
+      </c>
+      <c r="L21" s="31">
+        <v>77820</v>
+      </c>
+      <c r="M21" s="31">
+        <v>38910</v>
+      </c>
+      <c r="N21" s="29">
+        <v>6173</v>
+      </c>
+      <c r="O21" s="29">
+        <v>33</v>
       </c>
       <c r="P21" s="32" t="s">
         <v>36</v>
@@ -4626,7 +4578,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B22" s="27" t="s">
         <v>20</v>
       </c>
@@ -4642,32 +4594,32 @@
       <c r="F22" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="G22" s="30" t="n">
-        <v>5423.0</v>
-      </c>
-      <c r="H22" s="30" t="n">
-        <v>6748.0</v>
-      </c>
-      <c r="I22" s="29" t="n">
-        <v>1.24432971</v>
+      <c r="G22" s="30">
+        <v>5423</v>
+      </c>
+      <c r="H22" s="30">
+        <v>6748</v>
+      </c>
+      <c r="I22" s="29">
+        <v>1.2443297099999999</v>
       </c>
       <c r="J22" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="K22" s="29" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="L22" s="31" t="n">
-        <v>77820.0</v>
-      </c>
-      <c r="M22" s="31" t="n">
-        <v>38910.0</v>
-      </c>
-      <c r="N22" s="29" t="n">
-        <v>6173.0</v>
-      </c>
-      <c r="O22" s="29" t="n">
-        <v>33.0</v>
+      <c r="K22" s="29">
+        <v>2</v>
+      </c>
+      <c r="L22" s="31">
+        <v>77820</v>
+      </c>
+      <c r="M22" s="31">
+        <v>38910</v>
+      </c>
+      <c r="N22" s="29">
+        <v>6173</v>
+      </c>
+      <c r="O22" s="29">
+        <v>33</v>
       </c>
       <c r="P22" s="32" t="s">
         <v>36</v>
@@ -4679,7 +4631,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B23" s="27" t="s">
         <v>20</v>
       </c>
@@ -4695,14 +4647,14 @@
       <c r="F23" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="G23" s="30" t="n">
-        <v>1143.0</v>
-      </c>
-      <c r="H23" s="30" t="n">
-        <v>1402.0</v>
-      </c>
-      <c r="I23" s="29" t="n">
-        <v>1.22659668</v>
+      <c r="G23" s="30">
+        <v>1143</v>
+      </c>
+      <c r="H23" s="30">
+        <v>1402</v>
+      </c>
+      <c r="I23" s="29">
+        <v>1.2265966800000001</v>
       </c>
       <c r="J23" s="29" t="s">
         <v>2</v>
@@ -4710,17 +4662,17 @@
       <c r="K23" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="L23" s="31" t="n">
-        <v>17415.0</v>
+      <c r="L23" s="31">
+        <v>17415</v>
       </c>
       <c r="M23" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="N23" s="29" t="n">
-        <v>1249.0</v>
-      </c>
-      <c r="O23" s="29" t="n">
-        <v>5.0</v>
+      <c r="N23" s="29">
+        <v>1249</v>
+      </c>
+      <c r="O23" s="29">
+        <v>5</v>
       </c>
       <c r="P23" s="32" t="s">
         <v>37</v>
@@ -4732,7 +4684,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B24" s="27" t="s">
         <v>20</v>
       </c>
@@ -4748,14 +4700,14 @@
       <c r="F24" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="G24" s="30" t="n">
-        <v>1143.0</v>
-      </c>
-      <c r="H24" s="30" t="n">
-        <v>1402.0</v>
-      </c>
-      <c r="I24" s="29" t="n">
-        <v>1.22659668</v>
+      <c r="G24" s="30">
+        <v>1143</v>
+      </c>
+      <c r="H24" s="30">
+        <v>1402</v>
+      </c>
+      <c r="I24" s="29">
+        <v>1.2265966800000001</v>
       </c>
       <c r="J24" s="29" t="s">
         <v>2</v>
@@ -4763,17 +4715,17 @@
       <c r="K24" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="L24" s="31" t="n">
-        <v>17415.0</v>
+      <c r="L24" s="31">
+        <v>17415</v>
       </c>
       <c r="M24" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="N24" s="29" t="n">
-        <v>1249.0</v>
-      </c>
-      <c r="O24" s="29" t="n">
-        <v>5.0</v>
+      <c r="N24" s="29">
+        <v>1249</v>
+      </c>
+      <c r="O24" s="29">
+        <v>5</v>
       </c>
       <c r="P24" s="32" t="s">
         <v>37</v>
@@ -4785,7 +4737,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B25" s="27" t="s">
         <v>20</v>
       </c>
@@ -4801,32 +4753,32 @@
       <c r="F25" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="G25" s="30" t="n">
-        <v>2339.0</v>
-      </c>
-      <c r="H25" s="30" t="n">
-        <v>3053.0</v>
-      </c>
-      <c r="I25" s="29" t="n">
+      <c r="G25" s="30">
+        <v>2339</v>
+      </c>
+      <c r="H25" s="30">
+        <v>3053</v>
+      </c>
+      <c r="I25" s="29">
         <v>1.30525866</v>
       </c>
       <c r="J25" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="K25" s="29" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="L25" s="31" t="n">
-        <v>79309.0</v>
-      </c>
-      <c r="M25" s="31" t="n">
-        <v>79309.0</v>
-      </c>
-      <c r="N25" s="29" t="n">
-        <v>2739.0</v>
-      </c>
-      <c r="O25" s="29" t="n">
-        <v>27.0</v>
+      <c r="K25" s="29">
+        <v>1</v>
+      </c>
+      <c r="L25" s="31">
+        <v>79309</v>
+      </c>
+      <c r="M25" s="31">
+        <v>79309</v>
+      </c>
+      <c r="N25" s="29">
+        <v>2739</v>
+      </c>
+      <c r="O25" s="29">
+        <v>27</v>
       </c>
       <c r="P25" s="32" t="s">
         <v>38</v>
@@ -4838,7 +4790,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B26" s="27" t="s">
         <v>20</v>
       </c>
@@ -4854,32 +4806,32 @@
       <c r="F26" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="G26" s="30" t="n">
-        <v>2339.0</v>
-      </c>
-      <c r="H26" s="30" t="n">
-        <v>3053.0</v>
-      </c>
-      <c r="I26" s="29" t="n">
+      <c r="G26" s="30">
+        <v>2339</v>
+      </c>
+      <c r="H26" s="30">
+        <v>3053</v>
+      </c>
+      <c r="I26" s="29">
         <v>1.30525866</v>
       </c>
       <c r="J26" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="K26" s="29" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="L26" s="31" t="n">
-        <v>79309.0</v>
-      </c>
-      <c r="M26" s="31" t="n">
-        <v>79309.0</v>
-      </c>
-      <c r="N26" s="29" t="n">
-        <v>2739.0</v>
-      </c>
-      <c r="O26" s="29" t="n">
-        <v>27.0</v>
+      <c r="K26" s="29">
+        <v>1</v>
+      </c>
+      <c r="L26" s="31">
+        <v>79309</v>
+      </c>
+      <c r="M26" s="31">
+        <v>79309</v>
+      </c>
+      <c r="N26" s="29">
+        <v>2739</v>
+      </c>
+      <c r="O26" s="29">
+        <v>27</v>
       </c>
       <c r="P26" s="32" t="s">
         <v>38</v>
@@ -4891,7 +4843,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B27" s="27" t="s">
         <v>20</v>
       </c>
@@ -4907,14 +4859,14 @@
       <c r="F27" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="G27" s="30" t="n">
-        <v>1073.0</v>
-      </c>
-      <c r="H27" s="30" t="n">
-        <v>1309.0</v>
-      </c>
-      <c r="I27" s="29" t="n">
-        <v>1.21994408</v>
+      <c r="G27" s="30">
+        <v>1073</v>
+      </c>
+      <c r="H27" s="30">
+        <v>1309</v>
+      </c>
+      <c r="I27" s="29">
+        <v>1.2199440800000001</v>
       </c>
       <c r="J27" s="29" t="s">
         <v>2</v>
@@ -4922,17 +4874,17 @@
       <c r="K27" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="L27" s="31" t="n">
-        <v>47369.0</v>
+      <c r="L27" s="31">
+        <v>47369</v>
       </c>
       <c r="M27" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="N27" s="29" t="n">
-        <v>1209.0</v>
-      </c>
-      <c r="O27" s="29" t="n">
-        <v>9.0</v>
+      <c r="N27" s="29">
+        <v>1209</v>
+      </c>
+      <c r="O27" s="29">
+        <v>9</v>
       </c>
       <c r="P27" s="32" t="s">
         <v>39</v>
@@ -4944,7 +4896,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B28" s="27" t="s">
         <v>20</v>
       </c>
@@ -4960,14 +4912,14 @@
       <c r="F28" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="G28" s="30" t="n">
-        <v>1073.0</v>
-      </c>
-      <c r="H28" s="30" t="n">
-        <v>1309.0</v>
-      </c>
-      <c r="I28" s="29" t="n">
-        <v>1.21994408</v>
+      <c r="G28" s="30">
+        <v>1073</v>
+      </c>
+      <c r="H28" s="30">
+        <v>1309</v>
+      </c>
+      <c r="I28" s="29">
+        <v>1.2199440800000001</v>
       </c>
       <c r="J28" s="29" t="s">
         <v>2</v>
@@ -4975,17 +4927,17 @@
       <c r="K28" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="L28" s="31" t="n">
-        <v>47369.0</v>
+      <c r="L28" s="31">
+        <v>47369</v>
       </c>
       <c r="M28" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="N28" s="29" t="n">
-        <v>1209.0</v>
-      </c>
-      <c r="O28" s="29" t="n">
-        <v>9.0</v>
+      <c r="N28" s="29">
+        <v>1209</v>
+      </c>
+      <c r="O28" s="29">
+        <v>9</v>
       </c>
       <c r="P28" s="32" t="s">
         <v>39</v>
@@ -4997,7 +4949,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B29" s="27" t="s">
         <v>20</v>
       </c>
@@ -5013,32 +4965,32 @@
       <c r="F29" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="G29" s="30" t="n">
-        <v>4401.0</v>
-      </c>
-      <c r="H29" s="30" t="n">
-        <v>5811.0</v>
-      </c>
-      <c r="I29" s="29" t="n">
+      <c r="G29" s="30">
+        <v>4401</v>
+      </c>
+      <c r="H29" s="30">
+        <v>5811</v>
+      </c>
+      <c r="I29" s="29">
         <v>1.32038173</v>
       </c>
       <c r="J29" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="K29" s="29" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="L29" s="31" t="n">
-        <v>135223.0</v>
-      </c>
-      <c r="M29" s="31" t="n">
-        <v>135223.0</v>
-      </c>
-      <c r="N29" s="29" t="n">
-        <v>5511.0</v>
-      </c>
-      <c r="O29" s="29" t="n">
-        <v>32.0</v>
+      <c r="K29" s="29">
+        <v>1</v>
+      </c>
+      <c r="L29" s="31">
+        <v>135223</v>
+      </c>
+      <c r="M29" s="31">
+        <v>135223</v>
+      </c>
+      <c r="N29" s="29">
+        <v>5511</v>
+      </c>
+      <c r="O29" s="29">
+        <v>32</v>
       </c>
       <c r="P29" s="32" t="s">
         <v>40</v>
@@ -5050,7 +5002,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B30" s="27" t="s">
         <v>20</v>
       </c>
@@ -5066,32 +5018,32 @@
       <c r="F30" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="G30" s="30" t="n">
-        <v>4401.0</v>
-      </c>
-      <c r="H30" s="30" t="n">
-        <v>5811.0</v>
-      </c>
-      <c r="I30" s="29" t="n">
+      <c r="G30" s="30">
+        <v>4401</v>
+      </c>
+      <c r="H30" s="30">
+        <v>5811</v>
+      </c>
+      <c r="I30" s="29">
         <v>1.32038173</v>
       </c>
       <c r="J30" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="K30" s="29" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="L30" s="31" t="n">
-        <v>135223.0</v>
-      </c>
-      <c r="M30" s="31" t="n">
-        <v>135223.0</v>
-      </c>
-      <c r="N30" s="29" t="n">
-        <v>5511.0</v>
-      </c>
-      <c r="O30" s="29" t="n">
-        <v>32.0</v>
+      <c r="K30" s="29">
+        <v>1</v>
+      </c>
+      <c r="L30" s="31">
+        <v>135223</v>
+      </c>
+      <c r="M30" s="31">
+        <v>135223</v>
+      </c>
+      <c r="N30" s="29">
+        <v>5511</v>
+      </c>
+      <c r="O30" s="29">
+        <v>32</v>
       </c>
       <c r="P30" s="32" t="s">
         <v>40</v>
@@ -5103,7 +5055,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B31" s="27" t="s">
         <v>20</v>
       </c>
@@ -5119,32 +5071,32 @@
       <c r="F31" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="G31" s="30" t="n">
-        <v>1442.0</v>
-      </c>
-      <c r="H31" s="30" t="n">
-        <v>2018.0</v>
-      </c>
-      <c r="I31" s="29" t="n">
-        <v>1.39944521</v>
+      <c r="G31" s="30">
+        <v>1442</v>
+      </c>
+      <c r="H31" s="30">
+        <v>2018</v>
+      </c>
+      <c r="I31" s="29">
+        <v>1.3994452100000001</v>
       </c>
       <c r="J31" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="K31" s="29" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="L31" s="31" t="n">
-        <v>98690.0</v>
-      </c>
-      <c r="M31" s="31" t="n">
-        <v>98690.0</v>
-      </c>
-      <c r="N31" s="29" t="n">
-        <v>1946.0</v>
-      </c>
-      <c r="O31" s="29" t="n">
-        <v>19.0</v>
+      <c r="K31" s="29">
+        <v>1</v>
+      </c>
+      <c r="L31" s="31">
+        <v>98690</v>
+      </c>
+      <c r="M31" s="31">
+        <v>98690</v>
+      </c>
+      <c r="N31" s="29">
+        <v>1946</v>
+      </c>
+      <c r="O31" s="29">
+        <v>19</v>
       </c>
       <c r="P31" s="32" t="s">
         <v>41</v>
@@ -5156,7 +5108,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B32" s="27" t="s">
         <v>20</v>
       </c>
@@ -5172,32 +5124,32 @@
       <c r="F32" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="G32" s="30" t="n">
-        <v>1442.0</v>
-      </c>
-      <c r="H32" s="30" t="n">
-        <v>2018.0</v>
-      </c>
-      <c r="I32" s="29" t="n">
-        <v>1.39944521</v>
+      <c r="G32" s="30">
+        <v>1442</v>
+      </c>
+      <c r="H32" s="30">
+        <v>2018</v>
+      </c>
+      <c r="I32" s="29">
+        <v>1.3994452100000001</v>
       </c>
       <c r="J32" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="K32" s="29" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="L32" s="31" t="n">
-        <v>98690.0</v>
-      </c>
-      <c r="M32" s="31" t="n">
-        <v>98690.0</v>
-      </c>
-      <c r="N32" s="29" t="n">
-        <v>1946.0</v>
-      </c>
-      <c r="O32" s="29" t="n">
-        <v>19.0</v>
+      <c r="K32" s="29">
+        <v>1</v>
+      </c>
+      <c r="L32" s="31">
+        <v>98690</v>
+      </c>
+      <c r="M32" s="31">
+        <v>98690</v>
+      </c>
+      <c r="N32" s="29">
+        <v>1946</v>
+      </c>
+      <c r="O32" s="29">
+        <v>19</v>
       </c>
       <c r="P32" s="32" t="s">
         <v>41</v>
@@ -5209,7 +5161,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B33" s="27" t="s">
         <v>20</v>
       </c>
@@ -5225,14 +5177,14 @@
       <c r="F33" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="G33" s="30" t="n">
-        <v>1410.0</v>
-      </c>
-      <c r="H33" s="30" t="n">
-        <v>1820.0</v>
-      </c>
-      <c r="I33" s="29" t="n">
-        <v>1.29078014</v>
+      <c r="G33" s="30">
+        <v>1410</v>
+      </c>
+      <c r="H33" s="30">
+        <v>1820</v>
+      </c>
+      <c r="I33" s="29">
+        <v>1.2907801400000001</v>
       </c>
       <c r="J33" s="29" t="s">
         <v>2</v>
@@ -5240,17 +5192,17 @@
       <c r="K33" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="L33" s="31" t="n">
-        <v>93493.0</v>
+      <c r="L33" s="31">
+        <v>93493</v>
       </c>
       <c r="M33" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="N33" s="29" t="n">
-        <v>1754.0</v>
-      </c>
-      <c r="O33" s="29" t="n">
-        <v>22.0</v>
+      <c r="N33" s="29">
+        <v>1754</v>
+      </c>
+      <c r="O33" s="29">
+        <v>22</v>
       </c>
       <c r="P33" s="32" t="s">
         <v>42</v>
@@ -5262,7 +5214,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B34" s="27" t="s">
         <v>20</v>
       </c>
@@ -5278,14 +5230,14 @@
       <c r="F34" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="G34" s="30" t="n">
-        <v>1410.0</v>
-      </c>
-      <c r="H34" s="30" t="n">
-        <v>1820.0</v>
-      </c>
-      <c r="I34" s="29" t="n">
-        <v>1.29078014</v>
+      <c r="G34" s="30">
+        <v>1410</v>
+      </c>
+      <c r="H34" s="30">
+        <v>1820</v>
+      </c>
+      <c r="I34" s="29">
+        <v>1.2907801400000001</v>
       </c>
       <c r="J34" s="29" t="s">
         <v>2</v>
@@ -5293,17 +5245,17 @@
       <c r="K34" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="L34" s="31" t="n">
-        <v>93493.0</v>
+      <c r="L34" s="31">
+        <v>93493</v>
       </c>
       <c r="M34" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="N34" s="29" t="n">
-        <v>1754.0</v>
-      </c>
-      <c r="O34" s="29" t="n">
-        <v>22.0</v>
+      <c r="N34" s="29">
+        <v>1754</v>
+      </c>
+      <c r="O34" s="29">
+        <v>22</v>
       </c>
       <c r="P34" s="32" t="s">
         <v>42</v>
@@ -5315,7 +5267,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B35" s="27" t="s">
         <v>20</v>
       </c>
@@ -5331,32 +5283,32 @@
       <c r="F35" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="G35" s="30" t="n">
-        <v>3364.0</v>
-      </c>
-      <c r="H35" s="30" t="n">
-        <v>4572.0</v>
-      </c>
-      <c r="I35" s="29" t="n">
+      <c r="G35" s="30">
+        <v>3364</v>
+      </c>
+      <c r="H35" s="30">
+        <v>4572</v>
+      </c>
+      <c r="I35" s="29">
         <v>1.35909631</v>
       </c>
       <c r="J35" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="K35" s="29" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="L35" s="31" t="n">
-        <v>148329.0</v>
-      </c>
-      <c r="M35" s="31" t="n">
-        <v>148329.0</v>
-      </c>
-      <c r="N35" s="29" t="n">
-        <v>4359.0</v>
-      </c>
-      <c r="O35" s="29" t="n">
-        <v>30.0</v>
+      <c r="K35" s="29">
+        <v>1</v>
+      </c>
+      <c r="L35" s="31">
+        <v>148329</v>
+      </c>
+      <c r="M35" s="31">
+        <v>148329</v>
+      </c>
+      <c r="N35" s="29">
+        <v>4359</v>
+      </c>
+      <c r="O35" s="29">
+        <v>30</v>
       </c>
       <c r="P35" s="32" t="s">
         <v>43</v>
@@ -5368,7 +5320,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B36" s="27" t="s">
         <v>20</v>
       </c>
@@ -5384,32 +5336,32 @@
       <c r="F36" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="G36" s="30" t="n">
-        <v>3364.0</v>
-      </c>
-      <c r="H36" s="30" t="n">
-        <v>4572.0</v>
-      </c>
-      <c r="I36" s="29" t="n">
+      <c r="G36" s="30">
+        <v>3364</v>
+      </c>
+      <c r="H36" s="30">
+        <v>4572</v>
+      </c>
+      <c r="I36" s="29">
         <v>1.35909631</v>
       </c>
       <c r="J36" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="K36" s="29" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="L36" s="31" t="n">
-        <v>148329.0</v>
-      </c>
-      <c r="M36" s="31" t="n">
-        <v>148329.0</v>
-      </c>
-      <c r="N36" s="29" t="n">
-        <v>4359.0</v>
-      </c>
-      <c r="O36" s="29" t="n">
-        <v>30.0</v>
+      <c r="K36" s="29">
+        <v>1</v>
+      </c>
+      <c r="L36" s="31">
+        <v>148329</v>
+      </c>
+      <c r="M36" s="31">
+        <v>148329</v>
+      </c>
+      <c r="N36" s="29">
+        <v>4359</v>
+      </c>
+      <c r="O36" s="29">
+        <v>30</v>
       </c>
       <c r="P36" s="32" t="s">
         <v>43</v>
@@ -5421,7 +5373,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B37" s="27" t="s">
         <v>20</v>
       </c>
@@ -5437,13 +5389,13 @@
       <c r="F37" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="G37" s="30" t="n">
-        <v>2402.0</v>
-      </c>
-      <c r="H37" s="30" t="n">
-        <v>3384.0</v>
-      </c>
-      <c r="I37" s="29" t="n">
+      <c r="G37" s="30">
+        <v>2402</v>
+      </c>
+      <c r="H37" s="30">
+        <v>3384</v>
+      </c>
+      <c r="I37" s="29">
         <v>1.40882598</v>
       </c>
       <c r="J37" s="29" t="s">
@@ -5452,17 +5404,17 @@
       <c r="K37" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="L37" s="31" t="n">
-        <v>100892.0</v>
+      <c r="L37" s="31">
+        <v>100892</v>
       </c>
       <c r="M37" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="N37" s="29" t="n">
-        <v>3046.0</v>
-      </c>
-      <c r="O37" s="29" t="n">
-        <v>22.0</v>
+      <c r="N37" s="29">
+        <v>3046</v>
+      </c>
+      <c r="O37" s="29">
+        <v>22</v>
       </c>
       <c r="P37" s="32" t="s">
         <v>25</v>
@@ -5474,7 +5426,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B38" s="27" t="s">
         <v>20</v>
       </c>
@@ -5490,13 +5442,13 @@
       <c r="F38" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="G38" s="30" t="n">
-        <v>2402.0</v>
-      </c>
-      <c r="H38" s="30" t="n">
-        <v>3384.0</v>
-      </c>
-      <c r="I38" s="29" t="n">
+      <c r="G38" s="30">
+        <v>2402</v>
+      </c>
+      <c r="H38" s="30">
+        <v>3384</v>
+      </c>
+      <c r="I38" s="29">
         <v>1.40882598</v>
       </c>
       <c r="J38" s="29" t="s">
@@ -5505,17 +5457,17 @@
       <c r="K38" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="L38" s="31" t="n">
-        <v>100892.0</v>
+      <c r="L38" s="31">
+        <v>100892</v>
       </c>
       <c r="M38" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="N38" s="29" t="n">
-        <v>3046.0</v>
-      </c>
-      <c r="O38" s="29" t="n">
-        <v>22.0</v>
+      <c r="N38" s="29">
+        <v>3046</v>
+      </c>
+      <c r="O38" s="29">
+        <v>22</v>
       </c>
       <c r="P38" s="32" t="s">
         <v>25</v>
@@ -5527,7 +5479,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B39" s="27" t="s">
         <v>44</v>
       </c>
@@ -5543,32 +5495,32 @@
       <c r="F39" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="G39" s="30" t="n">
-        <v>995.0</v>
-      </c>
-      <c r="H39" s="30" t="n">
-        <v>1599.0</v>
-      </c>
-      <c r="I39" s="29" t="n">
+      <c r="G39" s="30">
+        <v>995</v>
+      </c>
+      <c r="H39" s="30">
+        <v>1599</v>
+      </c>
+      <c r="I39" s="29">
         <v>1.60703518</v>
       </c>
       <c r="J39" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="K39" s="29" t="n">
-        <v>6.0</v>
-      </c>
-      <c r="L39" s="31" t="n">
-        <v>104684.0</v>
-      </c>
-      <c r="M39" s="31" t="n">
+      <c r="K39" s="29">
+        <v>6</v>
+      </c>
+      <c r="L39" s="31">
+        <v>104684</v>
+      </c>
+      <c r="M39" s="31">
         <v>17447.33333333</v>
       </c>
-      <c r="N39" s="29" t="n">
-        <v>1590.0</v>
-      </c>
-      <c r="O39" s="29" t="n">
-        <v>31.0</v>
+      <c r="N39" s="29">
+        <v>1590</v>
+      </c>
+      <c r="O39" s="29">
+        <v>31</v>
       </c>
       <c r="P39" s="32" t="s">
         <v>25</v>
@@ -5580,7 +5532,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B40" s="27" t="s">
         <v>44</v>
       </c>
@@ -5596,13 +5548,13 @@
       <c r="F40" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="G40" s="30" t="n">
-        <v>83.0</v>
-      </c>
-      <c r="H40" s="30" t="n">
-        <v>95.0</v>
-      </c>
-      <c r="I40" s="29" t="n">
+      <c r="G40" s="30">
+        <v>83</v>
+      </c>
+      <c r="H40" s="30">
+        <v>95</v>
+      </c>
+      <c r="I40" s="29">
         <v>1.14457831</v>
       </c>
       <c r="J40" s="29" t="s">
@@ -5611,17 +5563,17 @@
       <c r="K40" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="L40" s="31" t="n">
-        <v>3893.0</v>
+      <c r="L40" s="31">
+        <v>3893</v>
       </c>
       <c r="M40" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="N40" s="29" t="n">
-        <v>92.0</v>
-      </c>
-      <c r="O40" s="29" t="n">
-        <v>1.0</v>
+      <c r="N40" s="29">
+        <v>92</v>
+      </c>
+      <c r="O40" s="29">
+        <v>1</v>
       </c>
       <c r="P40" s="32" t="s">
         <v>32</v>
@@ -5633,7 +5585,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B41" s="27" t="s">
         <v>44</v>
       </c>
@@ -5649,13 +5601,13 @@
       <c r="F41" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="G41" s="30" t="n">
-        <v>83.0</v>
-      </c>
-      <c r="H41" s="30" t="n">
-        <v>95.0</v>
-      </c>
-      <c r="I41" s="29" t="n">
+      <c r="G41" s="30">
+        <v>83</v>
+      </c>
+      <c r="H41" s="30">
+        <v>95</v>
+      </c>
+      <c r="I41" s="29">
         <v>1.14457831</v>
       </c>
       <c r="J41" s="29" t="s">
@@ -5664,17 +5616,17 @@
       <c r="K41" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="L41" s="31" t="n">
-        <v>3893.0</v>
+      <c r="L41" s="31">
+        <v>3893</v>
       </c>
       <c r="M41" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="N41" s="29" t="n">
-        <v>92.0</v>
-      </c>
-      <c r="O41" s="29" t="n">
-        <v>1.0</v>
+      <c r="N41" s="29">
+        <v>92</v>
+      </c>
+      <c r="O41" s="29">
+        <v>1</v>
       </c>
       <c r="P41" s="32" t="s">
         <v>32</v>
@@ -5686,7 +5638,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B42" s="27" t="s">
         <v>44</v>
       </c>
@@ -5702,32 +5654,32 @@
       <c r="F42" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="G42" s="30" t="n">
-        <v>305.0</v>
-      </c>
-      <c r="H42" s="30" t="n">
-        <v>408.0</v>
-      </c>
-      <c r="I42" s="29" t="n">
+      <c r="G42" s="30">
+        <v>305</v>
+      </c>
+      <c r="H42" s="30">
+        <v>408</v>
+      </c>
+      <c r="I42" s="29">
         <v>1.33770492</v>
       </c>
       <c r="J42" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="K42" s="29" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="L42" s="31" t="n">
-        <v>24007.0</v>
-      </c>
-      <c r="M42" s="31" t="n">
+      <c r="K42" s="29">
+        <v>2</v>
+      </c>
+      <c r="L42" s="31">
+        <v>24007</v>
+      </c>
+      <c r="M42" s="31">
         <v>12003.5</v>
       </c>
-      <c r="N42" s="29" t="n">
-        <v>415.0</v>
-      </c>
-      <c r="O42" s="29" t="n">
-        <v>5.0</v>
+      <c r="N42" s="29">
+        <v>415</v>
+      </c>
+      <c r="O42" s="29">
+        <v>5</v>
       </c>
       <c r="P42" s="32" t="s">
         <v>33</v>
@@ -5739,7 +5691,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B43" s="27" t="s">
         <v>44</v>
       </c>
@@ -5755,32 +5707,32 @@
       <c r="F43" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="G43" s="30" t="n">
-        <v>305.0</v>
-      </c>
-      <c r="H43" s="30" t="n">
-        <v>408.0</v>
-      </c>
-      <c r="I43" s="29" t="n">
+      <c r="G43" s="30">
+        <v>305</v>
+      </c>
+      <c r="H43" s="30">
+        <v>408</v>
+      </c>
+      <c r="I43" s="29">
         <v>1.33770492</v>
       </c>
       <c r="J43" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="K43" s="29" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="L43" s="31" t="n">
-        <v>24007.0</v>
-      </c>
-      <c r="M43" s="31" t="n">
+      <c r="K43" s="29">
+        <v>2</v>
+      </c>
+      <c r="L43" s="31">
+        <v>24007</v>
+      </c>
+      <c r="M43" s="31">
         <v>12003.5</v>
       </c>
-      <c r="N43" s="29" t="n">
-        <v>415.0</v>
-      </c>
-      <c r="O43" s="29" t="n">
-        <v>5.0</v>
+      <c r="N43" s="29">
+        <v>415</v>
+      </c>
+      <c r="O43" s="29">
+        <v>5</v>
       </c>
       <c r="P43" s="32" t="s">
         <v>33</v>
@@ -5792,7 +5744,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B44" s="27" t="s">
         <v>44</v>
       </c>
@@ -5808,32 +5760,32 @@
       <c r="F44" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="G44" s="30" t="n">
-        <v>216.0</v>
-      </c>
-      <c r="H44" s="30" t="n">
-        <v>308.0</v>
-      </c>
-      <c r="I44" s="29" t="n">
+      <c r="G44" s="30">
+        <v>216</v>
+      </c>
+      <c r="H44" s="30">
+        <v>308</v>
+      </c>
+      <c r="I44" s="29">
         <v>1.42592593</v>
       </c>
       <c r="J44" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="K44" s="29" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="L44" s="31" t="n">
-        <v>26578.0</v>
-      </c>
-      <c r="M44" s="31" t="n">
-        <v>8859.33333333</v>
-      </c>
-      <c r="N44" s="29" t="n">
-        <v>299.0</v>
-      </c>
-      <c r="O44" s="29" t="n">
-        <v>9.0</v>
+      <c r="K44" s="29">
+        <v>3</v>
+      </c>
+      <c r="L44" s="31">
+        <v>26578</v>
+      </c>
+      <c r="M44" s="31">
+        <v>8859.3333333299997</v>
+      </c>
+      <c r="N44" s="29">
+        <v>299</v>
+      </c>
+      <c r="O44" s="29">
+        <v>9</v>
       </c>
       <c r="P44" s="32" t="s">
         <v>34</v>
@@ -5845,7 +5797,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B45" s="27" t="s">
         <v>44</v>
       </c>
@@ -5861,32 +5813,32 @@
       <c r="F45" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="G45" s="30" t="n">
-        <v>216.0</v>
-      </c>
-      <c r="H45" s="30" t="n">
-        <v>308.0</v>
-      </c>
-      <c r="I45" s="29" t="n">
+      <c r="G45" s="30">
+        <v>216</v>
+      </c>
+      <c r="H45" s="30">
+        <v>308</v>
+      </c>
+      <c r="I45" s="29">
         <v>1.42592593</v>
       </c>
       <c r="J45" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="K45" s="29" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="L45" s="31" t="n">
-        <v>26578.0</v>
-      </c>
-      <c r="M45" s="31" t="n">
-        <v>8859.33333333</v>
-      </c>
-      <c r="N45" s="29" t="n">
-        <v>299.0</v>
-      </c>
-      <c r="O45" s="29" t="n">
-        <v>9.0</v>
+      <c r="K45" s="29">
+        <v>3</v>
+      </c>
+      <c r="L45" s="31">
+        <v>26578</v>
+      </c>
+      <c r="M45" s="31">
+        <v>8859.3333333299997</v>
+      </c>
+      <c r="N45" s="29">
+        <v>299</v>
+      </c>
+      <c r="O45" s="29">
+        <v>9</v>
       </c>
       <c r="P45" s="32" t="s">
         <v>34</v>
@@ -5898,7 +5850,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B46" s="27" t="s">
         <v>44</v>
       </c>
@@ -5914,32 +5866,32 @@
       <c r="F46" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="G46" s="30" t="n">
-        <v>291.0</v>
-      </c>
-      <c r="H46" s="30" t="n">
-        <v>371.0</v>
-      </c>
-      <c r="I46" s="29" t="n">
+      <c r="G46" s="30">
+        <v>291</v>
+      </c>
+      <c r="H46" s="30">
+        <v>371</v>
+      </c>
+      <c r="I46" s="29">
         <v>1.27491409</v>
       </c>
       <c r="J46" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="K46" s="29" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="L46" s="31" t="n">
-        <v>27404.0</v>
-      </c>
-      <c r="M46" s="31" t="n">
-        <v>27404.0</v>
-      </c>
-      <c r="N46" s="29" t="n">
-        <v>368.0</v>
-      </c>
-      <c r="O46" s="29" t="n">
-        <v>13.0</v>
+      <c r="K46" s="29">
+        <v>1</v>
+      </c>
+      <c r="L46" s="31">
+        <v>27404</v>
+      </c>
+      <c r="M46" s="31">
+        <v>27404</v>
+      </c>
+      <c r="N46" s="29">
+        <v>368</v>
+      </c>
+      <c r="O46" s="29">
+        <v>13</v>
       </c>
       <c r="P46" s="32" t="s">
         <v>35</v>
@@ -5951,7 +5903,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B47" s="27" t="s">
         <v>44</v>
       </c>
@@ -5967,32 +5919,32 @@
       <c r="F47" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="G47" s="30" t="n">
-        <v>291.0</v>
-      </c>
-      <c r="H47" s="30" t="n">
-        <v>371.0</v>
-      </c>
-      <c r="I47" s="29" t="n">
+      <c r="G47" s="30">
+        <v>291</v>
+      </c>
+      <c r="H47" s="30">
+        <v>371</v>
+      </c>
+      <c r="I47" s="29">
         <v>1.27491409</v>
       </c>
       <c r="J47" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="K47" s="29" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="L47" s="31" t="n">
-        <v>27404.0</v>
-      </c>
-      <c r="M47" s="31" t="n">
-        <v>27404.0</v>
-      </c>
-      <c r="N47" s="29" t="n">
-        <v>368.0</v>
-      </c>
-      <c r="O47" s="29" t="n">
-        <v>13.0</v>
+      <c r="K47" s="29">
+        <v>1</v>
+      </c>
+      <c r="L47" s="31">
+        <v>27404</v>
+      </c>
+      <c r="M47" s="31">
+        <v>27404</v>
+      </c>
+      <c r="N47" s="29">
+        <v>368</v>
+      </c>
+      <c r="O47" s="29">
+        <v>13</v>
       </c>
       <c r="P47" s="32" t="s">
         <v>35</v>
@@ -6004,7 +5956,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B48" s="27" t="s">
         <v>44</v>
       </c>
@@ -6020,14 +5972,14 @@
       <c r="F48" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="G48" s="30" t="n">
-        <v>362.0</v>
-      </c>
-      <c r="H48" s="30" t="n">
-        <v>417.0</v>
-      </c>
-      <c r="I48" s="29" t="n">
-        <v>1.1519337</v>
+      <c r="G48" s="30">
+        <v>362</v>
+      </c>
+      <c r="H48" s="30">
+        <v>417</v>
+      </c>
+      <c r="I48" s="29">
+        <v>1.1519337000000001</v>
       </c>
       <c r="J48" s="29" t="s">
         <v>2</v>
@@ -6035,17 +5987,17 @@
       <c r="K48" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="L48" s="31" t="n">
-        <v>22802.0</v>
+      <c r="L48" s="31">
+        <v>22802</v>
       </c>
       <c r="M48" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="N48" s="29" t="n">
-        <v>416.0</v>
-      </c>
-      <c r="O48" s="29" t="n">
-        <v>3.0</v>
+      <c r="N48" s="29">
+        <v>416</v>
+      </c>
+      <c r="O48" s="29">
+        <v>3</v>
       </c>
       <c r="P48" s="32" t="s">
         <v>36</v>
@@ -6057,7 +6009,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B49" s="27" t="s">
         <v>44</v>
       </c>
@@ -6073,14 +6025,14 @@
       <c r="F49" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="G49" s="30" t="n">
-        <v>362.0</v>
-      </c>
-      <c r="H49" s="30" t="n">
-        <v>417.0</v>
-      </c>
-      <c r="I49" s="29" t="n">
-        <v>1.1519337</v>
+      <c r="G49" s="30">
+        <v>362</v>
+      </c>
+      <c r="H49" s="30">
+        <v>417</v>
+      </c>
+      <c r="I49" s="29">
+        <v>1.1519337000000001</v>
       </c>
       <c r="J49" s="29" t="s">
         <v>2</v>
@@ -6088,17 +6040,17 @@
       <c r="K49" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="L49" s="31" t="n">
-        <v>22802.0</v>
+      <c r="L49" s="31">
+        <v>22802</v>
       </c>
       <c r="M49" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="N49" s="29" t="n">
-        <v>416.0</v>
-      </c>
-      <c r="O49" s="29" t="n">
-        <v>3.0</v>
+      <c r="N49" s="29">
+        <v>416</v>
+      </c>
+      <c r="O49" s="29">
+        <v>3</v>
       </c>
       <c r="P49" s="32" t="s">
         <v>36</v>
@@ -6112,9 +6064,9 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink location="'Formatted Report'!A1" ref="C1"/>
+    <hyperlink ref="C1" location="'Formatted Report'!A1" display="This is raw data. See Sheet 1 for a formatted report." xr:uid="{00000000-0004-0000-0100-000000000000}"/>
   </hyperlinks>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/back/storage/app/ads/2026-10/meta-okt-Format.xlsx
+++ b/back/storage/app/ads/2026-10/meta-okt-Format.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\projects\pulse-kembaliapps\ads-performance\back\storage\app\ads\2026-10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7ACE688-B823-419D-A36B-35DDC40FFC2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{144C0B46-6717-45A9-989F-0D2A25FB0929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1782,7 +1782,7 @@
         <v>2</v>
       </c>
       <c r="M18" s="15">
-        <v>116503</v>
+        <v>685443</v>
       </c>
       <c r="N18" s="15">
         <v>58251.5</v>

--- a/back/storage/app/ads/2026-10/meta-okt-Format.xlsx
+++ b/back/storage/app/ads/2026-10/meta-okt-Format.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\projects\pulse-kembaliapps\ads-performance\back\storage\app\ads\2026-10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AF776EE-B52E-4A84-A08C-4A0560D08A81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0209B475-1A1F-4203-B997-0886670B2AAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -888,7 +888,7 @@
         <v>3</v>
       </c>
       <c r="K6" s="8">
-        <v>113822</v>
+        <v>213822</v>
       </c>
       <c r="L6" s="8">
         <v>37940.666666669997</v>
